--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\All Auto Post\LoL - Prorona\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{592F27B5-A818-4743-9D70-DFBF56738E55}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2DEB4FC2-963E-41E6-9DF9-33C66D3C5CE4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{CEBFA179-F109-4830-AF10-F3EF48EB9847}"/>
   </bookViews>
@@ -560,7 +560,7 @@
         <v>10</v>
       </c>
       <c r="E2" s="4">
-        <v>46248.020833333336</v>
+        <v>46248.024305555555</v>
       </c>
       <c r="F2" s="5" t="s">
         <v>11</v>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\All Auto Post\LoL - Prorona\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2DEB4FC2-963E-41E6-9DF9-33C66D3C5CE4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EA8F91D7-211A-4FD0-90C3-94DF91CB95B0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{CEBFA179-F109-4830-AF10-F3EF48EB9847}"/>
   </bookViews>
@@ -560,7 +560,7 @@
         <v>10</v>
       </c>
       <c r="E2" s="4">
-        <v>46248.024305555555</v>
+        <v>46248.03125</v>
       </c>
       <c r="F2" s="5" t="s">
         <v>11</v>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -629,9 +629,14 @@
       <c r="E3" s="4" t="n">
         <v>46250.19097222222</v>
       </c>
-      <c r="F3" s="5" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F3" s="6" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>2291191098377907</t>
         </is>
       </c>
     </row>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -662,9 +662,14 @@
       <c r="E4" s="4" t="n">
         <v>46250.27430555555</v>
       </c>
-      <c r="F4" s="5" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F4" s="6" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>1622086479254704</t>
         </is>
       </c>
     </row>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -695,9 +695,14 @@
       <c r="E5" s="4" t="n">
         <v>46250.73263888889</v>
       </c>
-      <c r="F5" s="5" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F5" s="6" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>2699114600853398</t>
         </is>
       </c>
     </row>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -728,9 +728,14 @@
       <c r="E6" s="4" t="n">
         <v>46250.89930555555</v>
       </c>
-      <c r="F6" s="5" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F6" s="6" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>1104023398740940</t>
         </is>
       </c>
     </row>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -16,7 +16,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="5">
+  <fonts count="6">
     <font>
       <name val="Aptos Narrow"/>
       <family val="2"/>
@@ -46,8 +46,14 @@
       <color rgb="FF155724"/>
       <sz val="10"/>
     </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="00155724"/>
+      <sz val="10"/>
+    </font>
   </fonts>
-  <fills count="6">
+  <fills count="7">
     <fill>
       <patternFill/>
     </fill>
@@ -72,6 +78,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFD4EDDA"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00D4EDDA"/>
       </patternFill>
     </fill>
   </fills>
@@ -102,7 +113,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -120,6 +131,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -941,9 +955,14 @@
       <c r="E13" s="4" t="n">
         <v>46256.27430555555</v>
       </c>
-      <c r="F13" s="5" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F13" s="7" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>1474306817793877</t>
         </is>
       </c>
     </row>
@@ -1029,9 +1048,14 @@
       <c r="E16" s="4" t="n">
         <v>46257.02430555555</v>
       </c>
-      <c r="F16" s="5" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F16" s="7" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>2652407565179181</t>
         </is>
       </c>
     </row>
@@ -1147,9 +1171,14 @@
       <c r="E20" s="4" t="n">
         <v>46257.89930555555</v>
       </c>
-      <c r="F20" s="5" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F20" s="7" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>1606877654176267</t>
         </is>
       </c>
     </row>
@@ -1235,9 +1264,14 @@
       <c r="E23" s="4" t="n">
         <v>46258.27430555555</v>
       </c>
-      <c r="F23" s="5" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F23" s="7" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>2938722929798630</t>
         </is>
       </c>
     </row>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -1,12 +1,12 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Content Calendar" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Content Calendar" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="191029" fullCalcOnLoad="1"/>
@@ -15,8 +15,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="6">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="dd-mm-yyyy hh:mm"/>
+  </numFmts>
+  <fonts count="7">
     <font>
       <name val="Aptos Narrow"/>
       <family val="2"/>
@@ -52,8 +54,14 @@
       <color rgb="00155724"/>
       <sz val="10"/>
     </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="008A5300"/>
+      <sz val="10"/>
+    </font>
   </fonts>
-  <fills count="7">
+  <fills count="8">
     <fill>
       <patternFill/>
     </fill>
@@ -85,6 +93,11 @@
         <fgColor rgb="00D4EDDA"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFE5B4"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -113,7 +126,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -134,6 +147,12 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -772,14 +791,12 @@
           <t>A resident in my aquarium that attracts attention 🪸 [9LqN2R5d_gs].mp4</t>
         </is>
       </c>
-      <c r="E7" s="4" t="inlineStr">
-        <is>
-          <t>21-08-2026 04:35</t>
-        </is>
-      </c>
-      <c r="F7" s="5" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="E7" s="8" t="n">
+        <v>46255.19097222222</v>
+      </c>
+      <c r="F7" s="9" t="inlineStr">
+        <is>
+          <t>Hold</t>
         </is>
       </c>
     </row>
@@ -802,14 +819,12 @@
           <t>A surprisingly easy way to make a snow bunny with your own feet 🐰👍？ [NukkZEF5bSw].mp4</t>
         </is>
       </c>
-      <c r="E8" s="4" t="inlineStr">
-        <is>
-          <t>21-08-2026 06:35</t>
-        </is>
-      </c>
-      <c r="F8" s="5" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="E8" s="8" t="n">
+        <v>46255.27430555555</v>
+      </c>
+      <c r="F8" s="9" t="inlineStr">
+        <is>
+          <t>Hold</t>
         </is>
       </c>
     </row>
@@ -832,14 +847,12 @@
           <t>A tutorial on how to eat watermelon on TikTok 🍉❓ [EK1Z5aEDdkE].mp4</t>
         </is>
       </c>
-      <c r="E9" s="4" t="inlineStr">
-        <is>
-          <t>21-08-2026 17:35</t>
-        </is>
-      </c>
-      <c r="F9" s="5" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="E9" s="8" t="n">
+        <v>46255.73263888889</v>
+      </c>
+      <c r="F9" s="9" t="inlineStr">
+        <is>
+          <t>Hold</t>
         </is>
       </c>
     </row>
@@ -862,14 +875,12 @@
           <t>A tutorial on how to properly remove elastic bands from braces 😬❓ [i7rWD3V2_H4].mp4</t>
         </is>
       </c>
-      <c r="E10" s="4" t="inlineStr">
-        <is>
-          <t>21-08-2026 21:35</t>
-        </is>
-      </c>
-      <c r="F10" s="5" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="E10" s="8" t="n">
+        <v>46255.89930555555</v>
+      </c>
+      <c r="F10" s="9" t="inlineStr">
+        <is>
+          <t>Hold</t>
         </is>
       </c>
     </row>
@@ -892,14 +903,12 @@
           <t>AI Challenge for Popular Football Players： Didn't Expect This Ending？ 😂👍 [ryGC_Vqyg4M].mp4</t>
         </is>
       </c>
-      <c r="E11" s="4" t="inlineStr">
-        <is>
-          <t>22-08-2026 00:35</t>
-        </is>
-      </c>
-      <c r="F11" s="5" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="E11" s="8" t="n">
+        <v>46256.02430555555</v>
+      </c>
+      <c r="F11" s="9" t="inlineStr">
+        <is>
+          <t>Hold</t>
         </is>
       </c>
     </row>
@@ -922,14 +931,12 @@
           <t>AI Chef Reveals BEST Vegetable Cutting Techniques [0ad5doh6g4Y].mp4</t>
         </is>
       </c>
-      <c r="E12" s="4" t="inlineStr">
-        <is>
-          <t>22-08-2026 04:35</t>
-        </is>
-      </c>
-      <c r="F12" s="5" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="E12" s="8" t="n">
+        <v>46256.19097222222</v>
+      </c>
+      <c r="F12" s="9" t="inlineStr">
+        <is>
+          <t>Hold</t>
         </is>
       </c>
     </row>
@@ -985,14 +992,12 @@
           <t>Coca-Cola Can Trick 👌❓ [BsvUuG6Ptb8].mp4</t>
         </is>
       </c>
-      <c r="E14" s="4" t="inlineStr">
-        <is>
-          <t>22-08-2026 17:35</t>
-        </is>
-      </c>
-      <c r="F14" s="5" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="E14" s="8" t="n">
+        <v>46256.73263888889</v>
+      </c>
+      <c r="F14" s="9" t="inlineStr">
+        <is>
+          <t>Hold</t>
         </is>
       </c>
     </row>
@@ -1015,14 +1020,12 @@
           <t>AI Makes Stylish Hairstyles 👩❓ [EMN3HpyvNQ8].mp4</t>
         </is>
       </c>
-      <c r="E15" s="4" t="inlineStr">
-        <is>
-          <t>22-08-2026 21:35</t>
-        </is>
-      </c>
-      <c r="F15" s="5" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="E15" s="8" t="n">
+        <v>46256.89930555555</v>
+      </c>
+      <c r="F15" s="9" t="inlineStr">
+        <is>
+          <t>Hold</t>
         </is>
       </c>
     </row>
@@ -1078,14 +1081,12 @@
           <t>After eating toys, I work part-time as a washing machine at a garbage dump🫧❓ [w0JMp4H2lvo].mp4</t>
         </is>
       </c>
-      <c r="E17" s="4" t="inlineStr">
-        <is>
-          <t>23-08-2026 04:35</t>
-        </is>
-      </c>
-      <c r="F17" s="5" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="E17" s="8" t="n">
+        <v>46257.19097222222</v>
+      </c>
+      <c r="F17" s="9" t="inlineStr">
+        <is>
+          <t>Hold</t>
         </is>
       </c>
     </row>
@@ -1108,14 +1109,12 @@
           <t>All this time you were sliding down the hill incorrectly🛝❓ [N6DDbaZxLRw].mp4</t>
         </is>
       </c>
-      <c r="E18" s="4" t="inlineStr">
-        <is>
-          <t>23-08-2026 06:35</t>
-        </is>
-      </c>
-      <c r="F18" s="5" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="E18" s="8" t="n">
+        <v>46257.27430555555</v>
+      </c>
+      <c r="F18" s="9" t="inlineStr">
+        <is>
+          <t>Hold</t>
         </is>
       </c>
     </row>
@@ -1138,14 +1137,12 @@
           <t>All this time you've been flossing incorrectly 😮👍？ [qc0OGfHnmFM].mp4</t>
         </is>
       </c>
-      <c r="E19" s="4" t="inlineStr">
-        <is>
-          <t>23-08-2026 17:35</t>
-        </is>
-      </c>
-      <c r="F19" s="5" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="E19" s="8" t="n">
+        <v>46257.73263888889</v>
+      </c>
+      <c r="F19" s="9" t="inlineStr">
+        <is>
+          <t>Hold</t>
         </is>
       </c>
     </row>
@@ -1201,14 +1198,12 @@
           <t>An Ordinary Day of a Man in His Prime [I5wBMPHApy0].mp4</t>
         </is>
       </c>
-      <c r="E21" s="4" t="inlineStr">
-        <is>
-          <t>24-08-2026 00:35</t>
-        </is>
-      </c>
-      <c r="F21" s="5" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="E21" s="8" t="n">
+        <v>46258.02430555555</v>
+      </c>
+      <c r="F21" s="9" t="inlineStr">
+        <is>
+          <t>Hold</t>
         </is>
       </c>
     </row>
@@ -1231,14 +1226,12 @@
           <t>An unexpected kiss from a stranger 💋❓ [BfEYEJkpAy0].mp4</t>
         </is>
       </c>
-      <c r="E22" s="4" t="inlineStr">
-        <is>
-          <t>24-08-2026 04:35</t>
-        </is>
-      </c>
-      <c r="F22" s="5" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="E22" s="8" t="n">
+        <v>46258.19097222222</v>
+      </c>
+      <c r="F22" s="9" t="inlineStr">
+        <is>
+          <t>Hold</t>
         </is>
       </c>
     </row>
@@ -1294,14 +1287,12 @@
           <t>Antistress Cat 🐱❓ [26w1IgnyN4Q].mp4</t>
         </is>
       </c>
-      <c r="E24" s="4" t="inlineStr">
-        <is>
-          <t>24-08-2026 17:35</t>
-        </is>
-      </c>
-      <c r="F24" s="5" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="E24" s="8" t="n">
+        <v>46258.73263888889</v>
+      </c>
+      <c r="F24" s="9" t="inlineStr">
+        <is>
+          <t>Hold</t>
         </is>
       </c>
     </row>
@@ -1324,14 +1315,12 @@
           <t>Anyone else seen this animation trend everywhere？😝🙏 [A4mYp1bqH6E].mp4</t>
         </is>
       </c>
-      <c r="E25" s="4" t="inlineStr">
-        <is>
-          <t>24-08-2026 21:35</t>
-        </is>
-      </c>
-      <c r="F25" s="5" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="E25" s="8" t="n">
+        <v>46258.89930555555</v>
+      </c>
+      <c r="F25" s="9" t="inlineStr">
+        <is>
+          <t>Hold</t>
         </is>
       </c>
     </row>
@@ -1354,14 +1343,12 @@
           <t>As a result, I ate this meme and became full 🐶❓ [LT-eVzgTl1M].mp4</t>
         </is>
       </c>
-      <c r="E26" s="4" t="inlineStr">
-        <is>
-          <t>25-08-2026 00:35</t>
-        </is>
-      </c>
-      <c r="F26" s="5" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="E26" s="8" t="n">
+        <v>46259.02430555555</v>
+      </c>
+      <c r="F26" s="9" t="inlineStr">
+        <is>
+          <t>Hold</t>
         </is>
       </c>
     </row>
@@ -1384,14 +1371,12 @@
           <t>Asked the AI ​​to cut the hair of a purebred white dog 🐶👍？ [XzaBvH7ShJI].mp4</t>
         </is>
       </c>
-      <c r="E27" s="4" t="inlineStr">
-        <is>
-          <t>25-08-2026 04:35</t>
-        </is>
-      </c>
-      <c r="F27" s="5" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="E27" s="8" t="n">
+        <v>46259.19097222222</v>
+      </c>
+      <c r="F27" s="9" t="inlineStr">
+        <is>
+          <t>Hold</t>
         </is>
       </c>
     </row>
@@ -1414,14 +1399,12 @@
           <t>Ate Ice Cream from a Dog and Turned into a DOG 🐶❓ [0bX39UI28w8].mp4</t>
         </is>
       </c>
-      <c r="E28" s="4" t="inlineStr">
-        <is>
-          <t>25-08-2026 06:35</t>
-        </is>
-      </c>
-      <c r="F28" s="5" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="E28" s="8" t="n">
+        <v>46259.27430555555</v>
+      </c>
+      <c r="F28" s="9" t="inlineStr">
+        <is>
+          <t>Hold</t>
         </is>
       </c>
     </row>
@@ -1444,10 +1427,8 @@
           <t>Ate SpongeBob 🧽❓ [8kp5LKNQ1w8].mp4</t>
         </is>
       </c>
-      <c r="E29" s="4" t="inlineStr">
-        <is>
-          <t>25-08-2026 17:35</t>
-        </is>
+      <c r="E29" s="8" t="n">
+        <v>46259.73263888889</v>
       </c>
       <c r="F29" s="5" t="inlineStr">
         <is>
@@ -1474,10 +1455,8 @@
           <t>Baby Shark + Bonus Sound 🦈❓ [mUqdYCXoN7Q].mp4</t>
         </is>
       </c>
-      <c r="E30" s="4" t="inlineStr">
-        <is>
-          <t>25-08-2026 21:35</t>
-        </is>
+      <c r="E30" s="8" t="n">
+        <v>46259.89930555555</v>
       </c>
       <c r="F30" s="5" t="inlineStr">
         <is>
@@ -1504,10 +1483,8 @@
           <t>Became a Fairy with This Trick 🧚🏻❓ [KxmdOakWOF8].mp4</t>
         </is>
       </c>
-      <c r="E31" s="4" t="inlineStr">
-        <is>
-          <t>26-08-2026 00:35</t>
-        </is>
+      <c r="E31" s="8" t="n">
+        <v>46260.02430555555</v>
       </c>
       <c r="F31" s="5" t="inlineStr">
         <is>
@@ -1534,10 +1511,8 @@
           <t>Became a Housekeeper for 24 Hours [H-2z-TFX6W0].mp4</t>
         </is>
       </c>
-      <c r="E32" s="4" t="inlineStr">
-        <is>
-          <t>26-08-2026 04:35</t>
-        </is>
+      <c r="E32" s="8" t="n">
+        <v>46260.19097222222</v>
       </c>
       <c r="F32" s="5" t="inlineStr">
         <is>
@@ -1564,10 +1539,8 @@
           <t>A Truly Scary Trend That I've Exploited More Than Once [9m59nALe_yM].mp4</t>
         </is>
       </c>
-      <c r="E33" s="4" t="inlineStr">
-        <is>
-          <t>26-08-2026 06:35</t>
-        </is>
+      <c r="E33" s="8" t="n">
+        <v>46260.27430555555</v>
       </c>
       <c r="F33" s="5" t="inlineStr">
         <is>
@@ -1594,10 +1567,8 @@
           <t>Became a Motorcycle for 24 Hours 🏍️💨 [ejQ49ozRsIg].mp4</t>
         </is>
       </c>
-      <c r="E34" s="4" t="inlineStr">
-        <is>
-          <t>26-08-2026 17:35</t>
-        </is>
+      <c r="E34" s="8" t="n">
+        <v>46260.73263888889</v>
       </c>
       <c r="F34" s="5" t="inlineStr">
         <is>
@@ -1624,10 +1595,8 @@
           <t>Became a Ship Captain for 24 Hours 🚢❓ [1nCIjwykpCk].mp4</t>
         </is>
       </c>
-      <c r="E35" s="4" t="inlineStr">
-        <is>
-          <t>26-08-2026 21:35</t>
-        </is>
+      <c r="E35" s="8" t="n">
+        <v>46260.89930555555</v>
       </c>
       <c r="F35" s="5" t="inlineStr">
         <is>
@@ -1654,10 +1623,8 @@
           <t>Became a Surfer for 24 Hours 🏄️ [lzXVM7k7bW4].mp4</t>
         </is>
       </c>
-      <c r="E36" s="4" t="inlineStr">
-        <is>
-          <t>27-08-2026 00:35</t>
-        </is>
+      <c r="E36" s="8" t="n">
+        <v>46261.02430555555</v>
       </c>
       <c r="F36" s="5" t="inlineStr">
         <is>
@@ -1684,10 +1651,8 @@
           <t>Became a hunter in the Amazon for 24 hours 𓐬❓ [SoK2d0AZj4s].mp4</t>
         </is>
       </c>
-      <c r="E37" s="4" t="inlineStr">
-        <is>
-          <t>27-08-2026 04:35</t>
-        </is>
+      <c r="E37" s="8" t="n">
+        <v>46261.19097222222</v>
       </c>
       <c r="F37" s="5" t="inlineStr">
         <is>
@@ -1714,10 +1679,8 @@
           <t>Became spiderman for 24 Hours 👍❓ [q91D1L7rZrU].mp4</t>
         </is>
       </c>
-      <c r="E38" s="4" t="inlineStr">
-        <is>
-          <t>27-08-2026 06:35</t>
-        </is>
+      <c r="E38" s="8" t="n">
+        <v>46261.27430555555</v>
       </c>
       <c r="F38" s="5" t="inlineStr">
         <is>
@@ -1744,10 +1707,8 @@
           <t>Boiled Egg Trick Kids Level vs Pro 🥚❓ [5VA-uSbpQW4].mp4</t>
         </is>
       </c>
-      <c r="E39" s="4" t="inlineStr">
-        <is>
-          <t>27-08-2026 17:35</t>
-        </is>
+      <c r="E39" s="8" t="n">
+        <v>46261.73263888889</v>
       </c>
       <c r="F39" s="5" t="inlineStr">
         <is>
@@ -1774,10 +1735,8 @@
           <t>Breaking that ice cream was the BEST mistake 😲🍦 [GtgPuWQyCdc].mp4</t>
         </is>
       </c>
-      <c r="E40" s="4" t="inlineStr">
-        <is>
-          <t>27-08-2026 21:35</t>
-        </is>
+      <c r="E40" s="8" t="n">
+        <v>46261.89930555555</v>
       </c>
       <c r="F40" s="5" t="inlineStr">
         <is>
@@ -1804,10 +1763,8 @@
           <t>Bubbles are flying out of my mouth in large quantities after such a dinner 🫧❓ [3bIMtPyiApE].mp4</t>
         </is>
       </c>
-      <c r="E41" s="4" t="inlineStr">
-        <is>
-          <t>28-08-2026 00:35</t>
-        </is>
+      <c r="E41" s="8" t="n">
+        <v>46262.02430555555</v>
       </c>
       <c r="F41" s="5" t="inlineStr">
         <is>
@@ -1834,10 +1791,8 @@
           <t>Buying Cold Drinks in India 🥛❓ [Va5-HXY6G1I].mp4</t>
         </is>
       </c>
-      <c r="E42" s="4" t="inlineStr">
-        <is>
-          <t>28-08-2026 04:35</t>
-        </is>
+      <c r="E42" s="8" t="n">
+        <v>46262.19097222222</v>
       </c>
       <c r="F42" s="5" t="inlineStr">
         <is>
@@ -1864,10 +1819,8 @@
           <t>Cake Crush ASMR 🎂❓ [V9M3qFrnFOk].mp4</t>
         </is>
       </c>
-      <c r="E43" s="4" t="inlineStr">
-        <is>
-          <t>28-08-2026 06:35</t>
-        </is>
+      <c r="E43" s="8" t="n">
+        <v>46262.27430555555</v>
       </c>
       <c r="F43" s="5" t="inlineStr">
         <is>
@@ -1894,10 +1847,8 @@
           <t>Can Only Geniuses Solve This？ 🧠 [TFj1B8flDKc].mp4</t>
         </is>
       </c>
-      <c r="E44" s="4" t="inlineStr">
-        <is>
-          <t>28-08-2026 17:35</t>
-        </is>
+      <c r="E44" s="8" t="n">
+        <v>46262.73263888889</v>
       </c>
       <c r="F44" s="5" t="inlineStr">
         <is>
@@ -1924,10 +1875,8 @@
           <t>Can You Peel the Cucumber Faster Than This？ 🥒 [6qmfkDrJLPQ].mp4</t>
         </is>
       </c>
-      <c r="E45" s="4" t="inlineStr">
-        <is>
-          <t>28-08-2026 21:35</t>
-        </is>
+      <c r="E45" s="8" t="n">
+        <v>46262.89930555555</v>
       </c>
       <c r="F45" s="5" t="inlineStr">
         <is>
@@ -1954,10 +1903,8 @@
           <t>Can You Really MASTER This Thousand Year Old PUZZLE？ [BpaNMjE6lKM].mp4</t>
         </is>
       </c>
-      <c r="E46" s="4" t="inlineStr">
-        <is>
-          <t>29-08-2026 00:35</t>
-        </is>
+      <c r="E46" s="8" t="n">
+        <v>46263.02430555555</v>
       </c>
       <c r="F46" s="5" t="inlineStr">
         <is>
@@ -1984,10 +1931,8 @@
           <t>A TikTok Challenge That Turned Into a Delicious Delicacy 💩❓ [lrNnzZed_Uk].mp4</t>
         </is>
       </c>
-      <c r="E47" s="4" t="inlineStr">
-        <is>
-          <t>29-08-2026 04:35</t>
-        </is>
+      <c r="E47" s="8" t="n">
+        <v>46263.19097222222</v>
       </c>
       <c r="F47" s="5" t="inlineStr">
         <is>
@@ -2014,10 +1959,8 @@
           <t>Can we beat this record？👍 [qycNzWSuelw].mp4</t>
         </is>
       </c>
-      <c r="E48" s="4" t="inlineStr">
-        <is>
-          <t>29-08-2026 06:35</t>
-        </is>
+      <c r="E48" s="8" t="n">
+        <v>46263.27430555555</v>
       </c>
       <c r="F48" s="5" t="inlineStr">
         <is>
@@ -2044,10 +1987,8 @@
           <t>Car Transformed into a Snow Monster 🥶❓ [V82IEhmW-sw].mp4</t>
         </is>
       </c>
-      <c r="E49" s="4" t="inlineStr">
-        <is>
-          <t>29-08-2026 17:35</t>
-        </is>
+      <c r="E49" s="8" t="n">
+        <v>46263.73263888889</v>
       </c>
       <c r="F49" s="5" t="inlineStr">
         <is>
@@ -2074,10 +2015,8 @@
           <t>A Life Hack That Destroys Your Apartment 😂❓ [hgjd9pofbF4].mp4</t>
         </is>
       </c>
-      <c r="E50" s="4" t="inlineStr">
-        <is>
-          <t>29-08-2026 21:35</t>
-        </is>
+      <c r="E50" s="8" t="n">
+        <v>46263.89930555555</v>
       </c>
       <c r="F50" s="5" t="inlineStr">
         <is>
@@ -2104,10 +2043,8 @@
           <t>Cat With An Axe It's Terribly Scary 😹👍❓ [A9UPGNm4_ls].mp4</t>
         </is>
       </c>
-      <c r="E51" s="4" t="inlineStr">
-        <is>
-          <t>30-08-2026 00:35</t>
-        </is>
+      <c r="E51" s="8" t="n">
+        <v>46264.02430555555</v>
       </c>
       <c r="F51" s="5" t="inlineStr">
         <is>
@@ -2134,10 +2071,8 @@
           <t>Cats Want Meat But I'm Hungry Too 🐱❓ [gSxzBVCqu6c].mp4</t>
         </is>
       </c>
-      <c r="E52" s="4" t="inlineStr">
-        <is>
-          <t>30-08-2026 04:35</t>
-        </is>
+      <c r="E52" s="8" t="n">
+        <v>46264.19097222222</v>
       </c>
       <c r="F52" s="5" t="inlineStr">
         <is>
@@ -2164,10 +2099,8 @@
           <t>Caught a Ryaba for Dinner at the Neighbors' Plot 🐟❓ [hbgphnDZFro].mp4</t>
         </is>
       </c>
-      <c r="E53" s="4" t="inlineStr">
-        <is>
-          <t>30-08-2026 06:35</t>
-        </is>
+      <c r="E53" s="8" t="n">
+        <v>46264.27430555555</v>
       </c>
       <c r="F53" s="5" t="inlineStr">
         <is>
@@ -2194,10 +2127,8 @@
           <t>Checked if this drill actually works 😠❓ [VWneXJjj8g8].mp4</t>
         </is>
       </c>
-      <c r="E54" s="4" t="inlineStr">
-        <is>
-          <t>30-08-2026 17:35</t>
-        </is>
+      <c r="E54" s="8" t="n">
+        <v>46264.73263888889</v>
       </c>
       <c r="F54" s="5" t="inlineStr">
         <is>
@@ -2224,10 +2155,8 @@
           <t>Cherry Prank Gone WRONG 😂🍒 [9f4tLYL5oOE].mp4</t>
         </is>
       </c>
-      <c r="E55" s="4" t="inlineStr">
-        <is>
-          <t>30-08-2026 21:35</t>
-        </is>
+      <c r="E55" s="8" t="n">
+        <v>46264.89930555555</v>
       </c>
       <c r="F55" s="5" t="inlineStr">
         <is>
@@ -2254,10 +2183,8 @@
           <t>Children's Reaction to SCORPIO 🦂❓ [zE-yn0dRcH0].mp4</t>
         </is>
       </c>
-      <c r="E56" s="4" t="inlineStr">
-        <is>
-          <t>31-08-2026 00:35</t>
-        </is>
+      <c r="E56" s="8" t="n">
+        <v>46265.02430555555</v>
       </c>
       <c r="F56" s="5" t="inlineStr">
         <is>
@@ -2284,10 +2211,8 @@
           <t>Choose your mouth 👄❓ [F367EU4FjfE].mp4</t>
         </is>
       </c>
-      <c r="E57" s="4" t="inlineStr">
-        <is>
-          <t>31-08-2026 04:35</t>
-        </is>
+      <c r="E57" s="8" t="n">
+        <v>46265.19097222222</v>
       </c>
       <c r="F57" s="5" t="inlineStr">
         <is>
@@ -2314,10 +2239,8 @@
           <t>Coca Cola + Mentos in a giant rubber ball 👍❓ [XmYj9s2CamQ].mp4</t>
         </is>
       </c>
-      <c r="E58" s="4" t="inlineStr">
-        <is>
-          <t>31-08-2026 06:35</t>
-        </is>
+      <c r="E58" s="8" t="n">
+        <v>46265.27430555555</v>
       </c>
       <c r="F58" s="5" t="inlineStr">
         <is>
@@ -2344,10 +2267,8 @@
           <t>How Rich People Fall Asleep VS Poor 💰 [k6VNzMB4zXw].mp4</t>
         </is>
       </c>
-      <c r="E59" s="4" t="inlineStr">
-        <is>
-          <t>31-08-2026 17:35</t>
-        </is>
+      <c r="E59" s="8" t="n">
+        <v>46265.73263888889</v>
       </c>
       <c r="F59" s="5" t="inlineStr">
         <is>
@@ -2374,10 +2295,8 @@
           <t>Conquered the TV to Watch Cartoons 📺❓ [_orKyOUrcZo].mp4</t>
         </is>
       </c>
-      <c r="E60" s="4" t="inlineStr">
-        <is>
-          <t>31-08-2026 21:35</t>
-        </is>
+      <c r="E60" s="8" t="n">
+        <v>46265.89930555555</v>
       </c>
       <c r="F60" s="5" t="inlineStr">
         <is>
@@ -2404,10 +2323,8 @@
           <t>Corrected the Diet for a Pregnant Woman 👍❓ [vNrHnQ-a8ZI].mp4</t>
         </is>
       </c>
-      <c r="E61" s="4" t="inlineStr">
-        <is>
-          <t>01-09-2026 00:35</t>
-        </is>
+      <c r="E61" s="8" t="n">
+        <v>46266.02430555555</v>
       </c>
       <c r="F61" s="5" t="inlineStr">
         <is>
@@ -2434,10 +2351,8 @@
           <t>Corrected this misunderstanding [7J1xY7_fGuU].mp4</t>
         </is>
       </c>
-      <c r="E62" s="4" t="inlineStr">
-        <is>
-          <t>01-09-2026 04:35</t>
-        </is>
+      <c r="E62" s="8" t="n">
+        <v>46266.19097222222</v>
       </c>
       <c r="F62" s="5" t="inlineStr">
         <is>
@@ -2464,10 +2379,8 @@
           <t>Crazy 3D Animation 👍❓ [w1ngQMyeKiI].mp4</t>
         </is>
       </c>
-      <c r="E63" s="4" t="inlineStr">
-        <is>
-          <t>01-09-2026 06:35</t>
-        </is>
+      <c r="E63" s="8" t="n">
+        <v>46266.27430555555</v>
       </c>
       <c r="F63" s="5" t="inlineStr">
         <is>
@@ -2494,10 +2407,8 @@
           <t>Crazy AI 3D Animation That Looks Too Real 👍❓ [pC3In-fvfLg].mp4</t>
         </is>
       </c>
-      <c r="E64" s="4" t="inlineStr">
-        <is>
-          <t>01-09-2026 17:35</t>
-        </is>
+      <c r="E64" s="8" t="n">
+        <v>46266.73263888889</v>
       </c>
       <c r="F64" s="5" t="inlineStr">
         <is>
@@ -2524,10 +2435,8 @@
           <t>AI Made a VIDEO of a GIRL Lifting a Barbell with One Arm 👍❓ [U7EXGWlH0NI].mp4</t>
         </is>
       </c>
-      <c r="E65" s="4" t="inlineStr">
-        <is>
-          <t>01-09-2026 21:35</t>
-        </is>
+      <c r="E65" s="8" t="n">
+        <v>46266.89930555555</v>
       </c>
       <c r="F65" s="5" t="inlineStr">
         <is>
@@ -2554,10 +2463,8 @@
           <t>Crazy Banana Slicer 🍌❓ [qxgzFr5NYrA].mp4</t>
         </is>
       </c>
-      <c r="E66" s="4" t="inlineStr">
-        <is>
-          <t>02-09-2026 00:35</t>
-        </is>
+      <c r="E66" s="8" t="n">
+        <v>46267.02430555555</v>
       </c>
       <c r="F66" s="5" t="inlineStr">
         <is>
@@ -2584,10 +2491,8 @@
           <t>Crazy Modernization Didn't Lead to Anything Good 💩❓ [X_5r6Jn37FQ].mp4</t>
         </is>
       </c>
-      <c r="E67" s="4" t="inlineStr">
-        <is>
-          <t>02-09-2026 04:35</t>
-        </is>
+      <c r="E67" s="8" t="n">
+        <v>46267.19097222222</v>
       </c>
       <c r="F67" s="5" t="inlineStr">
         <is>
@@ -2614,10 +2519,8 @@
           <t>Create Your Own Face TikTok Challenge👶❓ [2QFOgvyFEKw].mp4</t>
         </is>
       </c>
-      <c r="E68" s="4" t="inlineStr">
-        <is>
-          <t>02-09-2026 06:35</t>
-        </is>
+      <c r="E68" s="8" t="n">
+        <v>46267.27430555555</v>
       </c>
       <c r="F68" s="5" t="inlineStr">
         <is>
@@ -2644,10 +2547,8 @@
           <t>Creepy finger makeup that will shock anyone ☝️❓ [0weub5ASnNA].mp4</t>
         </is>
       </c>
-      <c r="E69" s="4" t="inlineStr">
-        <is>
-          <t>02-09-2026 17:35</t>
-        </is>
+      <c r="E69" s="8" t="n">
+        <v>46267.73263888889</v>
       </c>
       <c r="F69" s="5" t="inlineStr">
         <is>
@@ -2674,10 +2575,8 @@
           <t>Cutting Metal Cubes Reveals Something Unexpected 🎲❓ [hykv4PtDnZw].mp4</t>
         </is>
       </c>
-      <c r="E70" s="4" t="inlineStr">
-        <is>
-          <t>02-09-2026 21:35</t>
-        </is>
+      <c r="E70" s="8" t="n">
+        <v>46267.89930555555</v>
       </c>
       <c r="F70" s="5" t="inlineStr">
         <is>
@@ -2704,10 +2603,8 @@
           <t>Cutting into the most dramatic dessert ever 🔴❓ [yT_K64DTapw].mp4</t>
         </is>
       </c>
-      <c r="E71" s="4" t="inlineStr">
-        <is>
-          <t>03-09-2026 00:35</t>
-        </is>
+      <c r="E71" s="8" t="n">
+        <v>46268.02430555555</v>
       </c>
       <c r="F71" s="5" t="inlineStr">
         <is>
@@ -2734,10 +2631,8 @@
           <t>DIY Fans for the Queen 🪭❓ [IbwrebDAWds].mp4</t>
         </is>
       </c>
-      <c r="E72" s="4" t="inlineStr">
-        <is>
-          <t>03-09-2026 04:35</t>
-        </is>
+      <c r="E72" s="8" t="n">
+        <v>46268.19097222222</v>
       </c>
       <c r="F72" s="5" t="inlineStr">
         <is>
@@ -2764,10 +2659,8 @@
           <t>DIY italian BrainRot Animals with AI 👍❓ [oOlkCZudXWY].mp4</t>
         </is>
       </c>
-      <c r="E73" s="4" t="inlineStr">
-        <is>
-          <t>03-09-2026 06:35</t>
-        </is>
+      <c r="E73" s="8" t="n">
+        <v>46268.27430555555</v>
       </c>
       <c r="F73" s="5" t="inlineStr">
         <is>
@@ -2794,10 +2687,8 @@
           <t>Damn, I got a Rotten Egg 🥚 [W5AEUiC4CS4].mp4</t>
         </is>
       </c>
-      <c r="E74" s="4" t="inlineStr">
-        <is>
-          <t>03-09-2026 17:35</t>
-        </is>
+      <c r="E74" s="8" t="n">
+        <v>46268.73263888889</v>
       </c>
       <c r="F74" s="5" t="inlineStr">
         <is>
@@ -2824,10 +2715,8 @@
           <t>Dear House INSECTS look like this 🪲❓ [984f6hm-_0I].mp4</t>
         </is>
       </c>
-      <c r="E75" s="4" t="inlineStr">
-        <is>
-          <t>03-09-2026 21:35</t>
-        </is>
+      <c r="E75" s="8" t="n">
+        <v>46268.89930555555</v>
       </c>
       <c r="F75" s="5" t="inlineStr">
         <is>
@@ -2854,10 +2743,8 @@
           <t>Dedicated to all lovers of scrambled eggs 🥚❓ [ruYcRSsHr6E].mp4</t>
         </is>
       </c>
-      <c r="E76" s="4" t="inlineStr">
-        <is>
-          <t>04-09-2026 00:35</t>
-        </is>
+      <c r="E76" s="8" t="n">
+        <v>46269.02430555555</v>
       </c>
       <c r="F76" s="5" t="inlineStr">
         <is>
@@ -2884,10 +2771,8 @@
           <t>Did You Do This When You Were a Child？ 👶 [mjQXwPuHTqo].mp4</t>
         </is>
       </c>
-      <c r="E77" s="4" t="inlineStr">
-        <is>
-          <t>04-09-2026 04:35</t>
-        </is>
+      <c r="E77" s="8" t="n">
+        <v>46269.19097222222</v>
       </c>
       <c r="F77" s="5" t="inlineStr">
         <is>
@@ -2914,10 +2799,8 @@
           <t>Did the same thing with the help of AI in a couple of seconds 👍❓ [m5K6i_RiXmk].mp4</t>
         </is>
       </c>
-      <c r="E78" s="4" t="inlineStr">
-        <is>
-          <t>04-09-2026 06:35</t>
-        </is>
+      <c r="E78" s="8" t="n">
+        <v>46269.27430555555</v>
       </c>
       <c r="F78" s="5" t="inlineStr">
         <is>
@@ -2944,10 +2827,8 @@
           <t>Didn't Expect That Ending 😂 #shorts #funny #fail [OwEKeLZUL2U].mp4</t>
         </is>
       </c>
-      <c r="E79" s="4" t="inlineStr">
-        <is>
-          <t>04-09-2026 17:35</t>
-        </is>
+      <c r="E79" s="8" t="n">
+        <v>46269.73263888889</v>
       </c>
       <c r="F79" s="5" t="inlineStr">
         <is>
@@ -2974,10 +2855,8 @@
           <t>Disinfection Product Turned Out to Be Unbearable Torture 😖❓ [g7-2w-BhIuQ].mp4</t>
         </is>
       </c>
-      <c r="E80" s="4" t="inlineStr">
-        <is>
-          <t>04-09-2026 21:35</t>
-        </is>
+      <c r="E80" s="8" t="n">
+        <v>46269.89930555555</v>
       </c>
       <c r="F80" s="5" t="inlineStr">
         <is>
@@ -3004,10 +2883,8 @@
           <t>Do You Really Like It When Monkeys Act Funny？ 🐵👍 [08U1vbAJeok].mp4</t>
         </is>
       </c>
-      <c r="E81" s="4" t="inlineStr">
-        <is>
-          <t>05-09-2026 00:35</t>
-        </is>
+      <c r="E81" s="8" t="n">
+        <v>46270.02430555555</v>
       </c>
       <c r="F81" s="5" t="inlineStr">
         <is>
@@ -3034,10 +2911,8 @@
           <t>Do you see it too or is it just me？ 👀 [_bVv-HMuftM].mp4</t>
         </is>
       </c>
-      <c r="E82" s="4" t="inlineStr">
-        <is>
-          <t>05-09-2026 04:35</t>
-        </is>
+      <c r="E82" s="8" t="n">
+        <v>46270.19097222222</v>
       </c>
       <c r="F82" s="5" t="inlineStr">
         <is>
@@ -3064,10 +2939,8 @@
           <t>Eating Children's Toys Causes Indigestion 💨❓ [EAao4sQ69uY].mp4</t>
         </is>
       </c>
-      <c r="E83" s="4" t="inlineStr">
-        <is>
-          <t>05-09-2026 06:35</t>
-        </is>
+      <c r="E83" s="8" t="n">
+        <v>46270.27430555555</v>
       </c>
       <c r="F83" s="5" t="inlineStr">
         <is>
@@ -3094,10 +2967,8 @@
           <t>FAKE OREO FANNY PRANK 👍❓ [_IIA5TKlV7Q].mp4</t>
         </is>
       </c>
-      <c r="E84" s="4" t="inlineStr">
-        <is>
-          <t>05-09-2026 17:35</t>
-        </is>
+      <c r="E84" s="8" t="n">
+        <v>46270.73263888889</v>
       </c>
       <c r="F84" s="5" t="inlineStr">
         <is>
@@ -3124,10 +2995,8 @@
           <t>FAKE OREO PRANK! 😂👍 [JUs1vs_6YSo].mp4</t>
         </is>
       </c>
-      <c r="E85" s="4" t="inlineStr">
-        <is>
-          <t>05-09-2026 21:35</t>
-        </is>
+      <c r="E85" s="8" t="n">
+        <v>46270.89930555555</v>
       </c>
       <c r="F85" s="5" t="inlineStr">
         <is>
@@ -3154,10 +3023,8 @@
           <t>Fake haircut machine prank goes wrong 🤣✂️ [Ybdx4wU6J_Y].mp4</t>
         </is>
       </c>
-      <c r="E86" s="4" t="inlineStr">
-        <is>
-          <t>06-09-2026 00:35</t>
-        </is>
+      <c r="E86" s="8" t="n">
+        <v>46271.02430555555</v>
       </c>
       <c r="F86" s="5" t="inlineStr">
         <is>
@@ -3184,10 +3051,8 @@
           <t>Football Causes Obesity According to AI (I Tried to Make a Viral Video Too)⚽❓ [M5UjM5Wq5LM].mp4</t>
         </is>
       </c>
-      <c r="E87" s="4" t="inlineStr">
-        <is>
-          <t>06-09-2026 04:35</t>
-        </is>
+      <c r="E87" s="8" t="n">
+        <v>46271.19097222222</v>
       </c>
       <c r="F87" s="5" t="inlineStr">
         <is>
@@ -3214,10 +3079,8 @@
           <t>Found an OTHERWORLDLY Being in My Home 👽🛸 [ZZ1YSvvQ_-E].mp4</t>
         </is>
       </c>
-      <c r="E88" s="4" t="inlineStr">
-        <is>
-          <t>06-09-2026 06:35</t>
-        </is>
+      <c r="E88" s="8" t="n">
+        <v>46271.27430555555</v>
       </c>
       <c r="F88" s="5" t="inlineStr">
         <is>
@@ -3244,10 +3107,8 @@
           <t>AI Made a Similar Video with a Cat ✌️😸？ [JuSrfZRSj0Q].mp4</t>
         </is>
       </c>
-      <c r="E89" s="4" t="inlineStr">
-        <is>
-          <t>06-09-2026 17:35</t>
-        </is>
+      <c r="E89" s="8" t="n">
+        <v>46271.73263888889</v>
       </c>
       <c r="F89" s="5" t="inlineStr">
         <is>
@@ -3274,10 +3135,8 @@
           <t>Frieza's Head From anime Dragon Ball Was Destroyed In Real Life! [eNXZxKYbcBY].mp4</t>
         </is>
       </c>
-      <c r="E90" s="4" t="inlineStr">
-        <is>
-          <t>06-09-2026 21:35</t>
-        </is>
+      <c r="E90" s="8" t="n">
+        <v>46271.89930555555</v>
       </c>
       <c r="F90" s="5" t="inlineStr">
         <is>
@@ -3304,10 +3163,8 @@
           <t>Funny Baby Head from TikTok Trending 👶👍 [2pghMpwlJxQ].mp4</t>
         </is>
       </c>
-      <c r="E91" s="4" t="inlineStr">
-        <is>
-          <t>07-09-2026 00:35</t>
-        </is>
+      <c r="E91" s="8" t="n">
+        <v>46272.02430555555</v>
       </c>
       <c r="F91" s="5" t="inlineStr">
         <is>
@@ -3334,10 +3191,8 @@
           <t>Gave this ILLUSION to AI 😨 His Reaction 👀❓ [2oIGhc4Cenc].mp4</t>
         </is>
       </c>
-      <c r="E92" s="4" t="inlineStr">
-        <is>
-          <t>07-09-2026 04:35</t>
-        </is>
+      <c r="E92" s="8" t="n">
+        <v>46272.19097222222</v>
       </c>
       <c r="F92" s="5" t="inlineStr">
         <is>
@@ -3392,10 +3247,8 @@
           <t>Giving an old man a brand new smile gone wrong 💀 [rpI-t-oAIpw].mp4</t>
         </is>
       </c>
-      <c r="E94" s="4" t="inlineStr">
-        <is>
-          <t>07-09-2026 17:35</t>
-        </is>
+      <c r="E94" s="8" t="n">
+        <v>46272.73263888889</v>
       </c>
       <c r="F94" s="5" t="inlineStr">
         <is>
@@ -3422,10 +3275,8 @@
           <t>God of Random Humor 👍❓ [rZdq9G4nn8o].mp4</t>
         </is>
       </c>
-      <c r="E95" s="4" t="inlineStr">
-        <is>
-          <t>07-09-2026 21:35</t>
-        </is>
+      <c r="E95" s="8" t="n">
+        <v>46272.89930555555</v>
       </c>
       <c r="F95" s="5" t="inlineStr">
         <is>
@@ -3480,10 +3331,8 @@
           <t>Got a job as a hairdresser for 24 hours 💇❓ [bWTTH72qm3k].mp4</t>
         </is>
       </c>
-      <c r="E97" s="4" t="inlineStr">
-        <is>
-          <t>08-09-2026 04:35</t>
-        </is>
+      <c r="E97" s="8" t="n">
+        <v>46273.19097222222</v>
       </c>
       <c r="F97" s="5" t="inlineStr">
         <is>
@@ -3510,10 +3359,8 @@
           <t>He Thought I Wouldn't Notice His Fake 😡❓ [uasZmeSKI7o].mp4</t>
         </is>
       </c>
-      <c r="E98" s="4" t="inlineStr">
-        <is>
-          <t>08-09-2026 06:35</t>
-        </is>
+      <c r="E98" s="8" t="n">
+        <v>46273.27430555555</v>
       </c>
       <c r="F98" s="5" t="inlineStr">
         <is>
@@ -3540,10 +3387,8 @@
           <t>He asked me to leave him a slice of pizza 😭🍕？ [K3fg0M22B34].mp4</t>
         </is>
       </c>
-      <c r="E99" s="4" t="inlineStr">
-        <is>
-          <t>08-09-2026 17:35</t>
-        </is>
+      <c r="E99" s="8" t="n">
+        <v>46273.73263888889</v>
       </c>
       <c r="F99" s="5" t="inlineStr">
         <is>
@@ -3570,10 +3415,8 @@
           <t>He burned down his house to film this video (Not AI) 👍❓ [z5RW_YgqDHk].mp4</t>
         </is>
       </c>
-      <c r="E100" s="4" t="inlineStr">
-        <is>
-          <t>08-09-2026 21:35</t>
-        </is>
+      <c r="E100" s="8" t="n">
+        <v>46273.89930555555</v>
       </c>
       <c r="F100" s="5" t="inlineStr">
         <is>
@@ -3600,10 +3443,8 @@
           <t>He doesn't understand the thrill of it 💩❓ [FkKOT3tdadU].mp4</t>
         </is>
       </c>
-      <c r="E101" s="4" t="inlineStr">
-        <is>
-          <t>09-09-2026 00:35</t>
-        </is>
+      <c r="E101" s="8" t="n">
+        <v>46274.02430555555</v>
       </c>
       <c r="F101" s="5" t="inlineStr">
         <is>
@@ -3630,10 +3471,8 @@
           <t>Help marine animals whenever possible😢❓ [d7TrMqmeX0k].mp4</t>
         </is>
       </c>
-      <c r="E102" s="4" t="inlineStr">
-        <is>
-          <t>09-09-2026 04:35</t>
-        </is>
+      <c r="E102" s="8" t="n">
+        <v>46274.19097222222</v>
       </c>
       <c r="F102" s="5" t="inlineStr">
         <is>
@@ -3660,10 +3499,8 @@
           <t>Helped him do this with the help of AI 👍❓ [Gga6s7TxjLc].mp4</t>
         </is>
       </c>
-      <c r="E103" s="4" t="inlineStr">
-        <is>
-          <t>09-09-2026 06:35</t>
-        </is>
+      <c r="E103" s="8" t="n">
+        <v>46274.27430555555</v>
       </c>
       <c r="F103" s="5" t="inlineStr">
         <is>
@@ -3690,10 +3527,8 @@
           <t>Here's How AI Thinks Humans Can Move on Water 😂👍？ [0vsT4S-4HPY].mp4</t>
         </is>
       </c>
-      <c r="E104" s="4" t="inlineStr">
-        <is>
-          <t>09-09-2026 17:35</t>
-        </is>
+      <c r="E104" s="8" t="n">
+        <v>46274.73263888889</v>
       </c>
       <c r="F104" s="5" t="inlineStr">
         <is>
@@ -3720,10 +3555,8 @@
           <t>Here's How AI Thinks Monkeys Behave When Someone Is in Danger 🐵👍？ [_-r5tkpskzA].mp4</t>
         </is>
       </c>
-      <c r="E105" s="4" t="inlineStr">
-        <is>
-          <t>09-09-2026 21:35</t>
-        </is>
+      <c r="E105" s="8" t="n">
+        <v>46274.89930555555</v>
       </c>
       <c r="F105" s="5" t="inlineStr">
         <is>
@@ -3750,10 +3583,8 @@
           <t>Here's Why Cake Decorating Tools Are Dangerous 😭❓ [CtgGhlFx_g0].mp4</t>
         </is>
       </c>
-      <c r="E106" s="4" t="inlineStr">
-        <is>
-          <t>10-09-2026 00:35</t>
-        </is>
+      <c r="E106" s="8" t="n">
+        <v>46275.02430555555</v>
       </c>
       <c r="F106" s="5" t="inlineStr">
         <is>
@@ -3780,10 +3611,8 @@
           <t>Here's Why I Don't Binge on Nutella 😂👍 [vWdZccNJ70A].mp4</t>
         </is>
       </c>
-      <c r="E107" s="4" t="inlineStr">
-        <is>
-          <t>10-09-2026 04:35</t>
-        </is>
+      <c r="E107" s="8" t="n">
+        <v>46275.19097222222</v>
       </c>
       <c r="F107" s="5" t="inlineStr">
         <is>
@@ -3810,10 +3639,8 @@
           <t>Here's Why You Shouldn't Make Popcorn This Way 😮❓ [WH7fL1iqtno].mp4</t>
         </is>
       </c>
-      <c r="E108" s="4" t="inlineStr">
-        <is>
-          <t>10-09-2026 06:35</t>
-        </is>
+      <c r="E108" s="8" t="n">
+        <v>46275.27430555555</v>
       </c>
       <c r="F108" s="5" t="inlineStr">
         <is>
@@ -3840,10 +3667,8 @@
           <t>How AI Imagines Living in the Same House with a Dog 🐶❓ [J8PfaNJVrjg].mp4</t>
         </is>
       </c>
-      <c r="E109" s="4" t="inlineStr">
-        <is>
-          <t>10-09-2026 17:35</t>
-        </is>
+      <c r="E109" s="8" t="n">
+        <v>46275.73263888889</v>
       </c>
       <c r="F109" s="5" t="inlineStr">
         <is>
@@ -3870,10 +3695,8 @@
           <t>How Boys Slide vs. Men 💀❓ [q78wUcZSgOA].mp4</t>
         </is>
       </c>
-      <c r="E110" s="4" t="inlineStr">
-        <is>
-          <t>10-09-2026 21:35</t>
-        </is>
+      <c r="E110" s="8" t="n">
+        <v>46275.89930555555</v>
       </c>
       <c r="F110" s="5" t="inlineStr">
         <is>
@@ -3900,10 +3723,8 @@
           <t>How Did This Cat Learn to Play Tic Tac Toe？ ❌ [BzZicKW9stE].mp4</t>
         </is>
       </c>
-      <c r="E111" s="4" t="inlineStr">
-        <is>
-          <t>11-09-2026 00:35</t>
-        </is>
+      <c r="E111" s="8" t="n">
+        <v>46276.02430555555</v>
       </c>
       <c r="F111" s="5" t="inlineStr">
         <is>
@@ -3930,10 +3751,8 @@
           <t>How I Feel During a Cold 💀❓ [Jyq2CWtIJk0].mp4</t>
         </is>
       </c>
-      <c r="E112" s="4" t="inlineStr">
-        <is>
-          <t>11-09-2026 04:35</t>
-        </is>
+      <c r="E112" s="8" t="n">
+        <v>46276.19097222222</v>
       </c>
       <c r="F112" s="5" t="inlineStr">
         <is>
@@ -3960,10 +3779,8 @@
           <t>Choosing a Vehicle for Underground Parking 🏍️💨 [lb7fYh03GZ8].mp4</t>
         </is>
       </c>
-      <c r="E113" s="4" t="inlineStr">
-        <is>
-          <t>11-09-2026 06:35</t>
-        </is>
+      <c r="E113" s="8" t="n">
+        <v>46276.27430555555</v>
       </c>
       <c r="F113" s="5" t="inlineStr">
         <is>
@@ -3990,10 +3807,8 @@
           <t>How I Get Food for My Dinners 🦆❓ [4VRuj8FVXTY].mp4</t>
         </is>
       </c>
-      <c r="E114" s="4" t="inlineStr">
-        <is>
-          <t>11-09-2026 17:35</t>
-        </is>
+      <c r="E114" s="8" t="n">
+        <v>46276.73263888889</v>
       </c>
       <c r="F114" s="5" t="inlineStr">
         <is>
@@ -4020,10 +3835,8 @@
           <t>How Much Can You Love Nutella？! Here's the Answer： [lGpeP54z_IQ].mp4</t>
         </is>
       </c>
-      <c r="E115" s="4" t="inlineStr">
-        <is>
-          <t>11-09-2026 21:35</t>
-        </is>
+      <c r="E115" s="8" t="n">
+        <v>46276.89930555555</v>
       </c>
       <c r="F115" s="5" t="inlineStr">
         <is>
@@ -4050,10 +3863,8 @@
           <t>How ai does HAIR 👍❓ [WJNoMT7_jlo].mp4</t>
         </is>
       </c>
-      <c r="E116" s="4" t="inlineStr">
-        <is>
-          <t>12-09-2026 00:35</t>
-        </is>
+      <c r="E116" s="8" t="n">
+        <v>46277.02430555555</v>
       </c>
       <c r="F116" s="5" t="inlineStr">
         <is>
@@ -4080,10 +3891,8 @@
           <t>How did these Pringles end up there？ 🤯 [MhOXekXGMaU].mp4</t>
         </is>
       </c>
-      <c r="E117" s="4" t="inlineStr">
-        <is>
-          <t>12-09-2026 04:35</t>
-        </is>
+      <c r="E117" s="8" t="n">
+        <v>46277.19097222222</v>
       </c>
       <c r="F117" s="5" t="inlineStr">
         <is>
@@ -4110,10 +3919,8 @@
           <t>How much kombucha did you have to drink to get this result？ 😂 [HbPRwY2WV9k].mp4</t>
         </is>
       </c>
-      <c r="E118" s="4" t="inlineStr">
-        <is>
-          <t>12-09-2026 06:35</t>
-        </is>
+      <c r="E118" s="8" t="n">
+        <v>46277.27430555555</v>
       </c>
       <c r="F118" s="5" t="inlineStr">
         <is>
@@ -4140,10 +3947,8 @@
           <t>How to Quickly Make Popcorn at Home 🍿❓ [perGa4Wa11E].mp4</t>
         </is>
       </c>
-      <c r="E119" s="4" t="inlineStr">
-        <is>
-          <t>12-09-2026 17:35</t>
-        </is>
+      <c r="E119" s="8" t="n">
+        <v>46277.73263888889</v>
       </c>
       <c r="F119" s="5" t="inlineStr">
         <is>
@@ -4170,10 +3975,8 @@
           <t>How to Walk on Water According to AI 😂👍？ [s4Tz8fcwu00].mp4</t>
         </is>
       </c>
-      <c r="E120" s="4" t="inlineStr">
-        <is>
-          <t>12-09-2026 21:35</t>
-        </is>
+      <c r="E120" s="8" t="n">
+        <v>46277.89930555555</v>
       </c>
       <c r="F120" s="5" t="inlineStr">
         <is>
@@ -4200,10 +4003,8 @@
           <t>How to get a lot of points in this challenge？ ✌️ [k0b36-JrqwQ].mp4</t>
         </is>
       </c>
-      <c r="E121" s="4" t="inlineStr">
-        <is>
-          <t>13-09-2026 00:35</t>
-        </is>
+      <c r="E121" s="8" t="n">
+        <v>46278.02430555555</v>
       </c>
       <c r="F121" s="5" t="inlineStr">
         <is>
@@ -4230,10 +4031,8 @@
           <t>How to get through this Labyrinth？ 🤯 [RN59XC9Sgs4].mp4</t>
         </is>
       </c>
-      <c r="E122" s="4" t="inlineStr">
-        <is>
-          <t>13-09-2026 04:35</t>
-        </is>
+      <c r="E122" s="8" t="n">
+        <v>46278.19097222222</v>
       </c>
       <c r="F122" s="5" t="inlineStr">
         <is>
@@ -4260,10 +4059,8 @@
           <t>How would AI behave in a similar simulation？😂👍 [R1YExEyB3Cc].mp4</t>
         </is>
       </c>
-      <c r="E123" s="4" t="inlineStr">
-        <is>
-          <t>13-09-2026 06:35</t>
-        </is>
+      <c r="E123" s="8" t="n">
+        <v>46278.27430555555</v>
       </c>
       <c r="F123" s="5" t="inlineStr">
         <is>
@@ -4290,10 +4087,8 @@
           <t>I Couldn't Resist This Trend 🤢🤮？ [BG30RdoAAxQ].mp4</t>
         </is>
       </c>
-      <c r="E124" s="4" t="inlineStr">
-        <is>
-          <t>13-09-2026 17:35</t>
-        </is>
+      <c r="E124" s="8" t="n">
+        <v>46278.73263888889</v>
       </c>
       <c r="F124" s="5" t="inlineStr">
         <is>
@@ -4320,10 +4115,8 @@
           <t>I Didn't Expect The Toilet Paper To Go THIS Far 🧻❓ [wLDZ7-u2fEA].mp4</t>
         </is>
       </c>
-      <c r="E125" s="4" t="inlineStr">
-        <is>
-          <t>13-09-2026 21:35</t>
-        </is>
+      <c r="E125" s="8" t="n">
+        <v>46278.89930555555</v>
       </c>
       <c r="F125" s="5" t="inlineStr">
         <is>
@@ -4350,10 +4143,8 @@
           <t>I Didn't Expect This Toy to HURT This Bad 😱❓ [XtZ60PkBqsM].mp4</t>
         </is>
       </c>
-      <c r="E126" s="4" t="inlineStr">
-        <is>
-          <t>14-09-2026 00:35</t>
-        </is>
+      <c r="E126" s="8" t="n">
+        <v>46279.02430555555</v>
       </c>
       <c r="F126" s="5" t="inlineStr">
         <is>
@@ -4380,10 +4171,8 @@
           <t>I Enlarged My HEAD With This Trick 👍❓ [iYFMCo0W6c0].mp4</t>
         </is>
       </c>
-      <c r="E127" s="4" t="inlineStr">
-        <is>
-          <t>14-09-2026 04:35</t>
-        </is>
+      <c r="E127" s="8" t="n">
+        <v>46279.19097222222</v>
       </c>
       <c r="F127" s="5" t="inlineStr">
         <is>
@@ -4410,10 +4199,8 @@
           <t>I Fed My Jaw Something More Appetizing 💩❓ [QchAbKb4JWw].mp4</t>
         </is>
       </c>
-      <c r="E128" s="4" t="inlineStr">
-        <is>
-          <t>14-09-2026 06:35</t>
-        </is>
+      <c r="E128" s="8" t="n">
+        <v>46279.27430555555</v>
       </c>
       <c r="F128" s="5" t="inlineStr">
         <is>
@@ -4440,10 +4227,8 @@
           <t>I Got Kidnapped by Shrek, and This Is What Happened Next [Vv-jAnzpDr8].mp4</t>
         </is>
       </c>
-      <c r="E129" s="4" t="inlineStr">
-        <is>
-          <t>14-09-2026 17:35</t>
-        </is>
+      <c r="E129" s="8" t="n">
+        <v>46279.73263888889</v>
       </c>
       <c r="F129" s="5" t="inlineStr">
         <is>
@@ -4470,10 +4255,8 @@
           <t>I Put My Own Spin On This Viral Trend 👍❓ [cExNcqc5ZiQ].mp4</t>
         </is>
       </c>
-      <c r="E130" s="4" t="inlineStr">
-        <is>
-          <t>14-09-2026 21:35</t>
-        </is>
+      <c r="E130" s="8" t="n">
+        <v>46279.89930555555</v>
       </c>
       <c r="F130" s="5" t="inlineStr">
         <is>
@@ -4500,10 +4283,8 @@
           <t>I Recreated the Magical Shoe Video Using AI 🦶❓ [y6glV6VJuxI].mp4</t>
         </is>
       </c>
-      <c r="E131" s="4" t="inlineStr">
-        <is>
-          <t>15-09-2026 00:35</t>
-        </is>
+      <c r="E131" s="8" t="n">
+        <v>46280.02430555555</v>
       </c>
       <c r="F131" s="5" t="inlineStr">
         <is>
@@ -4530,10 +4311,8 @@
           <t>I Spent 24 Hours as a TRAIN PASSENGER and Here's What Happened! [gPeE523gBBM].mp4</t>
         </is>
       </c>
-      <c r="E132" s="4" t="inlineStr">
-        <is>
-          <t>15-09-2026 04:35</t>
-        </is>
+      <c r="E132" s="8" t="n">
+        <v>46280.19097222222</v>
       </c>
       <c r="F132" s="5" t="inlineStr">
         <is>
@@ -4560,10 +4339,8 @@
           <t>I Tested This Life Hack With A Bike That Rides On Water 🚲️❓ [jS5rYj9i3fc].mp4</t>
         </is>
       </c>
-      <c r="E133" s="4" t="inlineStr">
-        <is>
-          <t>15-09-2026 06:35</t>
-        </is>
+      <c r="E133" s="8" t="n">
+        <v>46280.27430555555</v>
       </c>
       <c r="F133" s="5" t="inlineStr">
         <is>
@@ -4590,10 +4367,8 @@
           <t>I Tried To Do The Same Thing And Got A Different Result 💦ˎˊ˗ [O4fJhIpIBgw].mp4</t>
         </is>
       </c>
-      <c r="E134" s="4" t="inlineStr">
-        <is>
-          <t>15-09-2026 17:35</t>
-        </is>
+      <c r="E134" s="8" t="n">
+        <v>46280.73263888889</v>
       </c>
       <c r="F134" s="5" t="inlineStr">
         <is>
@@ -4620,10 +4395,8 @@
           <t>I Was Kidnapped by Shrek [VCegei0rqIk].mp4</t>
         </is>
       </c>
-      <c r="E135" s="4" t="inlineStr">
-        <is>
-          <t>15-09-2026 21:35</t>
-        </is>
+      <c r="E135" s="8" t="n">
+        <v>46280.89930555555</v>
       </c>
       <c r="F135" s="5" t="inlineStr">
         <is>
@@ -4650,10 +4423,8 @@
           <t>I also tried this Inflatable Slide and I Declare： It is the Best! [g_wpgmCxy60].mp4</t>
         </is>
       </c>
-      <c r="E136" s="4" t="inlineStr">
-        <is>
-          <t>16-09-2026 00:35</t>
-        </is>
+      <c r="E136" s="8" t="n">
+        <v>46281.02430555555</v>
       </c>
       <c r="F136" s="5" t="inlineStr">
         <is>
@@ -4680,10 +4451,8 @@
           <t>I am disappointed with this antiperspirant 🤬❓ [v1E7qoY3KiE].mp4</t>
         </is>
       </c>
-      <c r="E137" s="4" t="inlineStr">
-        <is>
-          <t>16-09-2026 04:35</t>
-        </is>
+      <c r="E137" s="8" t="n">
+        <v>46281.19097222222</v>
       </c>
       <c r="F137" s="5" t="inlineStr">
         <is>
@@ -4710,10 +4479,8 @@
           <t>I ate all these docile dominoes 😮❓ [tZn7bVrQx4I].mp4</t>
         </is>
       </c>
-      <c r="E138" s="4" t="inlineStr">
-        <is>
-          <t>16-09-2026 06:35</t>
-        </is>
+      <c r="E138" s="8" t="n">
+        <v>46281.27430555555</v>
       </c>
       <c r="F138" s="5" t="inlineStr">
         <is>
@@ -4740,10 +4507,8 @@
           <t>I became a moron playing this brain development game 💩 [SyRQR3BDfmw].mp4</t>
         </is>
       </c>
-      <c r="E139" s="4" t="inlineStr">
-        <is>
-          <t>16-09-2026 17:35</t>
-        </is>
+      <c r="E139" s="8" t="n">
+        <v>46281.73263888889</v>
       </c>
       <c r="F139" s="5" t="inlineStr">
         <is>
@@ -4770,10 +4535,8 @@
           <t>I broke the Squid Game doll's rules 👍❓ [yoLFv4TanjA].mp4</t>
         </is>
       </c>
-      <c r="E140" s="4" t="inlineStr">
-        <is>
-          <t>16-09-2026 21:35</t>
-        </is>
+      <c r="E140" s="8" t="n">
+        <v>46281.89930555555</v>
       </c>
       <c r="F140" s="5" t="inlineStr">
         <is>
@@ -4800,10 +4563,8 @@
           <t>I can't believe this rope trick actually worked 🤯 ❓ [d1SjcR3-Q0Q].mp4</t>
         </is>
       </c>
-      <c r="E141" s="4" t="inlineStr">
-        <is>
-          <t>17-09-2026 00:35</t>
-        </is>
+      <c r="E141" s="8" t="n">
+        <v>46282.02430555555</v>
       </c>
       <c r="F141" s="5" t="inlineStr">
         <is>
@@ -4830,10 +4591,8 @@
           <t>I completed the TikTok Chicken Challenge 🐔❓ [xzuTeu-UonQ].mp4</t>
         </is>
       </c>
-      <c r="E142" s="4" t="inlineStr">
-        <is>
-          <t>17-09-2026 04:35</t>
-        </is>
+      <c r="E142" s="8" t="n">
+        <v>46282.19097222222</v>
       </c>
       <c r="F142" s="5" t="inlineStr">
         <is>
@@ -4860,10 +4619,8 @@
           <t>I completed the TikTok Poop Challenge 💩🚽 [85U69nA1avU].mp4</t>
         </is>
       </c>
-      <c r="E143" s="4" t="inlineStr">
-        <is>
-          <t>17-09-2026 06:35</t>
-        </is>
+      <c r="E143" s="8" t="n">
+        <v>46282.27430555555</v>
       </c>
       <c r="F143" s="5" t="inlineStr">
         <is>
@@ -4890,10 +4647,8 @@
           <t>I covered my Ferrari with stickers but a plane crashed on it ✈️❓ [H-dMiPNTaNE].mp4</t>
         </is>
       </c>
-      <c r="E144" s="4" t="inlineStr">
-        <is>
-          <t>17-09-2026 17:35</t>
-        </is>
+      <c r="E144" s="8" t="n">
+        <v>46282.73263888889</v>
       </c>
       <c r="F144" s="5" t="inlineStr">
         <is>
@@ -4920,10 +4675,8 @@
           <t>I did the same thing in Roblox using AI 👍❓ [6r6OURzoeMw].mp4</t>
         </is>
       </c>
-      <c r="E145" s="4" t="inlineStr">
-        <is>
-          <t>17-09-2026 21:35</t>
-        </is>
+      <c r="E145" s="8" t="n">
+        <v>46282.89930555555</v>
       </c>
       <c r="F145" s="5" t="inlineStr">
         <is>
@@ -4950,10 +4703,8 @@
           <t>I didn't know my hands could do that ❤️❓ [Z17M0LmxxBo].mp4</t>
         </is>
       </c>
-      <c r="E146" s="4" t="inlineStr">
-        <is>
-          <t>18-09-2026 00:35</t>
-        </is>
+      <c r="E146" s="8" t="n">
+        <v>46283.02430555555</v>
       </c>
       <c r="F146" s="5" t="inlineStr">
         <is>
@@ -4980,10 +4731,8 @@
           <t>I do good 🌱 [XERIJYjSv8g].mp4</t>
         </is>
       </c>
-      <c r="E147" s="4" t="inlineStr">
-        <is>
-          <t>18-09-2026 04:35</t>
-        </is>
+      <c r="E147" s="8" t="n">
+        <v>46283.19097222222</v>
       </c>
       <c r="F147" s="5" t="inlineStr">
         <is>
@@ -5010,10 +4759,8 @@
           <t>I don't know how, but it managed to ferment and it got me drunk 🍇❓ [l_NOTRtvnbU].mp4</t>
         </is>
       </c>
-      <c r="E148" s="4" t="inlineStr">
-        <is>
-          <t>18-09-2026 06:35</t>
-        </is>
+      <c r="E148" s="8" t="n">
+        <v>46283.27430555555</v>
       </c>
       <c r="F148" s="5" t="inlineStr">
         <is>
@@ -5040,10 +4787,8 @@
           <t>I don't know why he felt bad 🚽❓ [88zBco75ZOg].mp4</t>
         </is>
       </c>
-      <c r="E149" s="4" t="inlineStr">
-        <is>
-          <t>18-09-2026 17:35</t>
-        </is>
+      <c r="E149" s="8" t="n">
+        <v>46283.73263888889</v>
       </c>
       <c r="F149" s="5" t="inlineStr">
         <is>
@@ -5070,10 +4815,8 @@
           <t>I drew a similar situation in animation 👍❓ [rIMsZ8BHQhw].mp4</t>
         </is>
       </c>
-      <c r="E150" s="4" t="inlineStr">
-        <is>
-          <t>18-09-2026 21:35</t>
-        </is>
+      <c r="E150" s="8" t="n">
+        <v>46283.89930555555</v>
       </c>
       <c r="F150" s="5" t="inlineStr">
         <is>
@@ -5100,10 +4843,8 @@
           <t>I fed the Mulberry and then I ate it 🍇❓ [msVlGcHOB30].mp4</t>
         </is>
       </c>
-      <c r="E151" s="4" t="inlineStr">
-        <is>
-          <t>19-09-2026 00:35</t>
-        </is>
+      <c r="E151" s="8" t="n">
+        <v>46284.02430555555</v>
       </c>
       <c r="F151" s="5" t="inlineStr">
         <is>
@@ -5130,10 +4871,8 @@
           <t>I found a secret in this TikTok challenge but I can't use it 😮👍 [ytG-4-3CfOc].mp4</t>
         </is>
       </c>
-      <c r="E152" s="4" t="inlineStr">
-        <is>
-          <t>19-09-2026 04:35</t>
-        </is>
+      <c r="E152" s="8" t="n">
+        <v>46284.19097222222</v>
       </c>
       <c r="F152" s="5" t="inlineStr">
         <is>
@@ -5160,10 +4899,8 @@
           <t>I got into the Universe of Legs this way 🦶❓ [sXtnBA06x4c].mp4</t>
         </is>
       </c>
-      <c r="E153" s="4" t="inlineStr">
-        <is>
-          <t>19-09-2026 06:35</t>
-        </is>
+      <c r="E153" s="8" t="n">
+        <v>46284.27430555555</v>
       </c>
       <c r="F153" s="5" t="inlineStr">
         <is>
@@ -5190,10 +4927,8 @@
           <t>I had the same situation again in Roblox 👍❓ [DhitPvL_WyQ].mp4</t>
         </is>
       </c>
-      <c r="E154" s="4" t="inlineStr">
-        <is>
-          <t>19-09-2026 17:35</t>
-        </is>
+      <c r="E154" s="8" t="n">
+        <v>46284.73263888889</v>
       </c>
       <c r="F154" s="5" t="inlineStr">
         <is>
@@ -5220,10 +4955,8 @@
           <t>I just wanted to REPEAT the bullying, but Angelina Jolie ruined it all 🐷❓ [yHbbuWnv-SI].mp4</t>
         </is>
       </c>
-      <c r="E155" s="4" t="inlineStr">
-        <is>
-          <t>19-09-2026 21:35</t>
-        </is>
+      <c r="E155" s="8" t="n">
+        <v>46284.89930555555</v>
       </c>
       <c r="F155" s="5" t="inlineStr">
         <is>
@@ -5250,10 +4983,8 @@
           <t>I made a similar animation but with Batman 🦇❓ [lbELU0EYYaQ].mp4</t>
         </is>
       </c>
-      <c r="E156" s="4" t="inlineStr">
-        <is>
-          <t>20-09-2026 00:35</t>
-        </is>
+      <c r="E156" s="8" t="n">
+        <v>46285.02430555555</v>
       </c>
       <c r="F156" s="5" t="inlineStr">
         <is>
@@ -5280,10 +5011,8 @@
           <t>The Crazy Trend You Need to Copy 👍❓ [QwGPyEwFyGE].mp4</t>
         </is>
       </c>
-      <c r="E157" s="4" t="inlineStr">
-        <is>
-          <t>20-09-2026 04:35</t>
-        </is>
+      <c r="E157" s="8" t="n">
+        <v>46285.19097222222</v>
       </c>
       <c r="F157" s="5" t="inlineStr">
         <is>
@@ -5310,10 +5039,8 @@
           <t>I recreated a funny cat video using Ai 😹👍？ [vuce759TYmQ].mp4</t>
         </is>
       </c>
-      <c r="E158" s="4" t="inlineStr">
-        <is>
-          <t>20-09-2026 06:35</t>
-        </is>
+      <c r="E158" s="8" t="n">
+        <v>46285.27430555555</v>
       </c>
       <c r="F158" s="5" t="inlineStr">
         <is>
@@ -5340,10 +5067,8 @@
           <t>I recreated a funny pets crazy Video using Ai 😮👍？ [oCzJ_XVy5NA].mp4</t>
         </is>
       </c>
-      <c r="E159" s="4" t="inlineStr">
-        <is>
-          <t>20-09-2026 17:35</t>
-        </is>
+      <c r="E159" s="8" t="n">
+        <v>46285.73263888889</v>
       </c>
       <c r="F159" s="5" t="inlineStr">
         <is>
@@ -5370,10 +5095,8 @@
           <t>I recreated the funniest animation in the world 👍❓ [q5LZ9hTGUJw].mp4</t>
         </is>
       </c>
-      <c r="E160" s="4" t="inlineStr">
-        <is>
-          <t>20-09-2026 21:35</t>
-        </is>
+      <c r="E160" s="8" t="n">
+        <v>46285.89930555555</v>
       </c>
       <c r="F160" s="5" t="inlineStr">
         <is>
@@ -5400,10 +5123,8 @@
           <t>I repeated another video about how AI sees monkey behavior when someone is in danger 🐵👍？ [s9kFUEtas84].mp4</t>
         </is>
       </c>
-      <c r="E161" s="4" t="inlineStr">
-        <is>
-          <t>21-09-2026 00:35</t>
-        </is>
+      <c r="E161" s="8" t="n">
+        <v>46286.02430555555</v>
       </c>
       <c r="F161" s="5" t="inlineStr">
         <is>
@@ -5430,10 +5151,8 @@
           <t>I thought I could handle this bike better 🚲️ [gjE7OIoGemo].mp4</t>
         </is>
       </c>
-      <c r="E162" s="4" t="inlineStr">
-        <is>
-          <t>21-09-2026 04:35</t>
-        </is>
+      <c r="E162" s="8" t="n">
+        <v>46286.19097222222</v>
       </c>
       <c r="F162" s="5" t="inlineStr">
         <is>
@@ -5460,10 +5179,8 @@
           <t>I thought I'd take off the same thing, but I was hungry 😂 [AeiehUmB1yk].mp4</t>
         </is>
       </c>
-      <c r="E163" s="4" t="inlineStr">
-        <is>
-          <t>21-09-2026 06:35</t>
-        </is>
+      <c r="E163" s="8" t="n">
+        <v>46286.27430555555</v>
       </c>
       <c r="F163" s="5" t="inlineStr">
         <is>
@@ -5490,10 +5207,8 @@
           <t>I thought he was stupid 🧠 I don't think so anymore 👀 [ucZozEuj0WA].mp4</t>
         </is>
       </c>
-      <c r="E164" s="4" t="inlineStr">
-        <is>
-          <t>21-09-2026 17:35</t>
-        </is>
+      <c r="E164" s="8" t="n">
+        <v>46286.73263888889</v>
       </c>
       <c r="F164" s="5" t="inlineStr">
         <is>
@@ -5520,10 +5235,8 @@
           <t>Funny video with my TV 😂👍 [E8Hi0kgLcPA].mp4</t>
         </is>
       </c>
-      <c r="E165" s="4" t="inlineStr">
-        <is>
-          <t>21-09-2026 21:35</t>
-        </is>
+      <c r="E165" s="8" t="n">
+        <v>46286.89930555555</v>
       </c>
       <c r="F165" s="5" t="inlineStr">
         <is>
@@ -5550,10 +5263,8 @@
           <t>I visualized a similar situation in Animation with myself in the leading roles 👍❓ [r7_R-8nyxIU].mp4</t>
         </is>
       </c>
-      <c r="E166" s="4" t="inlineStr">
-        <is>
-          <t>22-09-2026 00:35</t>
-        </is>
+      <c r="E166" s="8" t="n">
+        <v>46287.02430555555</v>
       </c>
       <c r="F166" s="5" t="inlineStr">
         <is>
@@ -5580,10 +5291,8 @@
           <t>I'm READY for the New 2026 Year! 🎄 [4YbgZhGeAqA].mp4</t>
         </is>
       </c>
-      <c r="E167" s="4" t="inlineStr">
-        <is>
-          <t>22-09-2026 04:35</t>
-        </is>
+      <c r="E167" s="8" t="n">
+        <v>46287.19097222222</v>
       </c>
       <c r="F167" s="5" t="inlineStr">
         <is>
@@ -5610,10 +5319,8 @@
           <t>I'm frying ONE popcorn 🍿❓ [RQzRsETayVA].mp4</t>
         </is>
       </c>
-      <c r="E168" s="4" t="inlineStr">
-        <is>
-          <t>22-09-2026 06:35</t>
-        </is>
+      <c r="E168" s="8" t="n">
+        <v>46287.27430555555</v>
       </c>
       <c r="F168" s="5" t="inlineStr">
         <is>
@@ -5640,10 +5347,8 @@
           <t>I'm taste testing Minion candies 😋❓ [WXbsuERkiYY].mp4</t>
         </is>
       </c>
-      <c r="E169" s="4" t="inlineStr">
-        <is>
-          <t>22-09-2026 17:35</t>
-        </is>
+      <c r="E169" s="8" t="n">
+        <v>46287.73263888889</v>
       </c>
       <c r="F169" s="5" t="inlineStr">
         <is>
@@ -5670,10 +5375,8 @@
           <t>If I Was On The Show： THE VOICE 🎤❓ [cJ3Rj61Yxmw].mp4</t>
         </is>
       </c>
-      <c r="E170" s="4" t="inlineStr">
-        <is>
-          <t>22-09-2026 21:35</t>
-        </is>
+      <c r="E170" s="8" t="n">
+        <v>46287.89930555555</v>
       </c>
       <c r="F170" s="5" t="inlineStr">
         <is>
@@ -5700,10 +5403,8 @@
           <t>Insects in Food Taste Disgusting 🐜❓ [GCSiHD9bqdM].mp4</t>
         </is>
       </c>
-      <c r="E171" s="4" t="inlineStr">
-        <is>
-          <t>23-09-2026 00:35</t>
-        </is>
+      <c r="E171" s="8" t="n">
+        <v>46288.02430555555</v>
       </c>
       <c r="F171" s="5" t="inlineStr">
         <is>
@@ -5730,10 +5431,8 @@
           <t>Instant Noodle Life Hack (checking) ❌❓ [i5HmO-9WROY].mp4</t>
         </is>
       </c>
-      <c r="E172" s="4" t="inlineStr">
-        <is>
-          <t>23-09-2026 04:35</t>
-        </is>
+      <c r="E172" s="8" t="n">
+        <v>46288.19097222222</v>
       </c>
       <c r="F172" s="5" t="inlineStr">
         <is>
@@ -5760,10 +5459,8 @@
           <t>Is This the Dumbest Plant in the World？🪴 [35Uy_QnlHR8].mp4</t>
         </is>
       </c>
-      <c r="E173" s="4" t="inlineStr">
-        <is>
-          <t>23-09-2026 06:35</t>
-        </is>
+      <c r="E173" s="8" t="n">
+        <v>46288.27430555555</v>
       </c>
       <c r="F173" s="5" t="inlineStr">
         <is>
@@ -5790,10 +5487,8 @@
           <t>Is This the Most Relatable Weekend Ever？ [ZlFqF7jbJAY].mp4</t>
         </is>
       </c>
-      <c r="E174" s="4" t="inlineStr">
-        <is>
-          <t>23-09-2026 17:35</t>
-        </is>
+      <c r="E174" s="8" t="n">
+        <v>46288.73263888889</v>
       </c>
       <c r="F174" s="5" t="inlineStr">
         <is>
@@ -5820,10 +5515,8 @@
           <t>Is Your Little Angry Dog's Behavior Trying To Tell You Something？ 🐶 [9DngQ00w3Gw].mp4</t>
         </is>
       </c>
-      <c r="E175" s="4" t="inlineStr">
-        <is>
-          <t>23-09-2026 21:35</t>
-        </is>
+      <c r="E175" s="8" t="n">
+        <v>46288.89930555555</v>
       </c>
       <c r="F175" s="5" t="inlineStr">
         <is>
@@ -5850,10 +5543,8 @@
           <t>Is this cat impossible to beat at Tic Tac Toe？ ❌⭕ [ogWdvoCs-R8].mp4</t>
         </is>
       </c>
-      <c r="E176" s="4" t="inlineStr">
-        <is>
-          <t>24-09-2026 00:35</t>
-        </is>
+      <c r="E176" s="8" t="n">
+        <v>46289.02430555555</v>
       </c>
       <c r="F176" s="5" t="inlineStr">
         <is>
@@ -5880,10 +5571,8 @@
           <t>It just happened to be my size 🤣👍？ [ap3QlvJYBvk].mp4</t>
         </is>
       </c>
-      <c r="E177" s="4" t="inlineStr">
-        <is>
-          <t>24-09-2026 04:35</t>
-        </is>
+      <c r="E177" s="8" t="n">
+        <v>46289.19097222222</v>
       </c>
       <c r="F177" s="5" t="inlineStr">
         <is>
@@ -5910,10 +5599,8 @@
           <t>It was a real grenade💥❓ [bQ1zrvJ42Vo].mp4</t>
         </is>
       </c>
-      <c r="E178" s="4" t="inlineStr">
-        <is>
-          <t>24-09-2026 06:35</t>
-        </is>
+      <c r="E178" s="8" t="n">
+        <v>46289.27430555555</v>
       </c>
       <c r="F178" s="5" t="inlineStr">
         <is>
@@ -5940,10 +5627,8 @@
           <t>It's Impossible to Catch Them But I Know Everything 📱❓ [f4SIoKnySlk].mp4</t>
         </is>
       </c>
-      <c r="E179" s="4" t="inlineStr">
-        <is>
-          <t>24-09-2026 17:35</t>
-        </is>
+      <c r="E179" s="8" t="n">
+        <v>46289.73263888889</v>
       </c>
       <c r="F179" s="5" t="inlineStr">
         <is>
@@ -5970,10 +5655,8 @@
           <t>Jumping into a BED not intended for sleeping👍❓ [Y5Z4uV27Kq0].mp4</t>
         </is>
       </c>
-      <c r="E180" s="4" t="inlineStr">
-        <is>
-          <t>24-09-2026 21:35</t>
-        </is>
+      <c r="E180" s="8" t="n">
+        <v>46289.89930555555</v>
       </c>
       <c r="F180" s="5" t="inlineStr">
         <is>
@@ -6000,10 +5683,8 @@
           <t>Kitten from a foam dispenser ✌️🐱？ [4V9qQReldR4].mp4</t>
         </is>
       </c>
-      <c r="E181" s="4" t="inlineStr">
-        <is>
-          <t>25-09-2026 00:35</t>
-        </is>
+      <c r="E181" s="8" t="n">
+        <v>46290.02430555555</v>
       </c>
       <c r="F181" s="5" t="inlineStr">
         <is>
@@ -6030,10 +5711,8 @@
           <t>Knights on Stilts VS Hungry Tigers🐯😂 [hqr31MIH58I].mp4</t>
         </is>
       </c>
-      <c r="E182" s="4" t="inlineStr">
-        <is>
-          <t>25-09-2026 04:35</t>
-        </is>
+      <c r="E182" s="8" t="n">
+        <v>46290.19097222222</v>
       </c>
       <c r="F182" s="5" t="inlineStr">
         <is>
@@ -6060,10 +5739,8 @@
           <t>LOL Cringe from Kinetic Sand ASMR Crush 👍❓ [MGEg0bTF6ns].mp4</t>
         </is>
       </c>
-      <c r="E183" s="4" t="inlineStr">
-        <is>
-          <t>25-09-2026 06:35</t>
-        </is>
+      <c r="E183" s="8" t="n">
+        <v>46290.27430555555</v>
       </c>
       <c r="F183" s="5" t="inlineStr">
         <is>
@@ -6090,10 +5767,8 @@
           <t>Learned to Fly a Pineapple While Doing This Trend 👍❓ [QVthHbKeEsE].mp4</t>
         </is>
       </c>
-      <c r="E184" s="4" t="inlineStr">
-        <is>
-          <t>25-09-2026 17:35</t>
-        </is>
+      <c r="E184" s="8" t="n">
+        <v>46290.73263888889</v>
       </c>
       <c r="F184" s="5" t="inlineStr">
         <is>
@@ -6120,10 +5795,8 @@
           <t>Lego Kids Level VS Pro 👍❓ [J0M4_ySEZ94].mp4</t>
         </is>
       </c>
-      <c r="E185" s="4" t="inlineStr">
-        <is>
-          <t>25-09-2026 21:35</t>
-        </is>
+      <c r="E185" s="8" t="n">
+        <v>46290.89930555555</v>
       </c>
       <c r="F185" s="5" t="inlineStr">
         <is>
@@ -6150,10 +5823,8 @@
           <t>Life Hack： How to Quickly Clean Your House 👌❓ [48-23laXvC4].mp4</t>
         </is>
       </c>
-      <c r="E186" s="4" t="inlineStr">
-        <is>
-          <t>26-09-2026 00:35</t>
-        </is>
+      <c r="E186" s="8" t="n">
+        <v>46291.02430555555</v>
       </c>
       <c r="F186" s="5" t="inlineStr">
         <is>
@@ -6180,10 +5851,8 @@
           <t>Lifehack on how to escape if you're buried in a coffin 💀❓ [F6mPj4Xrx2g].mp4</t>
         </is>
       </c>
-      <c r="E187" s="4" t="inlineStr">
-        <is>
-          <t>26-09-2026 04:35</t>
-        </is>
+      <c r="E187" s="8" t="n">
+        <v>46291.19097222222</v>
       </c>
       <c r="F187" s="5" t="inlineStr">
         <is>
@@ -6210,10 +5879,8 @@
           <t>Lifehack： Where You Can Easily and Quickly Make Money 🤑❓ [mIcM6jhzNI4].mp4</t>
         </is>
       </c>
-      <c r="E188" s="4" t="inlineStr">
-        <is>
-          <t>26-09-2026 06:35</t>
-        </is>
+      <c r="E188" s="8" t="n">
+        <v>46291.27430555555</v>
       </c>
       <c r="F188" s="5" t="inlineStr">
         <is>
@@ -6240,10 +5907,8 @@
           <t>Lollipop Lifehack： Child Level VS Professional👍❓ [z29on8CU6hc].mp4</t>
         </is>
       </c>
-      <c r="E189" s="4" t="inlineStr">
-        <is>
-          <t>26-09-2026 17:35</t>
-        </is>
+      <c r="E189" s="8" t="n">
+        <v>46291.73263888889</v>
       </c>
       <c r="F189" s="5" t="inlineStr">
         <is>
@@ -6270,10 +5935,8 @@
           <t>Luxury Women's Shoes on a Luxury Man 👠❓ [0jCxlsn4yUQ].mp4</t>
         </is>
       </c>
-      <c r="E190" s="4" t="inlineStr">
-        <is>
-          <t>26-09-2026 21:35</t>
-        </is>
+      <c r="E190" s="8" t="n">
+        <v>46291.89930555555</v>
       </c>
       <c r="F190" s="5" t="inlineStr">
         <is>
@@ -6300,10 +5963,8 @@
           <t>Made a Similar AI Video and Added a Mouse 🐭👍❓ [e6qR6ZmADxo].mp4</t>
         </is>
       </c>
-      <c r="E191" s="4" t="inlineStr">
-        <is>
-          <t>27-09-2026 00:35</t>
-        </is>
+      <c r="E191" s="8" t="n">
+        <v>46292.02430555555</v>
       </c>
       <c r="F191" s="5" t="inlineStr">
         <is>
@@ -6330,10 +5991,8 @@
           <t>Made a Similar Video Using AI 👍❓ [YIcFE4dl0Xw].mp4</t>
         </is>
       </c>
-      <c r="E192" s="4" t="inlineStr">
-        <is>
-          <t>27-09-2026 04:35</t>
-        </is>
+      <c r="E192" s="8" t="n">
+        <v>46292.19097222222</v>
       </c>
       <c r="F192" s="5" t="inlineStr">
         <is>
@@ -6360,10 +6019,8 @@
           <t>Made a drink in Pomegranate and my stomach exploded 😂👍 [UDvfeFkMMP8].mp4</t>
         </is>
       </c>
-      <c r="E193" s="4" t="inlineStr">
-        <is>
-          <t>27-09-2026 06:35</t>
-        </is>
+      <c r="E193" s="8" t="n">
+        <v>46292.27430555555</v>
       </c>
       <c r="F193" s="5" t="inlineStr">
         <is>
@@ -6390,10 +6047,8 @@
           <t>Made a similar video with animals using AI 🐯👍？ [U-dhQ18lwYU].mp4</t>
         </is>
       </c>
-      <c r="E194" s="4" t="inlineStr">
-        <is>
-          <t>27-09-2026 17:35</t>
-        </is>
+      <c r="E194" s="8" t="n">
+        <v>46292.73263888889</v>
       </c>
       <c r="F194" s="5" t="inlineStr">
         <is>
@@ -6420,10 +6075,8 @@
           <t>Mario Cosplay Gone Wrong 👲🏻❓ [uKes_0kFrhw].mp4</t>
         </is>
       </c>
-      <c r="E195" s="4" t="inlineStr">
-        <is>
-          <t>27-09-2026 21:35</t>
-        </is>
+      <c r="E195" s="8" t="n">
+        <v>46292.89930555555</v>
       </c>
       <c r="F195" s="5" t="inlineStr">
         <is>
@@ -6450,10 +6103,8 @@
           <t>Miniature chainsaw in the hands of a professional [9ZA2EB6gshg].mp4</t>
         </is>
       </c>
-      <c r="E196" s="4" t="inlineStr">
-        <is>
-          <t>28-09-2026 00:35</t>
-        </is>
+      <c r="E196" s="8" t="n">
+        <v>46293.02430555555</v>
       </c>
       <c r="F196" s="5" t="inlineStr">
         <is>
@@ -6480,10 +6131,8 @@
           <t>Misunderstanding in all its glory 💄❓ [sKWC4dKHe5Q].mp4</t>
         </is>
       </c>
-      <c r="E197" s="4" t="inlineStr">
-        <is>
-          <t>28-09-2026 04:35</t>
-        </is>
+      <c r="E197" s="8" t="n">
+        <v>46293.19097222222</v>
       </c>
       <c r="F197" s="5" t="inlineStr">
         <is>
@@ -6510,10 +6159,8 @@
           <t>Monkey Head-Shaped Treats 🐵❓ [LM7DFnGKAoA].mp4</t>
         </is>
       </c>
-      <c r="E198" s="4" t="inlineStr">
-        <is>
-          <t>28-09-2026 06:35</t>
-        </is>
+      <c r="E198" s="8" t="n">
+        <v>46293.27430555555</v>
       </c>
       <c r="F198" s="5" t="inlineStr">
         <is>
@@ -6540,10 +6187,8 @@
           <t>Mr. Sun New YouTube Trend Tutorial ☀️👍？ [9o3RuztRx4c].mp4</t>
         </is>
       </c>
-      <c r="E199" s="4" t="inlineStr">
-        <is>
-          <t>28-09-2026 17:35</t>
-        </is>
+      <c r="E199" s="8" t="n">
+        <v>46293.73263888889</v>
       </c>
       <c r="F199" s="5" t="inlineStr">
         <is>
@@ -6570,10 +6215,8 @@
           <t>My Editing Skills Doomed Him to Fall Off a Cliff 😂👍 [DweD5qNmckQ].mp4</t>
         </is>
       </c>
-      <c r="E200" s="4" t="inlineStr">
-        <is>
-          <t>28-09-2026 21:35</t>
-        </is>
+      <c r="E200" s="8" t="n">
+        <v>46293.89930555555</v>
       </c>
       <c r="F200" s="5" t="inlineStr">
         <is>
@@ -6600,10 +6243,8 @@
           <t>I have never seen anything funnier in my life 😂❓ [h3k4HQGwYY8].mp4</t>
         </is>
       </c>
-      <c r="E201" s="4" t="inlineStr">
-        <is>
-          <t>29-09-2026 00:35</t>
-        </is>
+      <c r="E201" s="8" t="n">
+        <v>46294.02430555555</v>
       </c>
       <c r="F201" s="5" t="inlineStr">
         <is>
@@ -6630,10 +6271,8 @@
           <t>My First lip sync With P. Diddy ✌️❓ [DgcxLoF6d6k].mp4</t>
         </is>
       </c>
-      <c r="E202" s="4" t="inlineStr">
-        <is>
-          <t>29-09-2026 04:35</t>
-        </is>
+      <c r="E202" s="8" t="n">
+        <v>46294.19097222222</v>
       </c>
       <c r="F202" s="5" t="inlineStr">
         <is>
@@ -6660,10 +6299,8 @@
           <t>My Nerves Couldn't Withstand Defeat 🎮❓ [kFLBI19zaDI].mp4</t>
         </is>
       </c>
-      <c r="E203" s="4" t="inlineStr">
-        <is>
-          <t>29-09-2026 06:35</t>
-        </is>
+      <c r="E203" s="8" t="n">
+        <v>46294.27430555555</v>
       </c>
       <c r="F203" s="5" t="inlineStr">
         <is>
@@ -6690,10 +6327,8 @@
           <t>My Rams Became Athletes [YcnlL2jEiTM].mp4</t>
         </is>
       </c>
-      <c r="E204" s="4" t="inlineStr">
-        <is>
-          <t>29-09-2026 17:35</t>
-        </is>
+      <c r="E204" s="8" t="n">
+        <v>46294.73263888889</v>
       </c>
       <c r="F204" s="5" t="inlineStr">
         <is>
@@ -6720,10 +6355,8 @@
           <t>My Wife Made Us Drinks But I Dropped Them 😭❓ [l2dDmdgh5GY].mp4</t>
         </is>
       </c>
-      <c r="E205" s="4" t="inlineStr">
-        <is>
-          <t>29-09-2026 21:35</t>
-        </is>
+      <c r="E205" s="8" t="n">
+        <v>46294.89930555555</v>
       </c>
       <c r="F205" s="5" t="inlineStr">
         <is>
@@ -6750,10 +6383,8 @@
           <t>My body if I actually committed to bodybuilding 💪❓ [-VpcrlVwLI4].mp4</t>
         </is>
       </c>
-      <c r="E206" s="4" t="inlineStr">
-        <is>
-          <t>30-09-2026 00:35</t>
-        </is>
+      <c r="E206" s="8" t="n">
+        <v>46295.02430555555</v>
       </c>
       <c r="F206" s="5" t="inlineStr">
         <is>
@@ -6780,10 +6411,8 @@
           <t>My nerves couldn't stand this impudence where they encroached on my apples 🍏❓ [SvW2k0J3kJM].mp4</t>
         </is>
       </c>
-      <c r="E207" s="4" t="inlineStr">
-        <is>
-          <t>30-09-2026 04:35</t>
-        </is>
+      <c r="E207" s="8" t="n">
+        <v>46295.19097222222</v>
       </c>
       <c r="F207" s="5" t="inlineStr">
         <is>
@@ -6810,10 +6439,8 @@
           <t>Never Eat Snow Again After Seeing This ❄️❓ [Z7_esJDszuY].mp4</t>
         </is>
       </c>
-      <c r="E208" s="4" t="inlineStr">
-        <is>
-          <t>30-09-2026 06:35</t>
-        </is>
+      <c r="E208" s="8" t="n">
+        <v>46295.27430555555</v>
       </c>
       <c r="F208" s="5" t="inlineStr">
         <is>
@@ -6840,10 +6467,8 @@
           <t>Never eating this again 💀❓ [Yj1ioFr35v8].mp4</t>
         </is>
       </c>
-      <c r="E209" s="4" t="inlineStr">
-        <is>
-          <t>30-09-2026 17:35</t>
-        </is>
+      <c r="E209" s="8" t="n">
+        <v>46295.73263888889</v>
       </c>
       <c r="F209" s="5" t="inlineStr">
         <is>
@@ -6870,10 +6495,8 @@
           <t>New Trend from 1 to 10 Launched 🎉🥳👍 [IHj1n15SCJ8].mp4</t>
         </is>
       </c>
-      <c r="E210" s="4" t="inlineStr">
-        <is>
-          <t>30-09-2026 21:35</t>
-        </is>
+      <c r="E210" s="8" t="n">
+        <v>46295.89930555555</v>
       </c>
       <c r="F210" s="5" t="inlineStr">
         <is>
@@ -6900,10 +6523,8 @@
           <t>Nobody Expected This Trick In A Shallow Water Zone 🏄‍♀️❓ [scx67t6mtN4].mp4</t>
         </is>
       </c>
-      <c r="E211" s="4" t="inlineStr">
-        <is>
-          <t>01-10-2026 00:35</t>
-        </is>
+      <c r="E211" s="8" t="n">
+        <v>46296.02430555555</v>
       </c>
       <c r="F211" s="5" t="inlineStr">
         <is>
@@ -6930,10 +6551,8 @@
           <t>Nobody Expects This Ear Hack to Actually Work  😮 [2HJlW7tvJlI].mp4</t>
         </is>
       </c>
-      <c r="E212" s="4" t="inlineStr">
-        <is>
-          <t>01-10-2026 04:35</t>
-        </is>
+      <c r="E212" s="8" t="n">
+        <v>46296.19097222222</v>
       </c>
       <c r="F212" s="5" t="inlineStr">
         <is>
@@ -6960,10 +6579,8 @@
           <t>Now you know how to do it👍❓ [t6g8_bCSA3A].mp4</t>
         </is>
       </c>
-      <c r="E213" s="4" t="inlineStr">
-        <is>
-          <t>01-10-2026 06:35</t>
-        </is>
+      <c r="E213" s="8" t="n">
+        <v>46296.27430555555</v>
       </c>
       <c r="F213" s="5" t="inlineStr">
         <is>
@@ -6990,10 +6607,8 @@
           <t>Nutella Nobody Knows What It's Really Made Of [Pgb2c5ksDDo].mp4</t>
         </is>
       </c>
-      <c r="E214" s="4" t="inlineStr">
-        <is>
-          <t>01-10-2026 17:35</t>
-        </is>
+      <c r="E214" s="8" t="n">
+        <v>46296.73263888889</v>
       </c>
       <c r="F214" s="5" t="inlineStr">
         <is>
@@ -7020,10 +6635,8 @@
           <t>Nutella lovers will understand me 👍❓ [4DRQx7V0C1M].mp4</t>
         </is>
       </c>
-      <c r="E215" s="4" t="inlineStr">
-        <is>
-          <t>01-10-2026 21:35</t>
-        </is>
+      <c r="E215" s="8" t="n">
+        <v>46296.89930555555</v>
       </c>
       <c r="F215" s="5" t="inlineStr">
         <is>
@@ -7050,10 +6663,8 @@
           <t>PIGGY BANK with HIDDEN powers🪙 [4ZWaD02xK_k].mp4</t>
         </is>
       </c>
-      <c r="E216" s="4" t="inlineStr">
-        <is>
-          <t>02-10-2026 00:35</t>
-        </is>
+      <c r="E216" s="8" t="n">
+        <v>46297.02430555555</v>
       </c>
       <c r="F216" s="5" t="inlineStr">
         <is>
@@ -7080,10 +6691,8 @@
           <t>POV： Engineer in India 🧠❓ [YIRtDCydpso].mp4</t>
         </is>
       </c>
-      <c r="E217" s="4" t="inlineStr">
-        <is>
-          <t>02-10-2026 04:35</t>
-        </is>
+      <c r="E217" s="8" t="n">
+        <v>46297.19097222222</v>
       </c>
       <c r="F217" s="5" t="inlineStr">
         <is>
@@ -7110,10 +6719,8 @@
           <t>POV： What Happens When You Use an Iron 🔌❓ [7xQxULp3Huw].mp4</t>
         </is>
       </c>
-      <c r="E218" s="4" t="inlineStr">
-        <is>
-          <t>02-10-2026 06:35</t>
-        </is>
+      <c r="E218" s="8" t="n">
+        <v>46297.27430555555</v>
       </c>
       <c r="F218" s="5" t="inlineStr">
         <is>
@@ -7140,10 +6747,8 @@
           <t>POV： When They Don't Know Your Worth! [y1eHfuzfDqY].mp4</t>
         </is>
       </c>
-      <c r="E219" s="4" t="inlineStr">
-        <is>
-          <t>02-10-2026 17:35</t>
-        </is>
+      <c r="E219" s="8" t="n">
+        <v>46297.73263888889</v>
       </c>
       <c r="F219" s="5" t="inlineStr">
         <is>
@@ -7170,10 +6775,8 @@
           <t>I visited an expensive restaurant TO TRY strange food 🦪 [NSGsf1dR-tU].mp4</t>
         </is>
       </c>
-      <c r="E220" s="4" t="inlineStr">
-        <is>
-          <t>02-10-2026 21:35</t>
-        </is>
+      <c r="E220" s="8" t="n">
+        <v>46297.89930555555</v>
       </c>
       <c r="F220" s="5" t="inlineStr">
         <is>
@@ -7200,10 +6803,8 @@
           <t>POV： You ask me to cook breakfast 🥚❓ [7RJYuN7C0AE].mp4</t>
         </is>
       </c>
-      <c r="E221" s="4" t="inlineStr">
-        <is>
-          <t>03-10-2026 00:35</t>
-        </is>
+      <c r="E221" s="8" t="n">
+        <v>46298.02430555555</v>
       </c>
       <c r="F221" s="5" t="inlineStr">
         <is>
@@ -7230,10 +6831,8 @@
           <t>POV： You're About to See the Funniest Trend Which I found today 😂👍 [sq5k8d6HPxU].mp4</t>
         </is>
       </c>
-      <c r="E222" s="4" t="inlineStr">
-        <is>
-          <t>03-10-2026 04:35</t>
-        </is>
+      <c r="E222" s="8" t="n">
+        <v>46298.19097222222</v>
       </c>
       <c r="F222" s="5" t="inlineStr">
         <is>
@@ -7260,10 +6859,8 @@
           <t>Paid a First-Class Specialist for His Work 🔨❓ [Oa138uA4iEc].mp4</t>
         </is>
       </c>
-      <c r="E223" s="4" t="inlineStr">
-        <is>
-          <t>03-10-2026 06:35</t>
-        </is>
+      <c r="E223" s="8" t="n">
+        <v>46298.27430555555</v>
       </c>
       <c r="F223" s="5" t="inlineStr">
         <is>
@@ -7290,10 +6887,8 @@
           <t>Pineapple's Superpower You Never Knew About 🍍❓ [nQZ3aBxJGc0].mp4</t>
         </is>
       </c>
-      <c r="E224" s="4" t="inlineStr">
-        <is>
-          <t>03-10-2026 17:35</t>
-        </is>
+      <c r="E224" s="8" t="n">
+        <v>46298.73263888889</v>
       </c>
       <c r="F224" s="5" t="inlineStr">
         <is>
@@ -7320,10 +6915,8 @@
           <t>Pineapple🍍+🍎Apple =❓ [xD6eN8acQJw].mp4</t>
         </is>
       </c>
-      <c r="E225" s="4" t="inlineStr">
-        <is>
-          <t>03-10-2026 21:35</t>
-        </is>
+      <c r="E225" s="8" t="n">
+        <v>46298.89930555555</v>
       </c>
       <c r="F225" s="5" t="inlineStr">
         <is>
@@ -7350,10 +6943,8 @@
           <t>Prank Anyone With This Umbrella ☂️❓ [jP8ybHNsW8g].mp4</t>
         </is>
       </c>
-      <c r="E226" s="4" t="inlineStr">
-        <is>
-          <t>04-10-2026 00:35</t>
-        </is>
+      <c r="E226" s="8" t="n">
+        <v>46299.02430555555</v>
       </c>
       <c r="F226" s="5" t="inlineStr">
         <is>
@@ -7380,10 +6971,8 @@
           <t>Prank with a fake knife 🔪❓ [09jDZD0c7ww].mp4</t>
         </is>
       </c>
-      <c r="E227" s="4" t="inlineStr">
-        <is>
-          <t>04-10-2026 04:35</t>
-        </is>
+      <c r="E227" s="8" t="n">
+        <v>46299.19097222222</v>
       </c>
       <c r="F227" s="5" t="inlineStr">
         <is>
@@ -7410,10 +6999,8 @@
           <t>Pranked Enraged Child of Enormous Size 👶❓ [UmJxh0XkJ9g].mp4</t>
         </is>
       </c>
-      <c r="E228" s="4" t="inlineStr">
-        <is>
-          <t>04-10-2026 06:35</t>
-        </is>
+      <c r="E228" s="8" t="n">
+        <v>46299.27430555555</v>
       </c>
       <c r="F228" s="5" t="inlineStr">
         <is>
@@ -7440,10 +7027,8 @@
           <t>Pranked a Dog with This Ancient Screamer 🐶❓ [yvUFPOWG0KQ].mp4</t>
         </is>
       </c>
-      <c r="E229" s="4" t="inlineStr">
-        <is>
-          <t>04-10-2026 17:35</t>
-        </is>
+      <c r="E229" s="8" t="n">
+        <v>46299.73263888889</v>
       </c>
       <c r="F229" s="5" t="inlineStr">
         <is>
@@ -7470,10 +7055,8 @@
           <t>Professional Level ASMR Experiment COMPLETELY Failed 🫙💦 [D07cEYEiGOI].mp4</t>
         </is>
       </c>
-      <c r="E230" s="4" t="inlineStr">
-        <is>
-          <t>04-10-2026 21:35</t>
-        </is>
+      <c r="E230" s="8" t="n">
+        <v>46299.89930555555</v>
       </c>
       <c r="F230" s="5" t="inlineStr">
         <is>
@@ -7500,10 +7083,8 @@
           <t>RAINBOW MOUTH HACK that actually works 🌈 [MA127iTlrt0].mp4</t>
         </is>
       </c>
-      <c r="E231" s="4" t="inlineStr">
-        <is>
-          <t>05-10-2026 00:35</t>
-        </is>
+      <c r="E231" s="8" t="n">
+        <v>46300.02430555555</v>
       </c>
       <c r="F231" s="5" t="inlineStr">
         <is>
@@ -7530,10 +7111,8 @@
           <t>Re-released the World's Most Popular ASMR Shorts 🍬❓ [EAl5zVu91TA].mp4</t>
         </is>
       </c>
-      <c r="E232" s="4" t="inlineStr">
-        <is>
-          <t>05-10-2026 04:35</t>
-        </is>
+      <c r="E232" s="8" t="n">
+        <v>46300.19097222222</v>
       </c>
       <c r="F232" s="5" t="inlineStr">
         <is>
@@ -7560,10 +7139,8 @@
           <t>Recreated Beautiful Animation with AI [Et_KWix9lGc].mp4</t>
         </is>
       </c>
-      <c r="E233" s="4" t="inlineStr">
-        <is>
-          <t>05-10-2026 06:35</t>
-        </is>
+      <c r="E233" s="8" t="n">
+        <v>46300.27430555555</v>
       </c>
       <c r="F233" s="5" t="inlineStr">
         <is>
@@ -7590,10 +7167,8 @@
           <t>Remote Control Ram Pulls Off Insane Stunt 🤪👍？ [7UHY9H-bYpY].mp4</t>
         </is>
       </c>
-      <c r="E234" s="4" t="inlineStr">
-        <is>
-          <t>05-10-2026 17:35</t>
-        </is>
+      <c r="E234" s="8" t="n">
+        <v>46300.73263888889</v>
       </c>
       <c r="F234" s="5" t="inlineStr">
         <is>
@@ -7620,10 +7195,8 @@
           <t>Renovate Your Apartment with AI 👍❓ [VhBGr8K6XeM].mp4</t>
         </is>
       </c>
-      <c r="E235" s="4" t="inlineStr">
-        <is>
-          <t>05-10-2026 21:35</t>
-        </is>
+      <c r="E235" s="8" t="n">
+        <v>46300.89930555555</v>
       </c>
       <c r="F235" s="5" t="inlineStr">
         <is>
@@ -7650,10 +7223,8 @@
           <t>Repeated a funny AI Fail video from TikTok 👍❓ [CAa1-RvZto0].mp4</t>
         </is>
       </c>
-      <c r="E236" s="4" t="inlineStr">
-        <is>
-          <t>06-10-2026 00:35</t>
-        </is>
+      <c r="E236" s="8" t="n">
+        <v>46301.02430555555</v>
       </c>
       <c r="F236" s="5" t="inlineStr">
         <is>
@@ -7680,10 +7251,8 @@
           <t>Repeated the ICE CREAM that AI loves to make 🐱✌️？ [zm3ZPWpdoyM].mp4</t>
         </is>
       </c>
-      <c r="E237" s="4" t="inlineStr">
-        <is>
-          <t>06-10-2026 04:35</t>
-        </is>
+      <c r="E237" s="8" t="n">
+        <v>46301.19097222222</v>
       </c>
       <c r="F237" s="5" t="inlineStr">
         <is>
@@ -7710,10 +7279,8 @@
           <t>Repeated this FUNNY Dance 👍❓ [SDxb24-BXiE].mp4</t>
         </is>
       </c>
-      <c r="E238" s="4" t="inlineStr">
-        <is>
-          <t>06-10-2026 06:35</t>
-        </is>
+      <c r="E238" s="8" t="n">
+        <v>46301.27430555555</v>
       </c>
       <c r="F238" s="5" t="inlineStr">
         <is>
@@ -7740,10 +7307,8 @@
           <t>Resin Rose Bubble Hack That's Actually Genius [3ZKnttQrGc4].mp4</t>
         </is>
       </c>
-      <c r="E239" s="4" t="inlineStr">
-        <is>
-          <t>06-10-2026 17:35</t>
-        </is>
+      <c r="E239" s="8" t="n">
+        <v>46301.73263888889</v>
       </c>
       <c r="F239" s="5" t="inlineStr">
         <is>
@@ -7770,10 +7335,8 @@
           <t>Roosters Are Ruining My Breakfast, But This Thing Saves It! [mt6TsrVFje4].mp4</t>
         </is>
       </c>
-      <c r="E240" s="4" t="inlineStr">
-        <is>
-          <t>06-10-2026 21:35</t>
-        </is>
+      <c r="E240" s="8" t="n">
+        <v>46301.89930555555</v>
       </c>
       <c r="F240" s="5" t="inlineStr">
         <is>
@@ -7800,10 +7363,8 @@
           <t>STOP Wasting Time on Manual Bubble Slicing🫧AI is Here to HELP👍 [xiz7urPf-po].mp4</t>
         </is>
       </c>
-      <c r="E241" s="4" t="inlineStr">
-        <is>
-          <t>07-10-2026 00:35</t>
-        </is>
+      <c r="E241" s="8" t="n">
+        <v>46302.02430555555</v>
       </c>
       <c r="F241" s="5" t="inlineStr">
         <is>
@@ -7830,10 +7391,8 @@
           <t>Same Thing But with Trollface 2D Animation 👍❓ [51fEvHOuEp8].mp4</t>
         </is>
       </c>
-      <c r="E242" s="4" t="inlineStr">
-        <is>
-          <t>07-10-2026 04:35</t>
-        </is>
+      <c r="E242" s="8" t="n">
+        <v>46302.19097222222</v>
       </c>
       <c r="F242" s="5" t="inlineStr">
         <is>
@@ -7860,10 +7419,8 @@
           <t>Same mistake, twice the embarrassment in Roblox 👍❓ [xHW2jHgQviY].mp4</t>
         </is>
       </c>
-      <c r="E243" s="4" t="inlineStr">
-        <is>
-          <t>07-10-2026 06:35</t>
-        </is>
+      <c r="E243" s="8" t="n">
+        <v>46302.27430555555</v>
       </c>
       <c r="F243" s="5" t="inlineStr">
         <is>
@@ -7890,10 +7447,8 @@
           <t>Santa Claus made of foil I'm officially ending this TikTok trend 🎅👍？ [0VMC-Ira7Q8].mp4</t>
         </is>
       </c>
-      <c r="E244" s="4" t="inlineStr">
-        <is>
-          <t>07-10-2026 17:35</t>
-        </is>
+      <c r="E244" s="8" t="n">
+        <v>46302.73263888889</v>
       </c>
       <c r="F244" s="5" t="inlineStr">
         <is>
@@ -7920,10 +7475,8 @@
           <t>Sat Down to Watch a Movie with Delicious Food 😂❓ [IMhmLL8G3Zs].mp4</t>
         </is>
       </c>
-      <c r="E245" s="4" t="inlineStr">
-        <is>
-          <t>07-10-2026 21:35</t>
-        </is>
+      <c r="E245" s="8" t="n">
+        <v>46302.89930555555</v>
       </c>
       <c r="F245" s="5" t="inlineStr">
         <is>
@@ -7950,10 +7503,8 @@
           <t>Satisfying Yet Disgusting tung tung tung sahur Slime [DvtW9pGrzyw].mp4</t>
         </is>
       </c>
-      <c r="E246" s="4" t="inlineStr">
-        <is>
-          <t>08-10-2026 00:35</t>
-        </is>
+      <c r="E246" s="8" t="n">
+        <v>46303.02430555555</v>
       </c>
       <c r="F246" s="5" t="inlineStr">
         <is>
@@ -7980,10 +7531,8 @@
           <t>Scary Leg Makeup That Shocks Everyone 🦶❓ [YZJd6vBAoJk].mp4</t>
         </is>
       </c>
-      <c r="E247" s="4" t="inlineStr">
-        <is>
-          <t>08-10-2026 04:35</t>
-        </is>
+      <c r="E247" s="8" t="n">
+        <v>46303.19097222222</v>
       </c>
       <c r="F247" s="5" t="inlineStr">
         <is>
@@ -8010,10 +7559,8 @@
           <t>School in a nutshell 🗑️👍？ [GqWEUteoPDE].mp4</t>
         </is>
       </c>
-      <c r="E248" s="4" t="inlineStr">
-        <is>
-          <t>08-10-2026 06:35</t>
-        </is>
+      <c r="E248" s="8" t="n">
+        <v>46303.27430555555</v>
       </c>
       <c r="F248" s="5" t="inlineStr">
         <is>
@@ -8040,10 +7587,8 @@
           <t>Scooter Balance Challenge Gone Wrong🛴❓ [IsDxJiXUV7w].mp4</t>
         </is>
       </c>
-      <c r="E249" s="4" t="inlineStr">
-        <is>
-          <t>08-10-2026 17:35</t>
-        </is>
+      <c r="E249" s="8" t="n">
+        <v>46303.73263888889</v>
       </c>
       <c r="F249" s="5" t="inlineStr">
         <is>
@@ -8070,10 +7615,8 @@
           <t>Setibabu Funny Trend 👍❓ [V-kj06-6Z7k].mp4</t>
         </is>
       </c>
-      <c r="E250" s="4" t="inlineStr">
-        <is>
-          <t>08-10-2026 21:35</t>
-        </is>
+      <c r="E250" s="8" t="n">
+        <v>46303.89930555555</v>
       </c>
       <c r="F250" s="5" t="inlineStr">
         <is>
@@ -8100,10 +7643,8 @@
           <t>Setibabu New TikTok Trend 😹👍❓ [HWGxJl5YgBk].mp4</t>
         </is>
       </c>
-      <c r="E251" s="4" t="inlineStr">
-        <is>
-          <t>09-10-2026 00:35</t>
-        </is>
+      <c r="E251" s="8" t="n">
+        <v>46304.02430555555</v>
       </c>
       <c r="F251" s="5" t="inlineStr">
         <is>
@@ -8130,10 +7671,8 @@
           <t>She Can't Imagine Where This Chupa Chups Has Been📍 [qBexcjdbGnQ].mp4</t>
         </is>
       </c>
-      <c r="E252" s="4" t="inlineStr">
-        <is>
-          <t>09-10-2026 04:35</t>
-        </is>
+      <c r="E252" s="8" t="n">
+        <v>46304.19097222222</v>
       </c>
       <c r="F252" s="5" t="inlineStr">
         <is>
@@ -8160,10 +7699,8 @@
           <t>Showed her a SHOCKING illusion [rEkdZtGbqdw].mp4</t>
         </is>
       </c>
-      <c r="E253" s="4" t="inlineStr">
-        <is>
-          <t>09-10-2026 06:35</t>
-        </is>
+      <c r="E253" s="8" t="n">
+        <v>46304.27430555555</v>
       </c>
       <c r="F253" s="5" t="inlineStr">
         <is>
@@ -8190,10 +7727,8 @@
           <t>Shower Curtain Horror Stories You Won't Believe Happened 😹❓ [mugBDPJ1IWQ].mp4</t>
         </is>
       </c>
-      <c r="E254" s="4" t="inlineStr">
-        <is>
-          <t>09-10-2026 17:35</t>
-        </is>
+      <c r="E254" s="8" t="n">
+        <v>46304.73263888889</v>
       </c>
       <c r="F254" s="5" t="inlineStr">
         <is>
@@ -8220,10 +7755,8 @@
           <t>Skibidi Toilet Gets CAUGHT by Police 🚨 [YW9El6bAsCY].mp4</t>
         </is>
       </c>
-      <c r="E255" s="4" t="inlineStr">
-        <is>
-          <t>09-10-2026 21:35</t>
-        </is>
+      <c r="E255" s="8" t="n">
+        <v>46304.89930555555</v>
       </c>
       <c r="F255" s="5" t="inlineStr">
         <is>
@@ -8250,10 +7783,8 @@
           <t>Smart Consumption VS Crazy Consumption 👍❓ [NXy3aY5j-ks].mp4</t>
         </is>
       </c>
-      <c r="E256" s="4" t="inlineStr">
-        <is>
-          <t>10-10-2026 00:35</t>
-        </is>
+      <c r="E256" s="8" t="n">
+        <v>46305.02430555555</v>
       </c>
       <c r="F256" s="5" t="inlineStr">
         <is>
@@ -8280,10 +7811,8 @@
           <t>Smashing This Glass Orb Was the Biggest Mistake [At-Z5Xm0vHM].mp4</t>
         </is>
       </c>
-      <c r="E257" s="4" t="inlineStr">
-        <is>
-          <t>10-10-2026 04:35</t>
-        </is>
+      <c r="E257" s="8" t="n">
+        <v>46305.19097222222</v>
       </c>
       <c r="F257" s="5" t="inlineStr">
         <is>
@@ -8310,10 +7839,8 @@
           <t>Snake Venom vs Blood - Science Experiment 🐍 [B5ygy5jarec].mp4</t>
         </is>
       </c>
-      <c r="E258" s="4" t="inlineStr">
-        <is>
-          <t>10-10-2026 06:35</t>
-        </is>
+      <c r="E258" s="8" t="n">
+        <v>46305.27430555555</v>
       </c>
       <c r="F258" s="5" t="inlineStr">
         <is>
@@ -8340,10 +7867,8 @@
           <t>Snow Bunny Gains Great Popularity in Winter🐰👍 [Z37iU-h_OFc].mp4</t>
         </is>
       </c>
-      <c r="E259" s="4" t="inlineStr">
-        <is>
-          <t>10-10-2026 17:35</t>
-        </is>
+      <c r="E259" s="8" t="n">
+        <v>46305.73263888889</v>
       </c>
       <c r="F259" s="5" t="inlineStr">
         <is>
@@ -8370,10 +7895,8 @@
           <t>Soap Pump Hack You Need To See! [-PgAivj1YD0].mp4</t>
         </is>
       </c>
-      <c r="E260" s="4" t="inlineStr">
-        <is>
-          <t>10-10-2026 21:35</t>
-        </is>
+      <c r="E260" s="8" t="n">
+        <v>46305.89930555555</v>
       </c>
       <c r="F260" s="5" t="inlineStr">
         <is>
@@ -8400,10 +7923,8 @@
           <t>Squid Game Doll vs Panda Cup Chaos 💀 [09CnZ2NHrHU].mp4</t>
         </is>
       </c>
-      <c r="E261" s="4" t="inlineStr">
-        <is>
-          <t>11-10-2026 00:35</t>
-        </is>
+      <c r="E261" s="8" t="n">
+        <v>46306.02430555555</v>
       </c>
       <c r="F261" s="5" t="inlineStr">
         <is>
@@ -8430,10 +7951,8 @@
           <t>Stylish Roller Skates for the Weekend [V5DH-zoTqJc].mp4</t>
         </is>
       </c>
-      <c r="E262" s="4" t="inlineStr">
-        <is>
-          <t>11-10-2026 04:35</t>
-        </is>
+      <c r="E262" s="8" t="n">
+        <v>46306.19097222222</v>
       </c>
       <c r="F262" s="5" t="inlineStr">
         <is>
@@ -8460,10 +7979,8 @@
           <t>Styrofoam VS Hot Stuff (Crazy Test Drive) 👍❓ [pKa-zbyx19c].mp4</t>
         </is>
       </c>
-      <c r="E263" s="4" t="inlineStr">
-        <is>
-          <t>11-10-2026 06:35</t>
-        </is>
+      <c r="E263" s="8" t="n">
+        <v>46306.27430555555</v>
       </c>
       <c r="F263" s="5" t="inlineStr">
         <is>
@@ -8490,10 +8007,8 @@
           <t>Sushi Lover, A Short History 😂👍？ [tacW3si4_lI].mp4</t>
         </is>
       </c>
-      <c r="E264" s="4" t="inlineStr">
-        <is>
-          <t>11-10-2026 17:35</t>
-        </is>
+      <c r="E264" s="8" t="n">
+        <v>46306.73263888889</v>
       </c>
       <c r="F264" s="5" t="inlineStr">
         <is>
@@ -8520,10 +8035,8 @@
           <t>Tea at the Most Expensive Restaurant in the World [8iMnjsvicdg].mp4</t>
         </is>
       </c>
-      <c r="E265" s="4" t="inlineStr">
-        <is>
-          <t>11-10-2026 21:35</t>
-        </is>
+      <c r="E265" s="8" t="n">
+        <v>46306.89930555555</v>
       </c>
       <c r="F265" s="5" t="inlineStr">
         <is>
@@ -8550,10 +8063,8 @@
           <t>Tell me honestly, what did you see？ [Bgd5R3lHz5g].mp4</t>
         </is>
       </c>
-      <c r="E266" s="4" t="inlineStr">
-        <is>
-          <t>12-10-2026 00:35</t>
-        </is>
+      <c r="E266" s="8" t="n">
+        <v>46307.02430555555</v>
       </c>
       <c r="F266" s="5" t="inlineStr">
         <is>
@@ -8580,10 +8091,8 @@
           <t>Testing Popular Candy on Dentures GONE WRONG 😬❓ [Xkx447kLLU4].mp4</t>
         </is>
       </c>
-      <c r="E267" s="4" t="inlineStr">
-        <is>
-          <t>12-10-2026 04:35</t>
-        </is>
+      <c r="E267" s="8" t="n">
+        <v>46307.19097222222</v>
       </c>
       <c r="F267" s="5" t="inlineStr">
         <is>
@@ -8610,10 +8119,8 @@
           <t>Testing WORKING Life Hacks on a Lie Detector ✅ [CfCsA1R5l0E].mp4</t>
         </is>
       </c>
-      <c r="E268" s="4" t="inlineStr">
-        <is>
-          <t>12-10-2026 06:35</t>
-        </is>
+      <c r="E268" s="8" t="n">
+        <v>46307.27430555555</v>
       </c>
       <c r="F268" s="5" t="inlineStr">
         <is>
@@ -8668,10 +8175,8 @@
           <t>That water TRICK everyone's sharing doesn't actually work？💦 [gZqM89xB63o].mp4</t>
         </is>
       </c>
-      <c r="E270" s="4" t="inlineStr">
-        <is>
-          <t>12-10-2026 21:35</t>
-        </is>
+      <c r="E270" s="8" t="n">
+        <v>46307.89930555555</v>
       </c>
       <c r="F270" s="5" t="inlineStr">
         <is>
@@ -8698,10 +8203,8 @@
           <t>The AI ​​didn't understand my request completely correctly 😂👍 [voUk2ZIMIqA].mp4</t>
         </is>
       </c>
-      <c r="E271" s="4" t="inlineStr">
-        <is>
-          <t>13-10-2026 00:35</t>
-        </is>
+      <c r="E271" s="8" t="n">
+        <v>46308.02430555555</v>
       </c>
       <c r="F271" s="5" t="inlineStr">
         <is>
@@ -8728,10 +8231,8 @@
           <t>The Best Sink in the World 👍❓ [Dpna9alkvUA].mp4</t>
         </is>
       </c>
-      <c r="E272" s="4" t="inlineStr">
-        <is>
-          <t>13-10-2026 04:35</t>
-        </is>
+      <c r="E272" s="8" t="n">
+        <v>46308.19097222222</v>
       </c>
       <c r="F272" s="5" t="inlineStr">
         <is>
@@ -8758,10 +8259,8 @@
           <t>The Biggest Pill in the World 💊❓ [d5O1vg_H8jU].mp4</t>
         </is>
       </c>
-      <c r="E273" s="4" t="inlineStr">
-        <is>
-          <t>13-10-2026 06:35</t>
-        </is>
+      <c r="E273" s="8" t="n">
+        <v>46308.27430555555</v>
       </c>
       <c r="F273" s="5" t="inlineStr">
         <is>
@@ -8788,10 +8287,8 @@
           <t>The CRAZY Difference Between Cheap and EXPENSIVE Water Guns 🔫❓ [dfYWT07MvAs].mp4</t>
         </is>
       </c>
-      <c r="E274" s="4" t="inlineStr">
-        <is>
-          <t>13-10-2026 17:35</t>
-        </is>
+      <c r="E274" s="8" t="n">
+        <v>46308.73263888889</v>
       </c>
       <c r="F274" s="5" t="inlineStr">
         <is>
@@ -8818,10 +8315,8 @@
           <t>The Crazy Foil Santa Trend 🎅👍？ [Mx6q4VoMDJM].mp4</t>
         </is>
       </c>
-      <c r="E275" s="4" t="inlineStr">
-        <is>
-          <t>13-10-2026 21:35</t>
-        </is>
+      <c r="E275" s="8" t="n">
+        <v>46308.89930555555</v>
       </c>
       <c r="F275" s="5" t="inlineStr">
         <is>
@@ -8848,10 +8343,8 @@
           <t>POV： When a Girl Wanted Breakfast in Bed 🥚❓ [OIV8PjCTjm4].mp4</t>
         </is>
       </c>
-      <c r="E276" s="4" t="inlineStr">
-        <is>
-          <t>14-10-2026 00:35</t>
-        </is>
+      <c r="E276" s="8" t="n">
+        <v>46309.02430555555</v>
       </c>
       <c r="F276" s="5" t="inlineStr">
         <is>
@@ -8878,10 +8371,8 @@
           <t>The Crazy Puzzle That Won't Fit 😡❓ [Y9bWuq9Tfo4].mp4</t>
         </is>
       </c>
-      <c r="E277" s="4" t="inlineStr">
-        <is>
-          <t>14-10-2026 04:35</t>
-        </is>
+      <c r="E277" s="8" t="n">
+        <v>46309.19097222222</v>
       </c>
       <c r="F277" s="5" t="inlineStr">
         <is>
@@ -8908,10 +8399,8 @@
           <t>The Deadly TikTok Challenge  💀 [YRf8SPd8KZY].mp4</t>
         </is>
       </c>
-      <c r="E278" s="4" t="inlineStr">
-        <is>
-          <t>14-10-2026 06:35</t>
-        </is>
+      <c r="E278" s="8" t="n">
+        <v>46309.27430555555</v>
       </c>
       <c r="F278" s="5" t="inlineStr">
         <is>
@@ -8938,10 +8427,8 @@
           <t>The FOIL Santa Trend is OVER! What Happened？ 🎅👍 [dWAzXBuFn8Q].mp4</t>
         </is>
       </c>
-      <c r="E279" s="4" t="inlineStr">
-        <is>
-          <t>14-10-2026 17:35</t>
-        </is>
+      <c r="E279" s="8" t="n">
+        <v>46309.73263888889</v>
       </c>
       <c r="F279" s="5" t="inlineStr">
         <is>
@@ -8968,10 +8455,8 @@
           <t>The First And Last Time I Played As A Target Stand! [N6W8Nh3zUmU].mp4</t>
         </is>
       </c>
-      <c r="E280" s="4" t="inlineStr">
-        <is>
-          <t>14-10-2026 21:35</t>
-        </is>
+      <c r="E280" s="8" t="n">
+        <v>46309.89930555555</v>
       </c>
       <c r="F280" s="5" t="inlineStr">
         <is>
@@ -8998,10 +8483,8 @@
           <t>The Hare Who Saw More Than You in These Shorts 🐇❓ [Cw-RLBYrvpA].mp4</t>
         </is>
       </c>
-      <c r="E281" s="4" t="inlineStr">
-        <is>
-          <t>15-10-2026 00:35</t>
-        </is>
+      <c r="E281" s="8" t="n">
+        <v>46310.02430555555</v>
       </c>
       <c r="F281" s="5" t="inlineStr">
         <is>
@@ -9028,10 +8511,8 @@
           <t>The Incomprehensible TikTok Puzzle 🧠❓ [Yz1Y84ZDEBw].mp4</t>
         </is>
       </c>
-      <c r="E282" s="4" t="inlineStr">
-        <is>
-          <t>15-10-2026 04:35</t>
-        </is>
+      <c r="E282" s="8" t="n">
+        <v>46310.19097222222</v>
       </c>
       <c r="F282" s="5" t="inlineStr">
         <is>
@@ -9058,10 +8539,8 @@
           <t>The Iron Horse That I Wanted to Ride Too 🐴❓ [W5rk8sqRZ3U].mp4</t>
         </is>
       </c>
-      <c r="E283" s="4" t="inlineStr">
-        <is>
-          <t>15-10-2026 06:35</t>
-        </is>
+      <c r="E283" s="8" t="n">
+        <v>46310.27430555555</v>
       </c>
       <c r="F283" s="5" t="inlineStr">
         <is>
@@ -9088,10 +8567,8 @@
           <t>The Life Hack That Changed My Life [m8ko5S3SIrA].mp4</t>
         </is>
       </c>
-      <c r="E284" s="4" t="inlineStr">
-        <is>
-          <t>15-10-2026 17:35</t>
-        </is>
+      <c r="E284" s="8" t="n">
+        <v>46310.73263888889</v>
       </c>
       <c r="F284" s="5" t="inlineStr">
         <is>
@@ -9118,10 +8595,8 @@
           <t>The Man Who Uses a Miniature Chainsaw [7GfcPUeRRac].mp4</t>
         </is>
       </c>
-      <c r="E285" s="4" t="inlineStr">
-        <is>
-          <t>15-10-2026 21:35</t>
-        </is>
+      <c r="E285" s="8" t="n">
+        <v>46310.89930555555</v>
       </c>
       <c r="F285" s="5" t="inlineStr">
         <is>
@@ -9148,10 +8623,8 @@
           <t>The Monkey Went Crazy 🐵❓ [FFxa2FPpZ08].mp4</t>
         </is>
       </c>
-      <c r="E286" s="4" t="inlineStr">
-        <is>
-          <t>16-10-2026 00:35</t>
-        </is>
+      <c r="E286" s="8" t="n">
+        <v>46311.02430555555</v>
       </c>
       <c r="F286" s="5" t="inlineStr">
         <is>
@@ -9178,10 +8651,8 @@
           <t>The New Trend That Will Take Over the Internet 🐻👍？ [-DVCDfWd8n8].mp4</t>
         </is>
       </c>
-      <c r="E287" s="4" t="inlineStr">
-        <is>
-          <t>16-10-2026 04:35</t>
-        </is>
+      <c r="E287" s="8" t="n">
+        <v>46311.19097222222</v>
       </c>
       <c r="F287" s="5" t="inlineStr">
         <is>
@@ -9208,10 +8679,8 @@
           <t>The Only Pet I Feed Gourmet Meals 🚽❓ [RYU38X5vsrM].mp4</t>
         </is>
       </c>
-      <c r="E288" s="4" t="inlineStr">
-        <is>
-          <t>16-10-2026 06:35</t>
-        </is>
+      <c r="E288" s="8" t="n">
+        <v>46311.27430555555</v>
       </c>
       <c r="F288" s="5" t="inlineStr">
         <is>
@@ -9238,10 +8707,8 @@
           <t>The Puzzle That Broke My Life 😖❓ [hZDUAnTHg74].mp4</t>
         </is>
       </c>
-      <c r="E289" s="4" t="inlineStr">
-        <is>
-          <t>16-10-2026 17:35</t>
-        </is>
+      <c r="E289" s="8" t="n">
+        <v>46311.73263888889</v>
       </c>
       <c r="F289" s="5" t="inlineStr">
         <is>
@@ -9268,10 +8735,8 @@
           <t>The Puzzle That Drives You Crazy 🤯❓ [4n88CAkl-2g].mp4</t>
         </is>
       </c>
-      <c r="E290" s="4" t="inlineStr">
-        <is>
-          <t>16-10-2026 21:35</t>
-        </is>
+      <c r="E290" s="8" t="n">
+        <v>46311.89930555555</v>
       </c>
       <c r="F290" s="5" t="inlineStr">
         <is>
@@ -9298,10 +8763,8 @@
           <t>The Rarest Glasses Money Can Buy 👓👍？ [8O456iSo3c4].mp4</t>
         </is>
       </c>
-      <c r="E291" s="4" t="inlineStr">
-        <is>
-          <t>17-10-2026 00:35</t>
-        </is>
+      <c r="E291" s="8" t="n">
+        <v>46312.02430555555</v>
       </c>
       <c r="F291" s="5" t="inlineStr">
         <is>
@@ -9328,10 +8791,8 @@
           <t>The Robber Had No Idea Who He Was Messing With 💪❓ [WoKp_n_UDus].mp4</t>
         </is>
       </c>
-      <c r="E292" s="4" t="inlineStr">
-        <is>
-          <t>17-10-2026 04:35</t>
-        </is>
+      <c r="E292" s="8" t="n">
+        <v>46312.19097222222</v>
       </c>
       <c r="F292" s="5" t="inlineStr">
         <is>
@@ -9358,10 +8819,8 @@
           <t>The SECRET to Creating Hilarious Art Revealed 😂❓ [_Ff7R85f3YU].mp4</t>
         </is>
       </c>
-      <c r="E293" s="4" t="inlineStr">
-        <is>
-          <t>17-10-2026 06:35</t>
-        </is>
+      <c r="E293" s="8" t="n">
+        <v>46312.27430555555</v>
       </c>
       <c r="F293" s="5" t="inlineStr">
         <is>
@@ -9388,10 +8847,8 @@
           <t>The Secret Way That Solves This Puzzle 🧠❓ [2a1Bxv3IShY].mp4</t>
         </is>
       </c>
-      <c r="E294" s="4" t="inlineStr">
-        <is>
-          <t>17-10-2026 17:35</t>
-        </is>
+      <c r="E294" s="8" t="n">
+        <v>46312.73263888889</v>
       </c>
       <c r="F294" s="5" t="inlineStr">
         <is>
@@ -9418,10 +8875,8 @@
           <t>The Silly TikTok Trend Everyone's Loving 🤙❓ [aBE0QqOdv8w].mp4</t>
         </is>
       </c>
-      <c r="E295" s="4" t="inlineStr">
-        <is>
-          <t>17-10-2026 21:35</t>
-        </is>
+      <c r="E295" s="8" t="n">
+        <v>46312.89930555555</v>
       </c>
       <c r="F295" s="5" t="inlineStr">
         <is>
@@ -9448,10 +8903,8 @@
           <t>The Strangest BED in the World [v9Yn5MetEmA].mp4</t>
         </is>
       </c>
-      <c r="E296" s="4" t="inlineStr">
-        <is>
-          <t>18-10-2026 00:35</t>
-        </is>
+      <c r="E296" s="8" t="n">
+        <v>46313.02430555555</v>
       </c>
       <c r="F296" s="5" t="inlineStr">
         <is>
@@ -9478,10 +8931,8 @@
           <t>The Trend That Exploded the Entire Internet 👍❓ [oz8DGQk4HeY].mp4</t>
         </is>
       </c>
-      <c r="E297" s="4" t="inlineStr">
-        <is>
-          <t>18-10-2026 04:35</t>
-        </is>
+      <c r="E297" s="8" t="n">
+        <v>46313.19097222222</v>
       </c>
       <c r="F297" s="5" t="inlineStr">
         <is>
@@ -9508,10 +8959,8 @@
           <t>The Trick That Turned Into Loss of Control 🥶❓ [v8uKQFQsx1I].mp4</t>
         </is>
       </c>
-      <c r="E298" s="4" t="inlineStr">
-        <is>
-          <t>18-10-2026 06:35</t>
-        </is>
+      <c r="E298" s="8" t="n">
+        <v>46313.27430555555</v>
       </c>
       <c r="F298" s="5" t="inlineStr">
         <is>
@@ -9538,10 +8987,8 @@
           <t>The Turtle Cup Holder You'll Now Dream About 🐢❓ [6gJLDx6sl9U].mp4</t>
         </is>
       </c>
-      <c r="E299" s="4" t="inlineStr">
-        <is>
-          <t>18-10-2026 17:35</t>
-        </is>
+      <c r="E299" s="8" t="n">
+        <v>46313.73263888889</v>
       </c>
       <c r="F299" s="5" t="inlineStr">
         <is>
@@ -9568,10 +9015,8 @@
           <t>The Ugly Truth About Where Popcorn Comes From 🌽❓ [bSs2TXcZtE8].mp4</t>
         </is>
       </c>
-      <c r="E300" s="4" t="inlineStr">
-        <is>
-          <t>18-10-2026 21:35</t>
-        </is>
+      <c r="E300" s="8" t="n">
+        <v>46313.89930555555</v>
       </c>
       <c r="F300" s="5" t="inlineStr">
         <is>
@@ -9598,10 +9043,8 @@
           <t>The Violinist You Deserve 🎻❓ [M3Y2JFHtLIU].mp4</t>
         </is>
       </c>
-      <c r="E301" s="4" t="inlineStr">
-        <is>
-          <t>19-10-2026 00:35</t>
-        </is>
+      <c r="E301" s="8" t="n">
+        <v>46314.02430555555</v>
       </c>
       <c r="F301" s="5" t="inlineStr">
         <is>
@@ -9628,10 +9071,8 @@
           <t>The WORST House Slippers According to AI 🩴 [iGIxDHR8wSg].mp4</t>
         </is>
       </c>
-      <c r="E302" s="4" t="inlineStr">
-        <is>
-          <t>19-10-2026 04:35</t>
-        </is>
+      <c r="E302" s="8" t="n">
+        <v>46314.19097222222</v>
       </c>
       <c r="F302" s="5" t="inlineStr">
         <is>
@@ -9658,10 +9099,8 @@
           <t>The WORST TikTok Filter Bug EVER 🚗❓ [xYSHogI_Z-Y].mp4</t>
         </is>
       </c>
-      <c r="E303" s="4" t="inlineStr">
-        <is>
-          <t>19-10-2026 06:35</t>
-        </is>
+      <c r="E303" s="8" t="n">
+        <v>46314.27430555555</v>
       </c>
       <c r="F303" s="5" t="inlineStr">
         <is>
@@ -9688,10 +9127,8 @@
           <t>The Woman Who Loves Eggs ASMR eating🥚❓ [XohnWw5l9FE].mp4</t>
         </is>
       </c>
-      <c r="E304" s="4" t="inlineStr">
-        <is>
-          <t>19-10-2026 17:35</t>
-        </is>
+      <c r="E304" s="8" t="n">
+        <v>46314.73263888889</v>
       </c>
       <c r="F304" s="5" t="inlineStr">
         <is>
@@ -9718,10 +9155,8 @@
           <t>The World's Longest Non-Domino Chain I Built [CGpNBy6p4Vo].mp4</t>
         </is>
       </c>
-      <c r="E305" s="4" t="inlineStr">
-        <is>
-          <t>19-10-2026 21:35</t>
-        </is>
+      <c r="E305" s="8" t="n">
+        <v>46314.89930555555</v>
       </c>
       <c r="F305" s="5" t="inlineStr">
         <is>
@@ -9748,10 +9183,8 @@
           <t>The World's Most Powerful Hair Growth Spray 🧴💨？ [21lHe1U9V68].mp4</t>
         </is>
       </c>
-      <c r="E306" s="4" t="inlineStr">
-        <is>
-          <t>20-10-2026 00:35</t>
-        </is>
+      <c r="E306" s="8" t="n">
+        <v>46315.02430555555</v>
       </c>
       <c r="F306" s="5" t="inlineStr">
         <is>
@@ -9778,10 +9211,8 @@
           <t>The broken toilet seat completely sucked me in 🚽❓ [Msbg70iJ7Cc].mp4</t>
         </is>
       </c>
-      <c r="E307" s="4" t="inlineStr">
-        <is>
-          <t>20-10-2026 04:35</t>
-        </is>
+      <c r="E307" s="8" t="n">
+        <v>46315.19097222222</v>
       </c>
       <c r="F307" s="5" t="inlineStr">
         <is>
@@ -9808,10 +9239,8 @@
           <t>The ending of this cat video 💀 [59YhfAtPAgs].mp4</t>
         </is>
       </c>
-      <c r="E308" s="4" t="inlineStr">
-        <is>
-          <t>20-10-2026 06:35</t>
-        </is>
+      <c r="E308" s="8" t="n">
+        <v>46315.27430555555</v>
       </c>
       <c r="F308" s="5" t="inlineStr">
         <is>
@@ -9838,10 +9267,8 @@
           <t>The father fed his eldest stepson [zHFUX3Pc-fk].mp4</t>
         </is>
       </c>
-      <c r="E309" s="4" t="inlineStr">
-        <is>
-          <t>20-10-2026 17:35</t>
-        </is>
+      <c r="E309" s="8" t="n">
+        <v>46315.73263888889</v>
       </c>
       <c r="F309" s="5" t="inlineStr">
         <is>
@@ -9868,10 +9295,8 @@
           <t>The funniest barista prank in the world 😂👍？ [kHcFVQKpu5I].mp4</t>
         </is>
       </c>
-      <c r="E310" s="4" t="inlineStr">
-        <is>
-          <t>20-10-2026 21:35</t>
-        </is>
+      <c r="E310" s="8" t="n">
+        <v>46315.89930555555</v>
       </c>
       <c r="F310" s="5" t="inlineStr">
         <is>
@@ -9898,10 +9323,8 @@
           <t>The kiss you didn't expect but really wanted 💋 [DpI33ou1uG8].mp4</t>
         </is>
       </c>
-      <c r="E311" s="4" t="inlineStr">
-        <is>
-          <t>21-10-2026 00:35</t>
-        </is>
+      <c r="E311" s="8" t="n">
+        <v>46316.02430555555</v>
       </c>
       <c r="F311" s="5" t="inlineStr">
         <is>
@@ -9928,10 +9351,8 @@
           <t>The moment my house caught fire and everyone helped!🔥 [EUZLRqBmYBk].mp4</t>
         </is>
       </c>
-      <c r="E312" s="4" t="inlineStr">
-        <is>
-          <t>21-10-2026 04:35</t>
-        </is>
+      <c r="E312" s="8" t="n">
+        <v>46316.19097222222</v>
       </c>
       <c r="F312" s="5" t="inlineStr">
         <is>
@@ -9958,10 +9379,8 @@
           <t>The most dangerous job in the world is an operator at the Olympic Games! [JwxfGr7Ab-4].mp4</t>
         </is>
       </c>
-      <c r="E313" s="4" t="inlineStr">
-        <is>
-          <t>21-10-2026 06:35</t>
-        </is>
+      <c r="E313" s="8" t="n">
+        <v>46316.27430555555</v>
       </c>
       <c r="F313" s="5" t="inlineStr">
         <is>
@@ -9988,10 +9407,8 @@
           <t>The most useful thing for your kitchen 🥒❓ [MULE6s7VgVg].mp4</t>
         </is>
       </c>
-      <c r="E314" s="4" t="inlineStr">
-        <is>
-          <t>21-10-2026 17:35</t>
-        </is>
+      <c r="E314" s="8" t="n">
+        <v>46316.73263888889</v>
       </c>
       <c r="F314" s="5" t="inlineStr">
         <is>
@@ -10018,10 +9435,8 @@
           <t>The most useless gadget ever invented 👀❓ [PkTjyLHUFBQ].mp4</t>
         </is>
       </c>
-      <c r="E315" s="4" t="inlineStr">
-        <is>
-          <t>21-10-2026 21:35</t>
-        </is>
+      <c r="E315" s="8" t="n">
+        <v>46316.89930555555</v>
       </c>
       <c r="F315" s="5" t="inlineStr">
         <is>
@@ -10048,10 +9463,8 @@
           <t>The naughty cat who tasted the delicacy 🐱👍 [NkBpTB6DLYQ].mp4</t>
         </is>
       </c>
-      <c r="E316" s="4" t="inlineStr">
-        <is>
-          <t>22-10-2026 00:35</t>
-        </is>
+      <c r="E316" s="8" t="n">
+        <v>46317.02430555555</v>
       </c>
       <c r="F316" s="5" t="inlineStr">
         <is>
@@ -10078,10 +9491,8 @@
           <t>The plot would be incomplete if I didn't add to it 👍❓ [vl7Zq5aSDVo].mp4</t>
         </is>
       </c>
-      <c r="E317" s="4" t="inlineStr">
-        <is>
-          <t>22-10-2026 04:35</t>
-        </is>
+      <c r="E317" s="8" t="n">
+        <v>46317.19097222222</v>
       </c>
       <c r="F317" s="5" t="inlineStr">
         <is>
@@ -10108,10 +9519,8 @@
           <t>The real reason I stopped making friends 🐈❓ [opfPSQvB6uo].mp4</t>
         </is>
       </c>
-      <c r="E318" s="4" t="inlineStr">
-        <is>
-          <t>22-10-2026 06:35</t>
-        </is>
+      <c r="E318" s="8" t="n">
+        <v>46317.27430555555</v>
       </c>
       <c r="F318" s="5" t="inlineStr">
         <is>
@@ -10138,10 +9547,8 @@
           <t>The request to surprise with an exquisite dish from the Chef was quite unexpected😂 [n4ctIs0FvII].mp4</t>
         </is>
       </c>
-      <c r="E319" s="4" t="inlineStr">
-        <is>
-          <t>22-10-2026 17:35</t>
-        </is>
+      <c r="E319" s="8" t="n">
+        <v>46317.73263888889</v>
       </c>
       <c r="F319" s="5" t="inlineStr">
         <is>
@@ -10168,10 +9575,8 @@
           <t>The situation in which a mouse died and then a person 🐭❓ [EWr_ex0R-K0].mp4</t>
         </is>
       </c>
-      <c r="E320" s="4" t="inlineStr">
-        <is>
-          <t>22-10-2026 21:35</t>
-        </is>
+      <c r="E320" s="8" t="n">
+        <v>46317.89930555555</v>
       </c>
       <c r="F320" s="5" t="inlineStr">
         <is>
@@ -10198,10 +9603,8 @@
           <t>The succulent tree to which I am attached [ouj7x34ZQV8].mp4</t>
         </is>
       </c>
-      <c r="E321" s="4" t="inlineStr">
-        <is>
-          <t>23-10-2026 00:35</t>
-        </is>
+      <c r="E321" s="8" t="n">
+        <v>46318.02430555555</v>
       </c>
       <c r="F321" s="5" t="inlineStr">
         <is>
@@ -10228,10 +9631,8 @@
           <t>These AI Italian Creatures Are Maximum Brain Rot 😮👍？ [FeF6SmRF6V0].mp4</t>
         </is>
       </c>
-      <c r="E322" s="4" t="inlineStr">
-        <is>
-          <t>23-10-2026 04:35</t>
-        </is>
+      <c r="E322" s="8" t="n">
+        <v>46318.19097222222</v>
       </c>
       <c r="F322" s="5" t="inlineStr">
         <is>
@@ -10258,10 +9659,8 @@
           <t>These Adorable AI Fruit Animations Are Going CRAZY 🍋 [7Ge1Oz9B3OA].mp4</t>
         </is>
       </c>
-      <c r="E323" s="4" t="inlineStr">
-        <is>
-          <t>23-10-2026 06:35</t>
-        </is>
+      <c r="E323" s="8" t="n">
+        <v>46318.27430555555</v>
       </c>
       <c r="F323" s="5" t="inlineStr">
         <is>
@@ -10288,10 +9687,8 @@
           <t>These Are the Teeth That TikTok Says Suit Me 🫦❓ [IZDNHZItvQE].mp4</t>
         </is>
       </c>
-      <c r="E324" s="4" t="inlineStr">
-        <is>
-          <t>23-10-2026 17:35</t>
-        </is>
+      <c r="E324" s="8" t="n">
+        <v>46318.73263888889</v>
       </c>
       <c r="F324" s="5" t="inlineStr">
         <is>
@@ -10318,10 +9715,8 @@
           <t>They asked to cut down this tree🌳 [w6iwnjbueVU].mp4</t>
         </is>
       </c>
-      <c r="E325" s="4" t="inlineStr">
-        <is>
-          <t>23-10-2026 21:35</t>
-        </is>
+      <c r="E325" s="8" t="n">
+        <v>46318.89930555555</v>
       </c>
       <c r="F325" s="5" t="inlineStr">
         <is>
@@ -10348,10 +9743,8 @@
           <t>They didn't send me a full-size Turtle Cup Holder 🐢❓ [JvmDLLWTtbg].mp4</t>
         </is>
       </c>
-      <c r="E326" s="4" t="inlineStr">
-        <is>
-          <t>24-10-2026 00:35</t>
-        </is>
+      <c r="E326" s="8" t="n">
+        <v>46319.02430555555</v>
       </c>
       <c r="F326" s="5" t="inlineStr">
         <is>
@@ -10378,10 +9771,8 @@
           <t>This AI Video was Easy to Repeat! [bj3-Ys0y8aw].mp4</t>
         </is>
       </c>
-      <c r="E327" s="4" t="inlineStr">
-        <is>
-          <t>24-10-2026 04:35</t>
-        </is>
+      <c r="E327" s="8" t="n">
+        <v>46319.19097222222</v>
       </c>
       <c r="F327" s="5" t="inlineStr">
         <is>
@@ -10408,10 +9799,8 @@
           <t>This AI fail trend is actually insane 💀👍？ [x3YLGmhp6-k].mp4</t>
         </is>
       </c>
-      <c r="E328" s="4" t="inlineStr">
-        <is>
-          <t>24-10-2026 06:35</t>
-        </is>
+      <c r="E328" s="8" t="n">
+        <v>46319.27430555555</v>
       </c>
       <c r="F328" s="5" t="inlineStr">
         <is>
@@ -10438,10 +9827,8 @@
           <t>This AI video is absolutely hilarious 😂👍 [vU7j6SMVmFk].mp4</t>
         </is>
       </c>
-      <c r="E329" s="4" t="inlineStr">
-        <is>
-          <t>24-10-2026 17:35</t>
-        </is>
+      <c r="E329" s="8" t="n">
+        <v>46319.73263888889</v>
       </c>
       <c r="F329" s="5" t="inlineStr">
         <is>
@@ -10468,10 +9855,8 @@
           <t>This Apple Peeler is Actually Useless 💀❓ [zEKGNsQCJ3Q].mp4</t>
         </is>
       </c>
-      <c r="E330" s="4" t="inlineStr">
-        <is>
-          <t>24-10-2026 21:35</t>
-        </is>
+      <c r="E330" s="8" t="n">
+        <v>46319.89930555555</v>
       </c>
       <c r="F330" s="5" t="inlineStr">
         <is>
@@ -10498,10 +9883,8 @@
           <t>This Attraction Was Not Friendly 🎢❓ [b6gKRxyoXXQ].mp4</t>
         </is>
       </c>
-      <c r="E331" s="4" t="inlineStr">
-        <is>
-          <t>25-10-2026 00:35</t>
-        </is>
+      <c r="E331" s="8" t="n">
+        <v>46320.02430555555</v>
       </c>
       <c r="F331" s="5" t="inlineStr">
         <is>
@@ -10528,10 +9911,8 @@
           <t>a trend that turned into madness 🍍❓ [W4M6C7HZ78Y].mp4</t>
         </is>
       </c>
-      <c r="E332" s="4" t="inlineStr">
-        <is>
-          <t>25-10-2026 04:35</t>
-        </is>
+      <c r="E332" s="8" t="n">
+        <v>46320.19097222222</v>
       </c>
       <c r="F332" s="5" t="inlineStr">
         <is>
@@ -10558,10 +9939,8 @@
           <t>automatic pear peeler 🍐❓ [HWC_FKX8kwM].mp4</t>
         </is>
       </c>
-      <c r="E333" s="4" t="inlineStr">
-        <is>
-          <t>25-10-2026 06:35</t>
-        </is>
+      <c r="E333" s="8" t="n">
+        <v>46320.27430555555</v>
       </c>
       <c r="F333" s="5" t="inlineStr">
         <is>
@@ -10588,10 +9967,8 @@
           <t>blah blah blah 🤙❓ [kqymmLGsPow].mp4</t>
         </is>
       </c>
-      <c r="E334" s="4" t="inlineStr">
-        <is>
-          <t>25-10-2026 17:35</t>
-        </is>
+      <c r="E334" s="8" t="n">
+        <v>46320.73263888889</v>
       </c>
       <c r="F334" s="5" t="inlineStr">
         <is>
@@ -10618,10 +9995,8 @@
           <t>iPhone 15 Cleaning Online 📱asmr❓ [sYW7kLlwBTc].mp4</t>
         </is>
       </c>
-      <c r="E335" s="4" t="inlineStr">
-        <is>
-          <t>25-10-2026 21:35</t>
-        </is>
+      <c r="E335" s="8" t="n">
+        <v>46320.89930555555</v>
       </c>
       <c r="F335" s="5" t="inlineStr">
         <is>
@@ -10648,10 +10023,8 @@
           <t>it happens to you too when you go to the wrong website 🫨 [zbSPeBLPrhg].mp4</t>
         </is>
       </c>
-      <c r="E336" s="4" t="inlineStr">
-        <is>
-          <t>26-10-2026 00:35</t>
-        </is>
+      <c r="E336" s="8" t="n">
+        <v>46321.02430555555</v>
       </c>
       <c r="F336" s="5" t="inlineStr">
         <is>
@@ -10678,10 +10051,8 @@
           <t>labubu is needed to shoot trends with her, and here's the best one 🐰❓ [UZumiyBdFQk].mp4</t>
         </is>
       </c>
-      <c r="E337" s="4" t="inlineStr">
-        <is>
-          <t>26-10-2026 04:35</t>
-        </is>
+      <c r="E337" s="8" t="n">
+        <v>46321.19097222222</v>
       </c>
       <c r="F337" s="5" t="inlineStr">
         <is>
@@ -10708,10 +10079,8 @@
           <t>solved the easiest puzzle in the world 🧠 [iZQsf0kCSeE].mp4</t>
         </is>
       </c>
-      <c r="E338" s="4" t="inlineStr">
-        <is>
-          <t>26-10-2026 06:35</t>
-        </is>
+      <c r="E338" s="8" t="n">
+        <v>46321.27430555555</v>
       </c>
       <c r="F338" s="5" t="inlineStr">
         <is>
@@ -10738,10 +10107,8 @@
           <t>spongebob Vulgar Sponge [60w56CMy_6g].mp4</t>
         </is>
       </c>
-      <c r="E339" s="4" t="inlineStr">
-        <is>
-          <t>26-10-2026 17:35</t>
-        </is>
+      <c r="E339" s="8" t="n">
+        <v>46321.73263888889</v>
       </c>
       <c r="F339" s="5" t="inlineStr">
         <is>
@@ -10768,10 +10135,8 @@
           <t>sunk to the bottom of the ocean because of SpongeBob 🧽❓ [GiDFvjzNWsw].mp4</t>
         </is>
       </c>
-      <c r="E340" s="4" t="inlineStr">
-        <is>
-          <t>26-10-2026 21:35</t>
-        </is>
+      <c r="E340" s="8" t="n">
+        <v>46321.89930555555</v>
       </c>
       <c r="F340" s="5" t="inlineStr">
         <is>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\All Auto Post\LoL - Prerona\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B5897797-7CD9-43A2-BCC9-DF4276390BB8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E9F93E50-0CC0-48AA-927F-0437B82F7533}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1169,7 +1169,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="dd\-mm\-yyyy\ hh:mm"/>
   </numFmts>
-  <fonts count="7" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1205,14 +1205,8 @@
       <color rgb="FF155724"/>
       <name val="Arial"/>
     </font>
-    <font>
-      <b/>
-      <sz val="10"/>
-      <color rgb="FF8A5300"/>
-      <name val="Arial"/>
-    </font>
   </fonts>
-  <fills count="8">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1244,11 +1238,6 @@
         <fgColor rgb="FFD4EDDA"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFE5B4"/>
-      </patternFill>
-    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -1277,7 +1266,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1301,9 +1290,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="2" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1796,531 +1782,531 @@
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7" s="3">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="B7" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="C7" t="s">
         <v>9</v>
       </c>
       <c r="D7" t="s">
-        <v>20</v>
-      </c>
-      <c r="E7" s="8">
-        <v>46326.190972222219</v>
-      </c>
-      <c r="F7" s="9" t="s">
-        <v>47</v>
+        <v>26</v>
+      </c>
+      <c r="E7" s="4">
+        <v>46256.274305555547</v>
+      </c>
+      <c r="F7" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="G7" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8" s="3">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="B8" t="s">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="C8" t="s">
         <v>9</v>
       </c>
       <c r="D8" t="s">
-        <v>21</v>
-      </c>
-      <c r="E8" s="8">
-        <v>46326.274305555555</v>
-      </c>
-      <c r="F8" s="9" t="s">
-        <v>47</v>
+        <v>30</v>
+      </c>
+      <c r="E8" s="4">
+        <v>46257.024305555547</v>
+      </c>
+      <c r="F8" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="G8" t="s">
+        <v>31</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A9" s="3">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="B9" t="s">
-        <v>22</v>
+        <v>35</v>
       </c>
       <c r="C9" t="s">
         <v>9</v>
       </c>
       <c r="D9" t="s">
-        <v>22</v>
-      </c>
-      <c r="E9" s="8">
-        <v>46326.732638888891</v>
-      </c>
-      <c r="F9" s="9" t="s">
-        <v>47</v>
+        <v>35</v>
+      </c>
+      <c r="E9" s="4">
+        <v>46257.899305555547</v>
+      </c>
+      <c r="F9" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="G9" t="s">
+        <v>36</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A10" s="3">
-        <v>9</v>
+        <v>22</v>
       </c>
       <c r="B10" t="s">
-        <v>23</v>
+        <v>39</v>
       </c>
       <c r="C10" t="s">
         <v>9</v>
       </c>
       <c r="D10" t="s">
-        <v>23</v>
-      </c>
-      <c r="E10" s="8">
-        <v>46326.899305555555</v>
-      </c>
-      <c r="F10" s="9" t="s">
-        <v>47</v>
+        <v>39</v>
+      </c>
+      <c r="E10" s="4">
+        <v>46258.274305555547</v>
+      </c>
+      <c r="F10" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="G10" t="s">
+        <v>40</v>
       </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A11" s="3">
-        <v>10</v>
+        <v>28</v>
       </c>
       <c r="B11" t="s">
-        <v>24</v>
+        <v>46</v>
       </c>
       <c r="C11" t="s">
         <v>9</v>
       </c>
       <c r="D11" t="s">
-        <v>24</v>
+        <v>46</v>
       </c>
       <c r="E11" s="8">
-        <v>46327.024305555555</v>
-      </c>
-      <c r="F11" s="9" t="s">
+        <v>46259.732638888891</v>
+      </c>
+      <c r="F11" s="5" t="s">
         <v>47</v>
       </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A12" s="3">
-        <v>11</v>
+        <v>29</v>
       </c>
       <c r="B12" t="s">
-        <v>25</v>
+        <v>48</v>
       </c>
       <c r="C12" t="s">
         <v>9</v>
       </c>
       <c r="D12" t="s">
-        <v>25</v>
+        <v>48</v>
       </c>
       <c r="E12" s="8">
-        <v>46327.190972222219</v>
-      </c>
-      <c r="F12" s="9" t="s">
+        <v>46259.899305555547</v>
+      </c>
+      <c r="F12" s="5" t="s">
         <v>47</v>
       </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A13" s="3">
-        <v>12</v>
+        <v>30</v>
       </c>
       <c r="B13" t="s">
-        <v>26</v>
+        <v>49</v>
       </c>
       <c r="C13" t="s">
         <v>9</v>
       </c>
       <c r="D13" t="s">
-        <v>26</v>
-      </c>
-      <c r="E13" s="4">
-        <v>46256.274305555547</v>
-      </c>
-      <c r="F13" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="G13" t="s">
-        <v>27</v>
+        <v>49</v>
+      </c>
+      <c r="E13" s="8">
+        <v>46260.024305555547</v>
+      </c>
+      <c r="F13" s="5" t="s">
+        <v>47</v>
       </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A14" s="3">
-        <v>13</v>
+        <v>31</v>
       </c>
       <c r="B14" t="s">
-        <v>28</v>
+        <v>50</v>
       </c>
       <c r="C14" t="s">
         <v>9</v>
       </c>
       <c r="D14" t="s">
-        <v>28</v>
+        <v>50</v>
       </c>
       <c r="E14" s="8">
-        <v>46327.274305555555</v>
-      </c>
-      <c r="F14" s="9" t="s">
+        <v>46260.190972222219</v>
+      </c>
+      <c r="F14" s="5" t="s">
         <v>47</v>
       </c>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A15" s="3">
-        <v>14</v>
+        <v>32</v>
       </c>
       <c r="B15" t="s">
-        <v>29</v>
+        <v>51</v>
       </c>
       <c r="C15" t="s">
         <v>9</v>
       </c>
       <c r="D15" t="s">
-        <v>29</v>
+        <v>51</v>
       </c>
       <c r="E15" s="8">
-        <v>46327.732638888891</v>
-      </c>
-      <c r="F15" s="9" t="s">
+        <v>46260.274305555547</v>
+      </c>
+      <c r="F15" s="5" t="s">
         <v>47</v>
       </c>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A16" s="3">
-        <v>15</v>
+        <v>33</v>
       </c>
       <c r="B16" t="s">
-        <v>30</v>
+        <v>52</v>
       </c>
       <c r="C16" t="s">
         <v>9</v>
       </c>
       <c r="D16" t="s">
-        <v>30</v>
-      </c>
-      <c r="E16" s="4">
-        <v>46257.024305555547</v>
-      </c>
-      <c r="F16" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="G16" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
+        <v>52</v>
+      </c>
+      <c r="E16" s="8">
+        <v>46260.732638888891</v>
+      </c>
+      <c r="F16" s="5" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="3">
-        <v>16</v>
+        <v>34</v>
       </c>
       <c r="B17" t="s">
-        <v>32</v>
+        <v>53</v>
       </c>
       <c r="C17" t="s">
         <v>9</v>
       </c>
       <c r="D17" t="s">
-        <v>32</v>
+        <v>53</v>
       </c>
       <c r="E17" s="8">
-        <v>46327.899305555555</v>
-      </c>
-      <c r="F17" s="9" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
+        <v>46260.899305555547</v>
+      </c>
+      <c r="F17" s="5" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" s="3">
-        <v>17</v>
+        <v>35</v>
       </c>
       <c r="B18" t="s">
-        <v>33</v>
+        <v>54</v>
       </c>
       <c r="C18" t="s">
         <v>9</v>
       </c>
       <c r="D18" t="s">
-        <v>33</v>
+        <v>54</v>
       </c>
       <c r="E18" s="8">
-        <v>46328.024305555555</v>
-      </c>
-      <c r="F18" s="9" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
+        <v>46261.024305555547</v>
+      </c>
+      <c r="F18" s="5" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="3">
-        <v>18</v>
+        <v>36</v>
       </c>
       <c r="B19" t="s">
-        <v>34</v>
+        <v>55</v>
       </c>
       <c r="C19" t="s">
         <v>9</v>
       </c>
       <c r="D19" t="s">
-        <v>34</v>
+        <v>55</v>
       </c>
       <c r="E19" s="8">
-        <v>46328.190972222219</v>
-      </c>
-      <c r="F19" s="9" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
+        <v>46261.190972222219</v>
+      </c>
+      <c r="F19" s="5" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" s="3">
-        <v>19</v>
+        <v>37</v>
       </c>
       <c r="B20" t="s">
-        <v>35</v>
+        <v>56</v>
       </c>
       <c r="C20" t="s">
         <v>9</v>
       </c>
       <c r="D20" t="s">
-        <v>35</v>
-      </c>
-      <c r="E20" s="4">
-        <v>46257.899305555547</v>
-      </c>
-      <c r="F20" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="G20" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
+        <v>56</v>
+      </c>
+      <c r="E20" s="8">
+        <v>46261.274305555547</v>
+      </c>
+      <c r="F20" s="5" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" s="3">
-        <v>20</v>
+        <v>38</v>
       </c>
       <c r="B21" t="s">
-        <v>37</v>
+        <v>57</v>
       </c>
       <c r="C21" t="s">
         <v>9</v>
       </c>
       <c r="D21" t="s">
-        <v>37</v>
+        <v>57</v>
       </c>
       <c r="E21" s="8">
-        <v>46328.274305555555</v>
-      </c>
-      <c r="F21" s="9" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
+        <v>46261.732638888891</v>
+      </c>
+      <c r="F21" s="5" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" s="3">
-        <v>21</v>
+        <v>39</v>
       </c>
       <c r="B22" t="s">
-        <v>38</v>
+        <v>58</v>
       </c>
       <c r="C22" t="s">
         <v>9</v>
       </c>
       <c r="D22" t="s">
-        <v>38</v>
+        <v>58</v>
       </c>
       <c r="E22" s="8">
-        <v>46328.732638888891</v>
-      </c>
-      <c r="F22" s="9" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
+        <v>46261.899305555547</v>
+      </c>
+      <c r="F22" s="5" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" s="3">
-        <v>22</v>
+        <v>40</v>
       </c>
       <c r="B23" t="s">
-        <v>39</v>
+        <v>59</v>
       </c>
       <c r="C23" t="s">
         <v>9</v>
       </c>
       <c r="D23" t="s">
-        <v>39</v>
-      </c>
-      <c r="E23" s="4">
-        <v>46258.274305555547</v>
-      </c>
-      <c r="F23" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="G23" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
+        <v>59</v>
+      </c>
+      <c r="E23" s="8">
+        <v>46262.024305555547</v>
+      </c>
+      <c r="F23" s="5" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" s="3">
-        <v>23</v>
+        <v>41</v>
       </c>
       <c r="B24" t="s">
-        <v>41</v>
+        <v>60</v>
       </c>
       <c r="C24" t="s">
         <v>9</v>
       </c>
       <c r="D24" t="s">
-        <v>41</v>
+        <v>60</v>
       </c>
       <c r="E24" s="8">
-        <v>46328.899305555555</v>
-      </c>
-      <c r="F24" s="9" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
+        <v>46262.190972222219</v>
+      </c>
+      <c r="F24" s="5" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" s="3">
-        <v>24</v>
+        <v>42</v>
       </c>
       <c r="B25" t="s">
-        <v>42</v>
+        <v>61</v>
       </c>
       <c r="C25" t="s">
         <v>9</v>
       </c>
       <c r="D25" t="s">
-        <v>42</v>
+        <v>61</v>
       </c>
       <c r="E25" s="8">
-        <v>46329.024305555555</v>
-      </c>
-      <c r="F25" s="9" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.25">
+        <v>46262.274305555547</v>
+      </c>
+      <c r="F25" s="5" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26" s="3">
-        <v>25</v>
+        <v>43</v>
       </c>
       <c r="B26" t="s">
-        <v>43</v>
+        <v>62</v>
       </c>
       <c r="C26" t="s">
         <v>9</v>
       </c>
       <c r="D26" t="s">
-        <v>43</v>
+        <v>62</v>
       </c>
       <c r="E26" s="8">
-        <v>46329.190972222219</v>
-      </c>
-      <c r="F26" s="9" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.25">
+        <v>46262.732638888891</v>
+      </c>
+      <c r="F26" s="5" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27" s="3">
-        <v>26</v>
+        <v>44</v>
       </c>
       <c r="B27" t="s">
-        <v>44</v>
+        <v>63</v>
       </c>
       <c r="C27" t="s">
         <v>9</v>
       </c>
       <c r="D27" t="s">
-        <v>44</v>
+        <v>63</v>
       </c>
       <c r="E27" s="8">
-        <v>46329.274305555555</v>
-      </c>
-      <c r="F27" s="9" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.25">
+        <v>46262.899305555547</v>
+      </c>
+      <c r="F27" s="5" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A28" s="3">
-        <v>27</v>
+        <v>45</v>
       </c>
       <c r="B28" t="s">
-        <v>45</v>
+        <v>64</v>
       </c>
       <c r="C28" t="s">
         <v>9</v>
       </c>
       <c r="D28" t="s">
-        <v>45</v>
+        <v>64</v>
       </c>
       <c r="E28" s="8">
-        <v>46351.542361111111</v>
-      </c>
-      <c r="F28" s="9" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.25">
+        <v>46263.024305555547</v>
+      </c>
+      <c r="F28" s="5" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A29" s="3">
-        <v>28</v>
+        <v>46</v>
       </c>
       <c r="B29" t="s">
-        <v>46</v>
+        <v>65</v>
       </c>
       <c r="C29" t="s">
         <v>9</v>
       </c>
       <c r="D29" t="s">
-        <v>46</v>
+        <v>65</v>
       </c>
       <c r="E29" s="8">
-        <v>46259.732638888891</v>
+        <v>46263.190972222219</v>
       </c>
       <c r="F29" s="5" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A30" s="3">
-        <v>29</v>
+        <v>47</v>
       </c>
       <c r="B30" t="s">
+        <v>66</v>
+      </c>
+      <c r="C30" t="s">
+        <v>9</v>
+      </c>
+      <c r="D30" t="s">
+        <v>66</v>
+      </c>
+      <c r="E30" s="8">
+        <v>46263.274305555547</v>
+      </c>
+      <c r="F30" s="5" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A31" s="3">
         <v>48</v>
       </c>
-      <c r="C30" t="s">
-        <v>9</v>
-      </c>
-      <c r="D30" t="s">
-        <v>48</v>
-      </c>
-      <c r="E30" s="8">
-        <v>46259.899305555547</v>
-      </c>
-      <c r="F30" s="5" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A31" s="3">
-        <v>30</v>
-      </c>
       <c r="B31" t="s">
+        <v>67</v>
+      </c>
+      <c r="C31" t="s">
+        <v>9</v>
+      </c>
+      <c r="D31" t="s">
+        <v>67</v>
+      </c>
+      <c r="E31" s="8">
+        <v>46263.732638888891</v>
+      </c>
+      <c r="F31" s="5" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A32" s="3">
         <v>49</v>
       </c>
-      <c r="C31" t="s">
-        <v>9</v>
-      </c>
-      <c r="D31" t="s">
-        <v>49</v>
-      </c>
-      <c r="E31" s="8">
-        <v>46260.024305555547</v>
-      </c>
-      <c r="F31" s="5" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A32" s="3">
-        <v>31</v>
-      </c>
       <c r="B32" t="s">
-        <v>50</v>
+        <v>68</v>
       </c>
       <c r="C32" t="s">
         <v>9</v>
       </c>
       <c r="D32" t="s">
-        <v>50</v>
+        <v>68</v>
       </c>
       <c r="E32" s="8">
-        <v>46260.190972222219</v>
+        <v>46263.899305555547</v>
       </c>
       <c r="F32" s="5" t="s">
         <v>47</v>
@@ -2328,19 +2314,19 @@
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A33" s="3">
-        <v>32</v>
+        <v>50</v>
       </c>
       <c r="B33" t="s">
-        <v>51</v>
+        <v>69</v>
       </c>
       <c r="C33" t="s">
         <v>9</v>
       </c>
       <c r="D33" t="s">
-        <v>51</v>
+        <v>69</v>
       </c>
       <c r="E33" s="8">
-        <v>46260.274305555547</v>
+        <v>46264.024305555547</v>
       </c>
       <c r="F33" s="5" t="s">
         <v>47</v>
@@ -2348,19 +2334,19 @@
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A34" s="3">
-        <v>33</v>
+        <v>51</v>
       </c>
       <c r="B34" t="s">
-        <v>52</v>
+        <v>70</v>
       </c>
       <c r="C34" t="s">
         <v>9</v>
       </c>
       <c r="D34" t="s">
-        <v>52</v>
+        <v>70</v>
       </c>
       <c r="E34" s="8">
-        <v>46260.732638888891</v>
+        <v>46264.190972222219</v>
       </c>
       <c r="F34" s="5" t="s">
         <v>47</v>
@@ -2368,19 +2354,19 @@
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A35" s="3">
-        <v>34</v>
+        <v>52</v>
       </c>
       <c r="B35" t="s">
-        <v>53</v>
+        <v>71</v>
       </c>
       <c r="C35" t="s">
         <v>9</v>
       </c>
       <c r="D35" t="s">
-        <v>53</v>
+        <v>71</v>
       </c>
       <c r="E35" s="8">
-        <v>46260.899305555547</v>
+        <v>46264.274305555547</v>
       </c>
       <c r="F35" s="5" t="s">
         <v>47</v>
@@ -2388,19 +2374,19 @@
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A36" s="3">
-        <v>35</v>
+        <v>53</v>
       </c>
       <c r="B36" t="s">
-        <v>54</v>
+        <v>72</v>
       </c>
       <c r="C36" t="s">
         <v>9</v>
       </c>
       <c r="D36" t="s">
-        <v>54</v>
+        <v>72</v>
       </c>
       <c r="E36" s="8">
-        <v>46261.024305555547</v>
+        <v>46264.732638888891</v>
       </c>
       <c r="F36" s="5" t="s">
         <v>47</v>
@@ -2408,19 +2394,19 @@
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A37" s="3">
-        <v>36</v>
+        <v>54</v>
       </c>
       <c r="B37" t="s">
-        <v>55</v>
+        <v>73</v>
       </c>
       <c r="C37" t="s">
         <v>9</v>
       </c>
       <c r="D37" t="s">
-        <v>55</v>
+        <v>73</v>
       </c>
       <c r="E37" s="8">
-        <v>46261.190972222219</v>
+        <v>46264.899305555547</v>
       </c>
       <c r="F37" s="5" t="s">
         <v>47</v>
@@ -2428,19 +2414,19 @@
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A38" s="3">
-        <v>37</v>
+        <v>55</v>
       </c>
       <c r="B38" t="s">
-        <v>56</v>
+        <v>74</v>
       </c>
       <c r="C38" t="s">
         <v>9</v>
       </c>
       <c r="D38" t="s">
-        <v>56</v>
+        <v>74</v>
       </c>
       <c r="E38" s="8">
-        <v>46261.274305555547</v>
+        <v>46265.024305555547</v>
       </c>
       <c r="F38" s="5" t="s">
         <v>47</v>
@@ -2448,19 +2434,19 @@
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A39" s="3">
-        <v>38</v>
+        <v>56</v>
       </c>
       <c r="B39" t="s">
-        <v>57</v>
+        <v>75</v>
       </c>
       <c r="C39" t="s">
         <v>9</v>
       </c>
       <c r="D39" t="s">
-        <v>57</v>
+        <v>75</v>
       </c>
       <c r="E39" s="8">
-        <v>46261.732638888891</v>
+        <v>46265.190972222219</v>
       </c>
       <c r="F39" s="5" t="s">
         <v>47</v>
@@ -2468,19 +2454,19 @@
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A40" s="3">
-        <v>39</v>
+        <v>57</v>
       </c>
       <c r="B40" t="s">
-        <v>58</v>
+        <v>76</v>
       </c>
       <c r="C40" t="s">
         <v>9</v>
       </c>
       <c r="D40" t="s">
-        <v>58</v>
+        <v>76</v>
       </c>
       <c r="E40" s="8">
-        <v>46261.899305555547</v>
+        <v>46265.274305555547</v>
       </c>
       <c r="F40" s="5" t="s">
         <v>47</v>
@@ -2488,19 +2474,19 @@
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A41" s="3">
-        <v>40</v>
+        <v>58</v>
       </c>
       <c r="B41" t="s">
-        <v>59</v>
+        <v>77</v>
       </c>
       <c r="C41" t="s">
         <v>9</v>
       </c>
       <c r="D41" t="s">
-        <v>59</v>
+        <v>77</v>
       </c>
       <c r="E41" s="8">
-        <v>46262.024305555547</v>
+        <v>46265.732638888891</v>
       </c>
       <c r="F41" s="5" t="s">
         <v>47</v>
@@ -2508,19 +2494,19 @@
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A42" s="3">
-        <v>41</v>
+        <v>59</v>
       </c>
       <c r="B42" t="s">
-        <v>60</v>
+        <v>78</v>
       </c>
       <c r="C42" t="s">
         <v>9</v>
       </c>
       <c r="D42" t="s">
-        <v>60</v>
+        <v>78</v>
       </c>
       <c r="E42" s="8">
-        <v>46262.190972222219</v>
+        <v>46265.899305555547</v>
       </c>
       <c r="F42" s="5" t="s">
         <v>47</v>
@@ -2528,19 +2514,19 @@
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A43" s="3">
-        <v>42</v>
+        <v>60</v>
       </c>
       <c r="B43" t="s">
-        <v>61</v>
+        <v>79</v>
       </c>
       <c r="C43" t="s">
         <v>9</v>
       </c>
       <c r="D43" t="s">
-        <v>61</v>
+        <v>79</v>
       </c>
       <c r="E43" s="8">
-        <v>46262.274305555547</v>
+        <v>46266.024305555547</v>
       </c>
       <c r="F43" s="5" t="s">
         <v>47</v>
@@ -2548,19 +2534,19 @@
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A44" s="3">
-        <v>43</v>
+        <v>61</v>
       </c>
       <c r="B44" t="s">
-        <v>62</v>
+        <v>80</v>
       </c>
       <c r="C44" t="s">
         <v>9</v>
       </c>
       <c r="D44" t="s">
-        <v>62</v>
+        <v>80</v>
       </c>
       <c r="E44" s="8">
-        <v>46262.732638888891</v>
+        <v>46266.190972222219</v>
       </c>
       <c r="F44" s="5" t="s">
         <v>47</v>
@@ -2568,19 +2554,19 @@
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A45" s="3">
-        <v>44</v>
+        <v>62</v>
       </c>
       <c r="B45" t="s">
-        <v>63</v>
+        <v>81</v>
       </c>
       <c r="C45" t="s">
         <v>9</v>
       </c>
       <c r="D45" t="s">
-        <v>63</v>
+        <v>81</v>
       </c>
       <c r="E45" s="8">
-        <v>46262.899305555547</v>
+        <v>46266.274305555547</v>
       </c>
       <c r="F45" s="5" t="s">
         <v>47</v>
@@ -2588,19 +2574,19 @@
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A46" s="3">
-        <v>45</v>
+        <v>63</v>
       </c>
       <c r="B46" t="s">
-        <v>64</v>
+        <v>82</v>
       </c>
       <c r="C46" t="s">
         <v>9</v>
       </c>
       <c r="D46" t="s">
-        <v>64</v>
+        <v>82</v>
       </c>
       <c r="E46" s="8">
-        <v>46263.024305555547</v>
+        <v>46266.732638888891</v>
       </c>
       <c r="F46" s="5" t="s">
         <v>47</v>
@@ -2608,19 +2594,19 @@
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A47" s="3">
-        <v>46</v>
+        <v>64</v>
       </c>
       <c r="B47" t="s">
-        <v>65</v>
+        <v>83</v>
       </c>
       <c r="C47" t="s">
         <v>9</v>
       </c>
       <c r="D47" t="s">
-        <v>65</v>
+        <v>83</v>
       </c>
       <c r="E47" s="8">
-        <v>46263.190972222219</v>
+        <v>46266.899305555547</v>
       </c>
       <c r="F47" s="5" t="s">
         <v>47</v>
@@ -2628,19 +2614,19 @@
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A48" s="3">
-        <v>47</v>
+        <v>65</v>
       </c>
       <c r="B48" t="s">
-        <v>66</v>
+        <v>84</v>
       </c>
       <c r="C48" t="s">
         <v>9</v>
       </c>
       <c r="D48" t="s">
-        <v>66</v>
+        <v>84</v>
       </c>
       <c r="E48" s="8">
-        <v>46263.274305555547</v>
+        <v>46267.024305555547</v>
       </c>
       <c r="F48" s="5" t="s">
         <v>47</v>
@@ -2648,19 +2634,19 @@
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A49" s="3">
-        <v>48</v>
+        <v>66</v>
       </c>
       <c r="B49" t="s">
-        <v>67</v>
+        <v>85</v>
       </c>
       <c r="C49" t="s">
         <v>9</v>
       </c>
       <c r="D49" t="s">
-        <v>67</v>
+        <v>85</v>
       </c>
       <c r="E49" s="8">
-        <v>46263.732638888891</v>
+        <v>46267.190972222219</v>
       </c>
       <c r="F49" s="5" t="s">
         <v>47</v>
@@ -2668,19 +2654,19 @@
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A50" s="3">
-        <v>49</v>
+        <v>67</v>
       </c>
       <c r="B50" t="s">
-        <v>68</v>
+        <v>86</v>
       </c>
       <c r="C50" t="s">
         <v>9</v>
       </c>
       <c r="D50" t="s">
-        <v>68</v>
+        <v>86</v>
       </c>
       <c r="E50" s="8">
-        <v>46263.899305555547</v>
+        <v>46267.274305555547</v>
       </c>
       <c r="F50" s="5" t="s">
         <v>47</v>
@@ -2688,19 +2674,19 @@
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A51" s="3">
-        <v>50</v>
+        <v>68</v>
       </c>
       <c r="B51" t="s">
-        <v>69</v>
+        <v>87</v>
       </c>
       <c r="C51" t="s">
         <v>9</v>
       </c>
       <c r="D51" t="s">
-        <v>69</v>
+        <v>87</v>
       </c>
       <c r="E51" s="8">
-        <v>46264.024305555547</v>
+        <v>46267.732638888891</v>
       </c>
       <c r="F51" s="5" t="s">
         <v>47</v>
@@ -2708,19 +2694,19 @@
     </row>
     <row r="52" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A52" s="3">
-        <v>51</v>
+        <v>69</v>
       </c>
       <c r="B52" t="s">
-        <v>70</v>
+        <v>88</v>
       </c>
       <c r="C52" t="s">
         <v>9</v>
       </c>
       <c r="D52" t="s">
-        <v>70</v>
+        <v>88</v>
       </c>
       <c r="E52" s="8">
-        <v>46264.190972222219</v>
+        <v>46267.899305555547</v>
       </c>
       <c r="F52" s="5" t="s">
         <v>47</v>
@@ -2728,19 +2714,19 @@
     </row>
     <row r="53" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A53" s="3">
-        <v>52</v>
+        <v>70</v>
       </c>
       <c r="B53" t="s">
-        <v>71</v>
+        <v>89</v>
       </c>
       <c r="C53" t="s">
         <v>9</v>
       </c>
       <c r="D53" t="s">
-        <v>71</v>
+        <v>89</v>
       </c>
       <c r="E53" s="8">
-        <v>46264.274305555547</v>
+        <v>46268.024305555547</v>
       </c>
       <c r="F53" s="5" t="s">
         <v>47</v>
@@ -2748,19 +2734,19 @@
     </row>
     <row r="54" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A54" s="3">
-        <v>53</v>
+        <v>71</v>
       </c>
       <c r="B54" t="s">
-        <v>72</v>
+        <v>90</v>
       </c>
       <c r="C54" t="s">
         <v>9</v>
       </c>
       <c r="D54" t="s">
-        <v>72</v>
+        <v>90</v>
       </c>
       <c r="E54" s="8">
-        <v>46264.732638888891</v>
+        <v>46268.190972222219</v>
       </c>
       <c r="F54" s="5" t="s">
         <v>47</v>
@@ -2768,19 +2754,19 @@
     </row>
     <row r="55" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A55" s="3">
-        <v>54</v>
+        <v>72</v>
       </c>
       <c r="B55" t="s">
-        <v>73</v>
+        <v>91</v>
       </c>
       <c r="C55" t="s">
         <v>9</v>
       </c>
       <c r="D55" t="s">
-        <v>73</v>
+        <v>91</v>
       </c>
       <c r="E55" s="8">
-        <v>46264.899305555547</v>
+        <v>46268.274305555547</v>
       </c>
       <c r="F55" s="5" t="s">
         <v>47</v>
@@ -2788,19 +2774,19 @@
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A56" s="3">
-        <v>55</v>
+        <v>73</v>
       </c>
       <c r="B56" t="s">
-        <v>74</v>
+        <v>92</v>
       </c>
       <c r="C56" t="s">
         <v>9</v>
       </c>
       <c r="D56" t="s">
-        <v>74</v>
+        <v>92</v>
       </c>
       <c r="E56" s="8">
-        <v>46265.024305555547</v>
+        <v>46268.732638888891</v>
       </c>
       <c r="F56" s="5" t="s">
         <v>47</v>
@@ -2808,19 +2794,19 @@
     </row>
     <row r="57" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A57" s="3">
-        <v>56</v>
+        <v>74</v>
       </c>
       <c r="B57" t="s">
-        <v>75</v>
+        <v>93</v>
       </c>
       <c r="C57" t="s">
         <v>9</v>
       </c>
       <c r="D57" t="s">
-        <v>75</v>
+        <v>93</v>
       </c>
       <c r="E57" s="8">
-        <v>46265.190972222219</v>
+        <v>46268.899305555547</v>
       </c>
       <c r="F57" s="5" t="s">
         <v>47</v>
@@ -2828,19 +2814,19 @@
     </row>
     <row r="58" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A58" s="3">
-        <v>57</v>
+        <v>75</v>
       </c>
       <c r="B58" t="s">
-        <v>76</v>
+        <v>94</v>
       </c>
       <c r="C58" t="s">
         <v>9</v>
       </c>
       <c r="D58" t="s">
-        <v>76</v>
+        <v>94</v>
       </c>
       <c r="E58" s="8">
-        <v>46265.274305555547</v>
+        <v>46269.024305555547</v>
       </c>
       <c r="F58" s="5" t="s">
         <v>47</v>
@@ -2848,19 +2834,19 @@
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A59" s="3">
-        <v>58</v>
+        <v>76</v>
       </c>
       <c r="B59" t="s">
-        <v>77</v>
+        <v>95</v>
       </c>
       <c r="C59" t="s">
         <v>9</v>
       </c>
       <c r="D59" t="s">
-        <v>77</v>
+        <v>95</v>
       </c>
       <c r="E59" s="8">
-        <v>46265.732638888891</v>
+        <v>46269.190972222219</v>
       </c>
       <c r="F59" s="5" t="s">
         <v>47</v>
@@ -2868,19 +2854,19 @@
     </row>
     <row r="60" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A60" s="3">
-        <v>59</v>
+        <v>77</v>
       </c>
       <c r="B60" t="s">
-        <v>78</v>
+        <v>96</v>
       </c>
       <c r="C60" t="s">
         <v>9</v>
       </c>
       <c r="D60" t="s">
-        <v>78</v>
+        <v>96</v>
       </c>
       <c r="E60" s="8">
-        <v>46265.899305555547</v>
+        <v>46269.274305555547</v>
       </c>
       <c r="F60" s="5" t="s">
         <v>47</v>
@@ -2888,19 +2874,19 @@
     </row>
     <row r="61" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A61" s="3">
-        <v>60</v>
+        <v>78</v>
       </c>
       <c r="B61" t="s">
-        <v>79</v>
+        <v>97</v>
       </c>
       <c r="C61" t="s">
         <v>9</v>
       </c>
       <c r="D61" t="s">
-        <v>79</v>
+        <v>97</v>
       </c>
       <c r="E61" s="8">
-        <v>46266.024305555547</v>
+        <v>46269.732638888891</v>
       </c>
       <c r="F61" s="5" t="s">
         <v>47</v>
@@ -2908,19 +2894,19 @@
     </row>
     <row r="62" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A62" s="3">
-        <v>61</v>
+        <v>79</v>
       </c>
       <c r="B62" t="s">
-        <v>80</v>
+        <v>98</v>
       </c>
       <c r="C62" t="s">
         <v>9</v>
       </c>
       <c r="D62" t="s">
-        <v>80</v>
+        <v>98</v>
       </c>
       <c r="E62" s="8">
-        <v>46266.190972222219</v>
+        <v>46269.899305555547</v>
       </c>
       <c r="F62" s="5" t="s">
         <v>47</v>
@@ -2928,19 +2914,19 @@
     </row>
     <row r="63" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A63" s="3">
-        <v>62</v>
+        <v>80</v>
       </c>
       <c r="B63" t="s">
-        <v>81</v>
+        <v>99</v>
       </c>
       <c r="C63" t="s">
         <v>9</v>
       </c>
       <c r="D63" t="s">
-        <v>81</v>
+        <v>99</v>
       </c>
       <c r="E63" s="8">
-        <v>46266.274305555547</v>
+        <v>46270.024305555547</v>
       </c>
       <c r="F63" s="5" t="s">
         <v>47</v>
@@ -2948,19 +2934,19 @@
     </row>
     <row r="64" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A64" s="3">
-        <v>63</v>
+        <v>81</v>
       </c>
       <c r="B64" t="s">
-        <v>82</v>
+        <v>100</v>
       </c>
       <c r="C64" t="s">
         <v>9</v>
       </c>
       <c r="D64" t="s">
-        <v>82</v>
+        <v>100</v>
       </c>
       <c r="E64" s="8">
-        <v>46266.732638888891</v>
+        <v>46270.190972222219</v>
       </c>
       <c r="F64" s="5" t="s">
         <v>47</v>
@@ -2968,19 +2954,19 @@
     </row>
     <row r="65" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A65" s="3">
-        <v>64</v>
+        <v>82</v>
       </c>
       <c r="B65" t="s">
-        <v>83</v>
+        <v>101</v>
       </c>
       <c r="C65" t="s">
         <v>9</v>
       </c>
       <c r="D65" t="s">
-        <v>83</v>
+        <v>101</v>
       </c>
       <c r="E65" s="8">
-        <v>46266.899305555547</v>
+        <v>46270.274305555547</v>
       </c>
       <c r="F65" s="5" t="s">
         <v>47</v>
@@ -2988,19 +2974,19 @@
     </row>
     <row r="66" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A66" s="3">
-        <v>65</v>
+        <v>83</v>
       </c>
       <c r="B66" t="s">
-        <v>84</v>
+        <v>102</v>
       </c>
       <c r="C66" t="s">
         <v>9</v>
       </c>
       <c r="D66" t="s">
-        <v>84</v>
+        <v>102</v>
       </c>
       <c r="E66" s="8">
-        <v>46267.024305555547</v>
+        <v>46270.732638888891</v>
       </c>
       <c r="F66" s="5" t="s">
         <v>47</v>
@@ -3008,19 +2994,19 @@
     </row>
     <row r="67" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A67" s="3">
-        <v>66</v>
+        <v>84</v>
       </c>
       <c r="B67" t="s">
-        <v>85</v>
+        <v>103</v>
       </c>
       <c r="C67" t="s">
         <v>9</v>
       </c>
       <c r="D67" t="s">
-        <v>85</v>
+        <v>103</v>
       </c>
       <c r="E67" s="8">
-        <v>46267.190972222219</v>
+        <v>46270.899305555547</v>
       </c>
       <c r="F67" s="5" t="s">
         <v>47</v>
@@ -3028,19 +3014,19 @@
     </row>
     <row r="68" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A68" s="3">
-        <v>67</v>
+        <v>85</v>
       </c>
       <c r="B68" t="s">
-        <v>86</v>
+        <v>104</v>
       </c>
       <c r="C68" t="s">
         <v>9</v>
       </c>
       <c r="D68" t="s">
-        <v>86</v>
+        <v>104</v>
       </c>
       <c r="E68" s="8">
-        <v>46267.274305555547</v>
+        <v>46271.024305555547</v>
       </c>
       <c r="F68" s="5" t="s">
         <v>47</v>
@@ -3048,19 +3034,19 @@
     </row>
     <row r="69" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A69" s="3">
-        <v>68</v>
+        <v>86</v>
       </c>
       <c r="B69" t="s">
-        <v>87</v>
+        <v>105</v>
       </c>
       <c r="C69" t="s">
         <v>9</v>
       </c>
       <c r="D69" t="s">
-        <v>87</v>
+        <v>105</v>
       </c>
       <c r="E69" s="8">
-        <v>46267.732638888891</v>
+        <v>46271.190972222219</v>
       </c>
       <c r="F69" s="5" t="s">
         <v>47</v>
@@ -3068,19 +3054,19 @@
     </row>
     <row r="70" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A70" s="3">
-        <v>69</v>
+        <v>87</v>
       </c>
       <c r="B70" t="s">
-        <v>88</v>
+        <v>106</v>
       </c>
       <c r="C70" t="s">
         <v>9</v>
       </c>
       <c r="D70" t="s">
-        <v>88</v>
+        <v>106</v>
       </c>
       <c r="E70" s="8">
-        <v>46267.899305555547</v>
+        <v>46271.274305555547</v>
       </c>
       <c r="F70" s="5" t="s">
         <v>47</v>
@@ -3088,19 +3074,19 @@
     </row>
     <row r="71" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A71" s="3">
-        <v>70</v>
+        <v>88</v>
       </c>
       <c r="B71" t="s">
-        <v>89</v>
+        <v>107</v>
       </c>
       <c r="C71" t="s">
         <v>9</v>
       </c>
       <c r="D71" t="s">
-        <v>89</v>
+        <v>107</v>
       </c>
       <c r="E71" s="8">
-        <v>46268.024305555547</v>
+        <v>46271.732638888891</v>
       </c>
       <c r="F71" s="5" t="s">
         <v>47</v>
@@ -3108,19 +3094,19 @@
     </row>
     <row r="72" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A72" s="3">
-        <v>71</v>
+        <v>89</v>
       </c>
       <c r="B72" t="s">
-        <v>90</v>
+        <v>108</v>
       </c>
       <c r="C72" t="s">
         <v>9</v>
       </c>
       <c r="D72" t="s">
-        <v>90</v>
+        <v>108</v>
       </c>
       <c r="E72" s="8">
-        <v>46268.190972222219</v>
+        <v>46271.899305555547</v>
       </c>
       <c r="F72" s="5" t="s">
         <v>47</v>
@@ -3128,19 +3114,19 @@
     </row>
     <row r="73" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A73" s="3">
-        <v>72</v>
+        <v>90</v>
       </c>
       <c r="B73" t="s">
-        <v>91</v>
+        <v>109</v>
       </c>
       <c r="C73" t="s">
         <v>9</v>
       </c>
       <c r="D73" t="s">
-        <v>91</v>
+        <v>109</v>
       </c>
       <c r="E73" s="8">
-        <v>46268.274305555547</v>
+        <v>46272.024305555547</v>
       </c>
       <c r="F73" s="5" t="s">
         <v>47</v>
@@ -3148,19 +3134,19 @@
     </row>
     <row r="74" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A74" s="3">
-        <v>73</v>
+        <v>91</v>
       </c>
       <c r="B74" t="s">
-        <v>92</v>
+        <v>110</v>
       </c>
       <c r="C74" t="s">
         <v>9</v>
       </c>
       <c r="D74" t="s">
-        <v>92</v>
+        <v>110</v>
       </c>
       <c r="E74" s="8">
-        <v>46268.732638888891</v>
+        <v>46272.190972222219</v>
       </c>
       <c r="F74" s="5" t="s">
         <v>47</v>
@@ -3168,19 +3154,19 @@
     </row>
     <row r="75" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A75" s="3">
-        <v>74</v>
+        <v>92</v>
       </c>
       <c r="B75" t="s">
-        <v>93</v>
+        <v>111</v>
       </c>
       <c r="C75" t="s">
         <v>9</v>
       </c>
       <c r="D75" t="s">
-        <v>93</v>
-      </c>
-      <c r="E75" s="8">
-        <v>46268.899305555547</v>
+        <v>111</v>
+      </c>
+      <c r="E75" s="4">
+        <v>46272.274305555547</v>
       </c>
       <c r="F75" s="5" t="s">
         <v>47</v>
@@ -3188,19 +3174,19 @@
     </row>
     <row r="76" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A76" s="3">
-        <v>75</v>
+        <v>93</v>
       </c>
       <c r="B76" t="s">
-        <v>94</v>
+        <v>112</v>
       </c>
       <c r="C76" t="s">
         <v>9</v>
       </c>
       <c r="D76" t="s">
-        <v>94</v>
+        <v>112</v>
       </c>
       <c r="E76" s="8">
-        <v>46269.024305555547</v>
+        <v>46272.732638888891</v>
       </c>
       <c r="F76" s="5" t="s">
         <v>47</v>
@@ -3208,19 +3194,19 @@
     </row>
     <row r="77" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A77" s="3">
-        <v>76</v>
+        <v>94</v>
       </c>
       <c r="B77" t="s">
-        <v>95</v>
+        <v>113</v>
       </c>
       <c r="C77" t="s">
         <v>9</v>
       </c>
       <c r="D77" t="s">
-        <v>95</v>
+        <v>113</v>
       </c>
       <c r="E77" s="8">
-        <v>46269.190972222219</v>
+        <v>46272.899305555547</v>
       </c>
       <c r="F77" s="5" t="s">
         <v>47</v>
@@ -3228,19 +3214,19 @@
     </row>
     <row r="78" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A78" s="3">
-        <v>77</v>
+        <v>95</v>
       </c>
       <c r="B78" t="s">
-        <v>96</v>
+        <v>114</v>
       </c>
       <c r="C78" t="s">
         <v>9</v>
       </c>
       <c r="D78" t="s">
-        <v>96</v>
-      </c>
-      <c r="E78" s="8">
-        <v>46269.274305555547</v>
+        <v>114</v>
+      </c>
+      <c r="E78" s="4">
+        <v>46273.024305555547</v>
       </c>
       <c r="F78" s="5" t="s">
         <v>47</v>
@@ -3248,19 +3234,19 @@
     </row>
     <row r="79" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A79" s="3">
-        <v>78</v>
+        <v>96</v>
       </c>
       <c r="B79" t="s">
-        <v>97</v>
+        <v>115</v>
       </c>
       <c r="C79" t="s">
         <v>9</v>
       </c>
       <c r="D79" t="s">
-        <v>97</v>
+        <v>115</v>
       </c>
       <c r="E79" s="8">
-        <v>46269.732638888891</v>
+        <v>46273.190972222219</v>
       </c>
       <c r="F79" s="5" t="s">
         <v>47</v>
@@ -3268,19 +3254,19 @@
     </row>
     <row r="80" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A80" s="3">
-        <v>79</v>
+        <v>97</v>
       </c>
       <c r="B80" t="s">
-        <v>98</v>
+        <v>116</v>
       </c>
       <c r="C80" t="s">
         <v>9</v>
       </c>
       <c r="D80" t="s">
-        <v>98</v>
+        <v>116</v>
       </c>
       <c r="E80" s="8">
-        <v>46269.899305555547</v>
+        <v>46273.274305555547</v>
       </c>
       <c r="F80" s="5" t="s">
         <v>47</v>
@@ -3288,19 +3274,19 @@
     </row>
     <row r="81" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A81" s="3">
-        <v>80</v>
+        <v>98</v>
       </c>
       <c r="B81" t="s">
-        <v>99</v>
+        <v>117</v>
       </c>
       <c r="C81" t="s">
         <v>9</v>
       </c>
       <c r="D81" t="s">
-        <v>99</v>
+        <v>117</v>
       </c>
       <c r="E81" s="8">
-        <v>46270.024305555547</v>
+        <v>46273.732638888891</v>
       </c>
       <c r="F81" s="5" t="s">
         <v>47</v>
@@ -3308,19 +3294,19 @@
     </row>
     <row r="82" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A82" s="3">
-        <v>81</v>
+        <v>99</v>
       </c>
       <c r="B82" t="s">
-        <v>100</v>
+        <v>118</v>
       </c>
       <c r="C82" t="s">
         <v>9</v>
       </c>
       <c r="D82" t="s">
-        <v>100</v>
+        <v>118</v>
       </c>
       <c r="E82" s="8">
-        <v>46270.190972222219</v>
+        <v>46273.899305555547</v>
       </c>
       <c r="F82" s="5" t="s">
         <v>47</v>
@@ -3328,19 +3314,19 @@
     </row>
     <row r="83" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A83" s="3">
-        <v>82</v>
+        <v>100</v>
       </c>
       <c r="B83" t="s">
-        <v>101</v>
+        <v>119</v>
       </c>
       <c r="C83" t="s">
         <v>9</v>
       </c>
       <c r="D83" t="s">
-        <v>101</v>
+        <v>119</v>
       </c>
       <c r="E83" s="8">
-        <v>46270.274305555547</v>
+        <v>46274.024305555547</v>
       </c>
       <c r="F83" s="5" t="s">
         <v>47</v>
@@ -3348,19 +3334,19 @@
     </row>
     <row r="84" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A84" s="3">
-        <v>83</v>
+        <v>101</v>
       </c>
       <c r="B84" t="s">
-        <v>102</v>
+        <v>120</v>
       </c>
       <c r="C84" t="s">
         <v>9</v>
       </c>
       <c r="D84" t="s">
-        <v>102</v>
+        <v>120</v>
       </c>
       <c r="E84" s="8">
-        <v>46270.732638888891</v>
+        <v>46274.190972222219</v>
       </c>
       <c r="F84" s="5" t="s">
         <v>47</v>
@@ -3368,19 +3354,19 @@
     </row>
     <row r="85" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A85" s="3">
-        <v>84</v>
+        <v>102</v>
       </c>
       <c r="B85" t="s">
-        <v>103</v>
+        <v>121</v>
       </c>
       <c r="C85" t="s">
         <v>9</v>
       </c>
       <c r="D85" t="s">
-        <v>103</v>
+        <v>121</v>
       </c>
       <c r="E85" s="8">
-        <v>46270.899305555547</v>
+        <v>46274.274305555547</v>
       </c>
       <c r="F85" s="5" t="s">
         <v>47</v>
@@ -3388,19 +3374,19 @@
     </row>
     <row r="86" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A86" s="3">
-        <v>85</v>
+        <v>103</v>
       </c>
       <c r="B86" t="s">
-        <v>104</v>
+        <v>122</v>
       </c>
       <c r="C86" t="s">
         <v>9</v>
       </c>
       <c r="D86" t="s">
-        <v>104</v>
+        <v>122</v>
       </c>
       <c r="E86" s="8">
-        <v>46271.024305555547</v>
+        <v>46274.732638888891</v>
       </c>
       <c r="F86" s="5" t="s">
         <v>47</v>
@@ -3408,19 +3394,19 @@
     </row>
     <row r="87" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A87" s="3">
-        <v>86</v>
+        <v>104</v>
       </c>
       <c r="B87" t="s">
-        <v>105</v>
+        <v>123</v>
       </c>
       <c r="C87" t="s">
         <v>9</v>
       </c>
       <c r="D87" t="s">
-        <v>105</v>
+        <v>123</v>
       </c>
       <c r="E87" s="8">
-        <v>46271.190972222219</v>
+        <v>46274.899305555547</v>
       </c>
       <c r="F87" s="5" t="s">
         <v>47</v>
@@ -3428,19 +3414,19 @@
     </row>
     <row r="88" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A88" s="3">
-        <v>87</v>
+        <v>105</v>
       </c>
       <c r="B88" t="s">
-        <v>106</v>
+        <v>124</v>
       </c>
       <c r="C88" t="s">
         <v>9</v>
       </c>
       <c r="D88" t="s">
-        <v>106</v>
+        <v>124</v>
       </c>
       <c r="E88" s="8">
-        <v>46271.274305555547</v>
+        <v>46275.024305555547</v>
       </c>
       <c r="F88" s="5" t="s">
         <v>47</v>
@@ -3448,19 +3434,19 @@
     </row>
     <row r="89" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A89" s="3">
-        <v>88</v>
+        <v>106</v>
       </c>
       <c r="B89" t="s">
-        <v>107</v>
+        <v>125</v>
       </c>
       <c r="C89" t="s">
         <v>9</v>
       </c>
       <c r="D89" t="s">
-        <v>107</v>
+        <v>125</v>
       </c>
       <c r="E89" s="8">
-        <v>46271.732638888891</v>
+        <v>46275.190972222219</v>
       </c>
       <c r="F89" s="5" t="s">
         <v>47</v>
@@ -3468,19 +3454,19 @@
     </row>
     <row r="90" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A90" s="3">
-        <v>89</v>
+        <v>107</v>
       </c>
       <c r="B90" t="s">
-        <v>108</v>
+        <v>126</v>
       </c>
       <c r="C90" t="s">
         <v>9</v>
       </c>
       <c r="D90" t="s">
-        <v>108</v>
+        <v>126</v>
       </c>
       <c r="E90" s="8">
-        <v>46271.899305555547</v>
+        <v>46275.274305555547</v>
       </c>
       <c r="F90" s="5" t="s">
         <v>47</v>
@@ -3488,19 +3474,19 @@
     </row>
     <row r="91" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A91" s="3">
-        <v>90</v>
+        <v>108</v>
       </c>
       <c r="B91" t="s">
-        <v>109</v>
+        <v>127</v>
       </c>
       <c r="C91" t="s">
         <v>9</v>
       </c>
       <c r="D91" t="s">
-        <v>109</v>
+        <v>127</v>
       </c>
       <c r="E91" s="8">
-        <v>46272.024305555547</v>
+        <v>46275.732638888891</v>
       </c>
       <c r="F91" s="5" t="s">
         <v>47</v>
@@ -3508,19 +3494,19 @@
     </row>
     <row r="92" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A92" s="3">
-        <v>91</v>
+        <v>109</v>
       </c>
       <c r="B92" t="s">
-        <v>110</v>
+        <v>128</v>
       </c>
       <c r="C92" t="s">
         <v>9</v>
       </c>
       <c r="D92" t="s">
-        <v>110</v>
+        <v>128</v>
       </c>
       <c r="E92" s="8">
-        <v>46272.190972222219</v>
+        <v>46275.899305555547</v>
       </c>
       <c r="F92" s="5" t="s">
         <v>47</v>
@@ -3528,19 +3514,19 @@
     </row>
     <row r="93" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A93" s="3">
-        <v>92</v>
+        <v>110</v>
       </c>
       <c r="B93" t="s">
-        <v>111</v>
+        <v>129</v>
       </c>
       <c r="C93" t="s">
         <v>9</v>
       </c>
       <c r="D93" t="s">
-        <v>111</v>
-      </c>
-      <c r="E93" s="4">
-        <v>46272.274305555547</v>
+        <v>129</v>
+      </c>
+      <c r="E93" s="8">
+        <v>46276.024305555547</v>
       </c>
       <c r="F93" s="5" t="s">
         <v>47</v>
@@ -3548,19 +3534,19 @@
     </row>
     <row r="94" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A94" s="3">
-        <v>93</v>
+        <v>111</v>
       </c>
       <c r="B94" t="s">
-        <v>112</v>
+        <v>130</v>
       </c>
       <c r="C94" t="s">
         <v>9</v>
       </c>
       <c r="D94" t="s">
-        <v>112</v>
+        <v>130</v>
       </c>
       <c r="E94" s="8">
-        <v>46272.732638888891</v>
+        <v>46276.190972222219</v>
       </c>
       <c r="F94" s="5" t="s">
         <v>47</v>
@@ -3568,19 +3554,19 @@
     </row>
     <row r="95" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A95" s="3">
-        <v>94</v>
+        <v>112</v>
       </c>
       <c r="B95" t="s">
-        <v>113</v>
+        <v>131</v>
       </c>
       <c r="C95" t="s">
         <v>9</v>
       </c>
       <c r="D95" t="s">
-        <v>113</v>
+        <v>131</v>
       </c>
       <c r="E95" s="8">
-        <v>46272.899305555547</v>
+        <v>46276.274305555547</v>
       </c>
       <c r="F95" s="5" t="s">
         <v>47</v>
@@ -3588,19 +3574,19 @@
     </row>
     <row r="96" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A96" s="3">
-        <v>95</v>
+        <v>113</v>
       </c>
       <c r="B96" t="s">
-        <v>114</v>
+        <v>132</v>
       </c>
       <c r="C96" t="s">
         <v>9</v>
       </c>
       <c r="D96" t="s">
-        <v>114</v>
-      </c>
-      <c r="E96" s="4">
-        <v>46273.024305555547</v>
+        <v>132</v>
+      </c>
+      <c r="E96" s="8">
+        <v>46276.732638888891</v>
       </c>
       <c r="F96" s="5" t="s">
         <v>47</v>
@@ -3608,19 +3594,19 @@
     </row>
     <row r="97" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A97" s="3">
-        <v>96</v>
+        <v>114</v>
       </c>
       <c r="B97" t="s">
-        <v>115</v>
+        <v>133</v>
       </c>
       <c r="C97" t="s">
         <v>9</v>
       </c>
       <c r="D97" t="s">
-        <v>115</v>
+        <v>133</v>
       </c>
       <c r="E97" s="8">
-        <v>46273.190972222219</v>
+        <v>46276.899305555547</v>
       </c>
       <c r="F97" s="5" t="s">
         <v>47</v>
@@ -3628,19 +3614,19 @@
     </row>
     <row r="98" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A98" s="3">
-        <v>97</v>
+        <v>115</v>
       </c>
       <c r="B98" t="s">
-        <v>116</v>
+        <v>134</v>
       </c>
       <c r="C98" t="s">
         <v>9</v>
       </c>
       <c r="D98" t="s">
-        <v>116</v>
+        <v>134</v>
       </c>
       <c r="E98" s="8">
-        <v>46273.274305555547</v>
+        <v>46277.024305555547</v>
       </c>
       <c r="F98" s="5" t="s">
         <v>47</v>
@@ -3648,19 +3634,19 @@
     </row>
     <row r="99" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A99" s="3">
-        <v>98</v>
+        <v>116</v>
       </c>
       <c r="B99" t="s">
-        <v>117</v>
+        <v>135</v>
       </c>
       <c r="C99" t="s">
         <v>9</v>
       </c>
       <c r="D99" t="s">
-        <v>117</v>
+        <v>135</v>
       </c>
       <c r="E99" s="8">
-        <v>46273.732638888891</v>
+        <v>46277.190972222219</v>
       </c>
       <c r="F99" s="5" t="s">
         <v>47</v>
@@ -3668,19 +3654,19 @@
     </row>
     <row r="100" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A100" s="3">
-        <v>99</v>
+        <v>117</v>
       </c>
       <c r="B100" t="s">
-        <v>118</v>
+        <v>136</v>
       </c>
       <c r="C100" t="s">
         <v>9</v>
       </c>
       <c r="D100" t="s">
-        <v>118</v>
+        <v>136</v>
       </c>
       <c r="E100" s="8">
-        <v>46273.899305555547</v>
+        <v>46277.274305555547</v>
       </c>
       <c r="F100" s="5" t="s">
         <v>47</v>
@@ -3688,19 +3674,19 @@
     </row>
     <row r="101" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A101" s="3">
-        <v>100</v>
+        <v>118</v>
       </c>
       <c r="B101" t="s">
-        <v>119</v>
+        <v>137</v>
       </c>
       <c r="C101" t="s">
         <v>9</v>
       </c>
       <c r="D101" t="s">
-        <v>119</v>
+        <v>137</v>
       </c>
       <c r="E101" s="8">
-        <v>46274.024305555547</v>
+        <v>46277.732638888891</v>
       </c>
       <c r="F101" s="5" t="s">
         <v>47</v>
@@ -3708,19 +3694,19 @@
     </row>
     <row r="102" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A102" s="3">
-        <v>101</v>
+        <v>119</v>
       </c>
       <c r="B102" t="s">
-        <v>120</v>
+        <v>138</v>
       </c>
       <c r="C102" t="s">
         <v>9</v>
       </c>
       <c r="D102" t="s">
-        <v>120</v>
+        <v>138</v>
       </c>
       <c r="E102" s="8">
-        <v>46274.190972222219</v>
+        <v>46277.899305555547</v>
       </c>
       <c r="F102" s="5" t="s">
         <v>47</v>
@@ -3728,19 +3714,19 @@
     </row>
     <row r="103" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A103" s="3">
-        <v>102</v>
+        <v>120</v>
       </c>
       <c r="B103" t="s">
-        <v>121</v>
+        <v>139</v>
       </c>
       <c r="C103" t="s">
         <v>9</v>
       </c>
       <c r="D103" t="s">
-        <v>121</v>
+        <v>139</v>
       </c>
       <c r="E103" s="8">
-        <v>46274.274305555547</v>
+        <v>46278.024305555547</v>
       </c>
       <c r="F103" s="5" t="s">
         <v>47</v>
@@ -3748,19 +3734,19 @@
     </row>
     <row r="104" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A104" s="3">
-        <v>103</v>
+        <v>121</v>
       </c>
       <c r="B104" t="s">
-        <v>122</v>
+        <v>140</v>
       </c>
       <c r="C104" t="s">
         <v>9</v>
       </c>
       <c r="D104" t="s">
-        <v>122</v>
+        <v>140</v>
       </c>
       <c r="E104" s="8">
-        <v>46274.732638888891</v>
+        <v>46278.190972222219</v>
       </c>
       <c r="F104" s="5" t="s">
         <v>47</v>
@@ -3768,19 +3754,19 @@
     </row>
     <row r="105" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A105" s="3">
-        <v>104</v>
+        <v>122</v>
       </c>
       <c r="B105" t="s">
-        <v>123</v>
+        <v>141</v>
       </c>
       <c r="C105" t="s">
         <v>9</v>
       </c>
       <c r="D105" t="s">
-        <v>123</v>
+        <v>141</v>
       </c>
       <c r="E105" s="8">
-        <v>46274.899305555547</v>
+        <v>46278.274305555547</v>
       </c>
       <c r="F105" s="5" t="s">
         <v>47</v>
@@ -3788,19 +3774,19 @@
     </row>
     <row r="106" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A106" s="3">
-        <v>105</v>
+        <v>123</v>
       </c>
       <c r="B106" t="s">
-        <v>124</v>
+        <v>142</v>
       </c>
       <c r="C106" t="s">
         <v>9</v>
       </c>
       <c r="D106" t="s">
-        <v>124</v>
+        <v>142</v>
       </c>
       <c r="E106" s="8">
-        <v>46275.024305555547</v>
+        <v>46278.732638888891</v>
       </c>
       <c r="F106" s="5" t="s">
         <v>47</v>
@@ -3808,19 +3794,19 @@
     </row>
     <row r="107" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A107" s="3">
-        <v>106</v>
+        <v>124</v>
       </c>
       <c r="B107" t="s">
-        <v>125</v>
+        <v>143</v>
       </c>
       <c r="C107" t="s">
         <v>9</v>
       </c>
       <c r="D107" t="s">
-        <v>125</v>
+        <v>143</v>
       </c>
       <c r="E107" s="8">
-        <v>46275.190972222219</v>
+        <v>46278.899305555547</v>
       </c>
       <c r="F107" s="5" t="s">
         <v>47</v>
@@ -3828,19 +3814,19 @@
     </row>
     <row r="108" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A108" s="3">
-        <v>107</v>
+        <v>125</v>
       </c>
       <c r="B108" t="s">
-        <v>126</v>
+        <v>144</v>
       </c>
       <c r="C108" t="s">
         <v>9</v>
       </c>
       <c r="D108" t="s">
-        <v>126</v>
+        <v>144</v>
       </c>
       <c r="E108" s="8">
-        <v>46275.274305555547</v>
+        <v>46279.024305555547</v>
       </c>
       <c r="F108" s="5" t="s">
         <v>47</v>
@@ -3848,19 +3834,19 @@
     </row>
     <row r="109" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A109" s="3">
-        <v>108</v>
+        <v>126</v>
       </c>
       <c r="B109" t="s">
-        <v>127</v>
+        <v>145</v>
       </c>
       <c r="C109" t="s">
         <v>9</v>
       </c>
       <c r="D109" t="s">
-        <v>127</v>
+        <v>145</v>
       </c>
       <c r="E109" s="8">
-        <v>46275.732638888891</v>
+        <v>46279.190972222219</v>
       </c>
       <c r="F109" s="5" t="s">
         <v>47</v>
@@ -3868,19 +3854,19 @@
     </row>
     <row r="110" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A110" s="3">
-        <v>109</v>
+        <v>127</v>
       </c>
       <c r="B110" t="s">
-        <v>128</v>
+        <v>146</v>
       </c>
       <c r="C110" t="s">
         <v>9</v>
       </c>
       <c r="D110" t="s">
-        <v>128</v>
+        <v>146</v>
       </c>
       <c r="E110" s="8">
-        <v>46275.899305555547</v>
+        <v>46279.274305555547</v>
       </c>
       <c r="F110" s="5" t="s">
         <v>47</v>
@@ -3888,19 +3874,19 @@
     </row>
     <row r="111" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A111" s="3">
-        <v>110</v>
+        <v>128</v>
       </c>
       <c r="B111" t="s">
-        <v>129</v>
+        <v>147</v>
       </c>
       <c r="C111" t="s">
         <v>9</v>
       </c>
       <c r="D111" t="s">
-        <v>129</v>
+        <v>147</v>
       </c>
       <c r="E111" s="8">
-        <v>46276.024305555547</v>
+        <v>46279.732638888891</v>
       </c>
       <c r="F111" s="5" t="s">
         <v>47</v>
@@ -3908,19 +3894,19 @@
     </row>
     <row r="112" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A112" s="3">
-        <v>111</v>
+        <v>129</v>
       </c>
       <c r="B112" t="s">
-        <v>130</v>
+        <v>148</v>
       </c>
       <c r="C112" t="s">
         <v>9</v>
       </c>
       <c r="D112" t="s">
-        <v>130</v>
+        <v>148</v>
       </c>
       <c r="E112" s="8">
-        <v>46276.190972222219</v>
+        <v>46279.899305555547</v>
       </c>
       <c r="F112" s="5" t="s">
         <v>47</v>
@@ -3928,19 +3914,19 @@
     </row>
     <row r="113" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A113" s="3">
-        <v>112</v>
+        <v>130</v>
       </c>
       <c r="B113" t="s">
-        <v>131</v>
+        <v>149</v>
       </c>
       <c r="C113" t="s">
         <v>9</v>
       </c>
       <c r="D113" t="s">
-        <v>131</v>
+        <v>149</v>
       </c>
       <c r="E113" s="8">
-        <v>46276.274305555547</v>
+        <v>46280.024305555547</v>
       </c>
       <c r="F113" s="5" t="s">
         <v>47</v>
@@ -3948,19 +3934,19 @@
     </row>
     <row r="114" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A114" s="3">
-        <v>113</v>
+        <v>131</v>
       </c>
       <c r="B114" t="s">
-        <v>132</v>
+        <v>150</v>
       </c>
       <c r="C114" t="s">
         <v>9</v>
       </c>
       <c r="D114" t="s">
-        <v>132</v>
+        <v>150</v>
       </c>
       <c r="E114" s="8">
-        <v>46276.732638888891</v>
+        <v>46280.190972222219</v>
       </c>
       <c r="F114" s="5" t="s">
         <v>47</v>
@@ -3968,19 +3954,19 @@
     </row>
     <row r="115" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A115" s="3">
-        <v>114</v>
+        <v>132</v>
       </c>
       <c r="B115" t="s">
-        <v>133</v>
+        <v>151</v>
       </c>
       <c r="C115" t="s">
         <v>9</v>
       </c>
       <c r="D115" t="s">
-        <v>133</v>
+        <v>151</v>
       </c>
       <c r="E115" s="8">
-        <v>46276.899305555547</v>
+        <v>46280.274305555547</v>
       </c>
       <c r="F115" s="5" t="s">
         <v>47</v>
@@ -3988,19 +3974,19 @@
     </row>
     <row r="116" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A116" s="3">
-        <v>115</v>
+        <v>133</v>
       </c>
       <c r="B116" t="s">
-        <v>134</v>
+        <v>152</v>
       </c>
       <c r="C116" t="s">
         <v>9</v>
       </c>
       <c r="D116" t="s">
-        <v>134</v>
+        <v>152</v>
       </c>
       <c r="E116" s="8">
-        <v>46277.024305555547</v>
+        <v>46280.732638888891</v>
       </c>
       <c r="F116" s="5" t="s">
         <v>47</v>
@@ -4008,19 +3994,19 @@
     </row>
     <row r="117" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A117" s="3">
-        <v>116</v>
+        <v>134</v>
       </c>
       <c r="B117" t="s">
-        <v>135</v>
+        <v>153</v>
       </c>
       <c r="C117" t="s">
         <v>9</v>
       </c>
       <c r="D117" t="s">
-        <v>135</v>
+        <v>153</v>
       </c>
       <c r="E117" s="8">
-        <v>46277.190972222219</v>
+        <v>46280.899305555547</v>
       </c>
       <c r="F117" s="5" t="s">
         <v>47</v>
@@ -4028,19 +4014,19 @@
     </row>
     <row r="118" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A118" s="3">
-        <v>117</v>
+        <v>135</v>
       </c>
       <c r="B118" t="s">
-        <v>136</v>
+        <v>154</v>
       </c>
       <c r="C118" t="s">
         <v>9</v>
       </c>
       <c r="D118" t="s">
-        <v>136</v>
+        <v>154</v>
       </c>
       <c r="E118" s="8">
-        <v>46277.274305555547</v>
+        <v>46281.024305555547</v>
       </c>
       <c r="F118" s="5" t="s">
         <v>47</v>
@@ -4048,19 +4034,19 @@
     </row>
     <row r="119" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A119" s="3">
-        <v>118</v>
+        <v>136</v>
       </c>
       <c r="B119" t="s">
-        <v>137</v>
+        <v>155</v>
       </c>
       <c r="C119" t="s">
         <v>9</v>
       </c>
       <c r="D119" t="s">
-        <v>137</v>
+        <v>155</v>
       </c>
       <c r="E119" s="8">
-        <v>46277.732638888891</v>
+        <v>46281.190972222219</v>
       </c>
       <c r="F119" s="5" t="s">
         <v>47</v>
@@ -4068,19 +4054,19 @@
     </row>
     <row r="120" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A120" s="3">
-        <v>119</v>
+        <v>137</v>
       </c>
       <c r="B120" t="s">
-        <v>138</v>
+        <v>156</v>
       </c>
       <c r="C120" t="s">
         <v>9</v>
       </c>
       <c r="D120" t="s">
-        <v>138</v>
+        <v>156</v>
       </c>
       <c r="E120" s="8">
-        <v>46277.899305555547</v>
+        <v>46281.274305555547</v>
       </c>
       <c r="F120" s="5" t="s">
         <v>47</v>
@@ -4088,19 +4074,19 @@
     </row>
     <row r="121" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A121" s="3">
-        <v>120</v>
+        <v>138</v>
       </c>
       <c r="B121" t="s">
-        <v>139</v>
+        <v>157</v>
       </c>
       <c r="C121" t="s">
         <v>9</v>
       </c>
       <c r="D121" t="s">
-        <v>139</v>
+        <v>157</v>
       </c>
       <c r="E121" s="8">
-        <v>46278.024305555547</v>
+        <v>46281.732638888891</v>
       </c>
       <c r="F121" s="5" t="s">
         <v>47</v>
@@ -4108,19 +4094,19 @@
     </row>
     <row r="122" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A122" s="3">
-        <v>121</v>
+        <v>139</v>
       </c>
       <c r="B122" t="s">
-        <v>140</v>
+        <v>158</v>
       </c>
       <c r="C122" t="s">
         <v>9</v>
       </c>
       <c r="D122" t="s">
-        <v>140</v>
+        <v>158</v>
       </c>
       <c r="E122" s="8">
-        <v>46278.190972222219</v>
+        <v>46281.899305555547</v>
       </c>
       <c r="F122" s="5" t="s">
         <v>47</v>
@@ -4128,19 +4114,19 @@
     </row>
     <row r="123" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A123" s="3">
-        <v>122</v>
+        <v>140</v>
       </c>
       <c r="B123" t="s">
-        <v>141</v>
+        <v>159</v>
       </c>
       <c r="C123" t="s">
         <v>9</v>
       </c>
       <c r="D123" t="s">
-        <v>141</v>
+        <v>159</v>
       </c>
       <c r="E123" s="8">
-        <v>46278.274305555547</v>
+        <v>46282.024305555547</v>
       </c>
       <c r="F123" s="5" t="s">
         <v>47</v>
@@ -4148,19 +4134,19 @@
     </row>
     <row r="124" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A124" s="3">
-        <v>123</v>
+        <v>141</v>
       </c>
       <c r="B124" t="s">
-        <v>142</v>
+        <v>160</v>
       </c>
       <c r="C124" t="s">
         <v>9</v>
       </c>
       <c r="D124" t="s">
-        <v>142</v>
+        <v>160</v>
       </c>
       <c r="E124" s="8">
-        <v>46278.732638888891</v>
+        <v>46282.190972222219</v>
       </c>
       <c r="F124" s="5" t="s">
         <v>47</v>
@@ -4168,19 +4154,19 @@
     </row>
     <row r="125" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A125" s="3">
-        <v>124</v>
+        <v>142</v>
       </c>
       <c r="B125" t="s">
-        <v>143</v>
+        <v>161</v>
       </c>
       <c r="C125" t="s">
         <v>9</v>
       </c>
       <c r="D125" t="s">
-        <v>143</v>
+        <v>161</v>
       </c>
       <c r="E125" s="8">
-        <v>46278.899305555547</v>
+        <v>46282.274305555547</v>
       </c>
       <c r="F125" s="5" t="s">
         <v>47</v>
@@ -4188,19 +4174,19 @@
     </row>
     <row r="126" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A126" s="3">
-        <v>125</v>
+        <v>143</v>
       </c>
       <c r="B126" t="s">
-        <v>144</v>
+        <v>162</v>
       </c>
       <c r="C126" t="s">
         <v>9</v>
       </c>
       <c r="D126" t="s">
-        <v>144</v>
+        <v>162</v>
       </c>
       <c r="E126" s="8">
-        <v>46279.024305555547</v>
+        <v>46282.732638888891</v>
       </c>
       <c r="F126" s="5" t="s">
         <v>47</v>
@@ -4208,19 +4194,19 @@
     </row>
     <row r="127" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A127" s="3">
-        <v>126</v>
+        <v>144</v>
       </c>
       <c r="B127" t="s">
-        <v>145</v>
+        <v>163</v>
       </c>
       <c r="C127" t="s">
         <v>9</v>
       </c>
       <c r="D127" t="s">
-        <v>145</v>
+        <v>163</v>
       </c>
       <c r="E127" s="8">
-        <v>46279.190972222219</v>
+        <v>46282.899305555547</v>
       </c>
       <c r="F127" s="5" t="s">
         <v>47</v>
@@ -4228,19 +4214,19 @@
     </row>
     <row r="128" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A128" s="3">
-        <v>127</v>
+        <v>145</v>
       </c>
       <c r="B128" t="s">
-        <v>146</v>
+        <v>164</v>
       </c>
       <c r="C128" t="s">
         <v>9</v>
       </c>
       <c r="D128" t="s">
-        <v>146</v>
+        <v>164</v>
       </c>
       <c r="E128" s="8">
-        <v>46279.274305555547</v>
+        <v>46283.024305555547</v>
       </c>
       <c r="F128" s="5" t="s">
         <v>47</v>
@@ -4248,19 +4234,19 @@
     </row>
     <row r="129" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A129" s="3">
-        <v>128</v>
+        <v>146</v>
       </c>
       <c r="B129" t="s">
-        <v>147</v>
+        <v>165</v>
       </c>
       <c r="C129" t="s">
         <v>9</v>
       </c>
       <c r="D129" t="s">
-        <v>147</v>
+        <v>165</v>
       </c>
       <c r="E129" s="8">
-        <v>46279.732638888891</v>
+        <v>46283.190972222219</v>
       </c>
       <c r="F129" s="5" t="s">
         <v>47</v>
@@ -4268,19 +4254,19 @@
     </row>
     <row r="130" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A130" s="3">
-        <v>129</v>
+        <v>147</v>
       </c>
       <c r="B130" t="s">
-        <v>148</v>
+        <v>166</v>
       </c>
       <c r="C130" t="s">
         <v>9</v>
       </c>
       <c r="D130" t="s">
-        <v>148</v>
+        <v>166</v>
       </c>
       <c r="E130" s="8">
-        <v>46279.899305555547</v>
+        <v>46283.274305555547</v>
       </c>
       <c r="F130" s="5" t="s">
         <v>47</v>
@@ -4288,19 +4274,19 @@
     </row>
     <row r="131" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A131" s="3">
-        <v>130</v>
+        <v>148</v>
       </c>
       <c r="B131" t="s">
-        <v>149</v>
+        <v>167</v>
       </c>
       <c r="C131" t="s">
         <v>9</v>
       </c>
       <c r="D131" t="s">
-        <v>149</v>
+        <v>167</v>
       </c>
       <c r="E131" s="8">
-        <v>46280.024305555547</v>
+        <v>46283.732638888891</v>
       </c>
       <c r="F131" s="5" t="s">
         <v>47</v>
@@ -4308,19 +4294,19 @@
     </row>
     <row r="132" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A132" s="3">
-        <v>131</v>
+        <v>149</v>
       </c>
       <c r="B132" t="s">
-        <v>150</v>
+        <v>168</v>
       </c>
       <c r="C132" t="s">
         <v>9</v>
       </c>
       <c r="D132" t="s">
-        <v>150</v>
+        <v>168</v>
       </c>
       <c r="E132" s="8">
-        <v>46280.190972222219</v>
+        <v>46283.899305555547</v>
       </c>
       <c r="F132" s="5" t="s">
         <v>47</v>
@@ -4328,19 +4314,19 @@
     </row>
     <row r="133" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A133" s="3">
-        <v>132</v>
+        <v>150</v>
       </c>
       <c r="B133" t="s">
-        <v>151</v>
+        <v>169</v>
       </c>
       <c r="C133" t="s">
         <v>9</v>
       </c>
       <c r="D133" t="s">
-        <v>151</v>
+        <v>169</v>
       </c>
       <c r="E133" s="8">
-        <v>46280.274305555547</v>
+        <v>46284.024305555547</v>
       </c>
       <c r="F133" s="5" t="s">
         <v>47</v>
@@ -4348,19 +4334,19 @@
     </row>
     <row r="134" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A134" s="3">
-        <v>133</v>
+        <v>151</v>
       </c>
       <c r="B134" t="s">
-        <v>152</v>
+        <v>170</v>
       </c>
       <c r="C134" t="s">
         <v>9</v>
       </c>
       <c r="D134" t="s">
-        <v>152</v>
+        <v>170</v>
       </c>
       <c r="E134" s="8">
-        <v>46280.732638888891</v>
+        <v>46284.190972222219</v>
       </c>
       <c r="F134" s="5" t="s">
         <v>47</v>
@@ -4368,19 +4354,19 @@
     </row>
     <row r="135" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A135" s="3">
-        <v>134</v>
+        <v>152</v>
       </c>
       <c r="B135" t="s">
-        <v>153</v>
+        <v>171</v>
       </c>
       <c r="C135" t="s">
         <v>9</v>
       </c>
       <c r="D135" t="s">
-        <v>153</v>
+        <v>171</v>
       </c>
       <c r="E135" s="8">
-        <v>46280.899305555547</v>
+        <v>46284.274305555547</v>
       </c>
       <c r="F135" s="5" t="s">
         <v>47</v>
@@ -4388,19 +4374,19 @@
     </row>
     <row r="136" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A136" s="3">
-        <v>135</v>
+        <v>153</v>
       </c>
       <c r="B136" t="s">
-        <v>154</v>
+        <v>172</v>
       </c>
       <c r="C136" t="s">
         <v>9</v>
       </c>
       <c r="D136" t="s">
-        <v>154</v>
+        <v>172</v>
       </c>
       <c r="E136" s="8">
-        <v>46281.024305555547</v>
+        <v>46284.732638888891</v>
       </c>
       <c r="F136" s="5" t="s">
         <v>47</v>
@@ -4408,19 +4394,19 @@
     </row>
     <row r="137" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A137" s="3">
-        <v>136</v>
+        <v>154</v>
       </c>
       <c r="B137" t="s">
-        <v>155</v>
+        <v>173</v>
       </c>
       <c r="C137" t="s">
         <v>9</v>
       </c>
       <c r="D137" t="s">
-        <v>155</v>
+        <v>173</v>
       </c>
       <c r="E137" s="8">
-        <v>46281.190972222219</v>
+        <v>46284.899305555547</v>
       </c>
       <c r="F137" s="5" t="s">
         <v>47</v>
@@ -4428,19 +4414,19 @@
     </row>
     <row r="138" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A138" s="3">
-        <v>137</v>
+        <v>155</v>
       </c>
       <c r="B138" t="s">
-        <v>156</v>
+        <v>174</v>
       </c>
       <c r="C138" t="s">
         <v>9</v>
       </c>
       <c r="D138" t="s">
-        <v>156</v>
+        <v>174</v>
       </c>
       <c r="E138" s="8">
-        <v>46281.274305555547</v>
+        <v>46285.024305555547</v>
       </c>
       <c r="F138" s="5" t="s">
         <v>47</v>
@@ -4448,19 +4434,19 @@
     </row>
     <row r="139" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A139" s="3">
-        <v>138</v>
+        <v>156</v>
       </c>
       <c r="B139" t="s">
-        <v>157</v>
+        <v>175</v>
       </c>
       <c r="C139" t="s">
         <v>9</v>
       </c>
       <c r="D139" t="s">
-        <v>157</v>
+        <v>175</v>
       </c>
       <c r="E139" s="8">
-        <v>46281.732638888891</v>
+        <v>46285.190972222219</v>
       </c>
       <c r="F139" s="5" t="s">
         <v>47</v>
@@ -4468,19 +4454,19 @@
     </row>
     <row r="140" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A140" s="3">
-        <v>139</v>
+        <v>157</v>
       </c>
       <c r="B140" t="s">
-        <v>158</v>
+        <v>176</v>
       </c>
       <c r="C140" t="s">
         <v>9</v>
       </c>
       <c r="D140" t="s">
-        <v>158</v>
+        <v>176</v>
       </c>
       <c r="E140" s="8">
-        <v>46281.899305555547</v>
+        <v>46285.274305555547</v>
       </c>
       <c r="F140" s="5" t="s">
         <v>47</v>
@@ -4488,19 +4474,19 @@
     </row>
     <row r="141" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A141" s="3">
-        <v>140</v>
+        <v>158</v>
       </c>
       <c r="B141" t="s">
-        <v>159</v>
+        <v>177</v>
       </c>
       <c r="C141" t="s">
         <v>9</v>
       </c>
       <c r="D141" t="s">
-        <v>159</v>
+        <v>177</v>
       </c>
       <c r="E141" s="8">
-        <v>46282.024305555547</v>
+        <v>46285.732638888891</v>
       </c>
       <c r="F141" s="5" t="s">
         <v>47</v>
@@ -4508,19 +4494,19 @@
     </row>
     <row r="142" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A142" s="3">
-        <v>141</v>
+        <v>159</v>
       </c>
       <c r="B142" t="s">
-        <v>160</v>
+        <v>178</v>
       </c>
       <c r="C142" t="s">
         <v>9</v>
       </c>
       <c r="D142" t="s">
-        <v>160</v>
+        <v>178</v>
       </c>
       <c r="E142" s="8">
-        <v>46282.190972222219</v>
+        <v>46285.899305555547</v>
       </c>
       <c r="F142" s="5" t="s">
         <v>47</v>
@@ -4528,19 +4514,19 @@
     </row>
     <row r="143" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A143" s="3">
-        <v>142</v>
+        <v>160</v>
       </c>
       <c r="B143" t="s">
-        <v>161</v>
+        <v>179</v>
       </c>
       <c r="C143" t="s">
         <v>9</v>
       </c>
       <c r="D143" t="s">
-        <v>161</v>
+        <v>179</v>
       </c>
       <c r="E143" s="8">
-        <v>46282.274305555547</v>
+        <v>46286.024305555547</v>
       </c>
       <c r="F143" s="5" t="s">
         <v>47</v>
@@ -4548,19 +4534,19 @@
     </row>
     <row r="144" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A144" s="3">
-        <v>143</v>
+        <v>161</v>
       </c>
       <c r="B144" t="s">
-        <v>162</v>
+        <v>180</v>
       </c>
       <c r="C144" t="s">
         <v>9</v>
       </c>
       <c r="D144" t="s">
-        <v>162</v>
+        <v>180</v>
       </c>
       <c r="E144" s="8">
-        <v>46282.732638888891</v>
+        <v>46286.190972222219</v>
       </c>
       <c r="F144" s="5" t="s">
         <v>47</v>
@@ -4568,19 +4554,19 @@
     </row>
     <row r="145" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A145" s="3">
-        <v>144</v>
+        <v>162</v>
       </c>
       <c r="B145" t="s">
-        <v>163</v>
+        <v>181</v>
       </c>
       <c r="C145" t="s">
         <v>9</v>
       </c>
       <c r="D145" t="s">
-        <v>163</v>
+        <v>181</v>
       </c>
       <c r="E145" s="8">
-        <v>46282.899305555547</v>
+        <v>46286.274305555547</v>
       </c>
       <c r="F145" s="5" t="s">
         <v>47</v>
@@ -4588,19 +4574,19 @@
     </row>
     <row r="146" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A146" s="3">
-        <v>145</v>
+        <v>163</v>
       </c>
       <c r="B146" t="s">
-        <v>164</v>
+        <v>182</v>
       </c>
       <c r="C146" t="s">
         <v>9</v>
       </c>
       <c r="D146" t="s">
-        <v>164</v>
+        <v>182</v>
       </c>
       <c r="E146" s="8">
-        <v>46283.024305555547</v>
+        <v>46286.732638888891</v>
       </c>
       <c r="F146" s="5" t="s">
         <v>47</v>
@@ -4608,19 +4594,19 @@
     </row>
     <row r="147" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A147" s="3">
-        <v>146</v>
+        <v>164</v>
       </c>
       <c r="B147" t="s">
-        <v>165</v>
+        <v>183</v>
       </c>
       <c r="C147" t="s">
         <v>9</v>
       </c>
       <c r="D147" t="s">
-        <v>165</v>
+        <v>183</v>
       </c>
       <c r="E147" s="8">
-        <v>46283.190972222219</v>
+        <v>46286.899305555547</v>
       </c>
       <c r="F147" s="5" t="s">
         <v>47</v>
@@ -4628,19 +4614,19 @@
     </row>
     <row r="148" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A148" s="3">
-        <v>147</v>
+        <v>165</v>
       </c>
       <c r="B148" t="s">
-        <v>166</v>
+        <v>184</v>
       </c>
       <c r="C148" t="s">
         <v>9</v>
       </c>
       <c r="D148" t="s">
-        <v>166</v>
+        <v>184</v>
       </c>
       <c r="E148" s="8">
-        <v>46283.274305555547</v>
+        <v>46287.024305555547</v>
       </c>
       <c r="F148" s="5" t="s">
         <v>47</v>
@@ -4648,19 +4634,19 @@
     </row>
     <row r="149" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A149" s="3">
-        <v>148</v>
+        <v>166</v>
       </c>
       <c r="B149" t="s">
-        <v>167</v>
+        <v>185</v>
       </c>
       <c r="C149" t="s">
         <v>9</v>
       </c>
       <c r="D149" t="s">
-        <v>167</v>
+        <v>185</v>
       </c>
       <c r="E149" s="8">
-        <v>46283.732638888891</v>
+        <v>46287.190972222219</v>
       </c>
       <c r="F149" s="5" t="s">
         <v>47</v>
@@ -4668,19 +4654,19 @@
     </row>
     <row r="150" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A150" s="3">
-        <v>149</v>
+        <v>167</v>
       </c>
       <c r="B150" t="s">
-        <v>168</v>
+        <v>186</v>
       </c>
       <c r="C150" t="s">
         <v>9</v>
       </c>
       <c r="D150" t="s">
-        <v>168</v>
+        <v>186</v>
       </c>
       <c r="E150" s="8">
-        <v>46283.899305555547</v>
+        <v>46287.274305555547</v>
       </c>
       <c r="F150" s="5" t="s">
         <v>47</v>
@@ -4688,19 +4674,19 @@
     </row>
     <row r="151" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A151" s="3">
-        <v>150</v>
+        <v>168</v>
       </c>
       <c r="B151" t="s">
-        <v>169</v>
+        <v>187</v>
       </c>
       <c r="C151" t="s">
         <v>9</v>
       </c>
       <c r="D151" t="s">
-        <v>169</v>
+        <v>187</v>
       </c>
       <c r="E151" s="8">
-        <v>46284.024305555547</v>
+        <v>46287.732638888891</v>
       </c>
       <c r="F151" s="5" t="s">
         <v>47</v>
@@ -4708,19 +4694,19 @@
     </row>
     <row r="152" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A152" s="3">
-        <v>151</v>
+        <v>169</v>
       </c>
       <c r="B152" t="s">
-        <v>170</v>
+        <v>188</v>
       </c>
       <c r="C152" t="s">
         <v>9</v>
       </c>
       <c r="D152" t="s">
-        <v>170</v>
+        <v>188</v>
       </c>
       <c r="E152" s="8">
-        <v>46284.190972222219</v>
+        <v>46287.899305555547</v>
       </c>
       <c r="F152" s="5" t="s">
         <v>47</v>
@@ -4728,19 +4714,19 @@
     </row>
     <row r="153" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A153" s="3">
-        <v>152</v>
+        <v>170</v>
       </c>
       <c r="B153" t="s">
-        <v>171</v>
+        <v>189</v>
       </c>
       <c r="C153" t="s">
         <v>9</v>
       </c>
       <c r="D153" t="s">
-        <v>171</v>
+        <v>189</v>
       </c>
       <c r="E153" s="8">
-        <v>46284.274305555547</v>
+        <v>46288.024305555547</v>
       </c>
       <c r="F153" s="5" t="s">
         <v>47</v>
@@ -4748,19 +4734,19 @@
     </row>
     <row r="154" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A154" s="3">
-        <v>153</v>
+        <v>171</v>
       </c>
       <c r="B154" t="s">
-        <v>172</v>
+        <v>190</v>
       </c>
       <c r="C154" t="s">
         <v>9</v>
       </c>
       <c r="D154" t="s">
-        <v>172</v>
+        <v>190</v>
       </c>
       <c r="E154" s="8">
-        <v>46284.732638888891</v>
+        <v>46288.190972222219</v>
       </c>
       <c r="F154" s="5" t="s">
         <v>47</v>
@@ -4768,19 +4754,19 @@
     </row>
     <row r="155" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A155" s="3">
-        <v>154</v>
+        <v>172</v>
       </c>
       <c r="B155" t="s">
-        <v>173</v>
+        <v>191</v>
       </c>
       <c r="C155" t="s">
         <v>9</v>
       </c>
       <c r="D155" t="s">
-        <v>173</v>
+        <v>191</v>
       </c>
       <c r="E155" s="8">
-        <v>46284.899305555547</v>
+        <v>46288.274305555547</v>
       </c>
       <c r="F155" s="5" t="s">
         <v>47</v>
@@ -4788,19 +4774,19 @@
     </row>
     <row r="156" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A156" s="3">
-        <v>155</v>
+        <v>173</v>
       </c>
       <c r="B156" t="s">
-        <v>174</v>
+        <v>192</v>
       </c>
       <c r="C156" t="s">
         <v>9</v>
       </c>
       <c r="D156" t="s">
-        <v>174</v>
+        <v>192</v>
       </c>
       <c r="E156" s="8">
-        <v>46285.024305555547</v>
+        <v>46288.732638888891</v>
       </c>
       <c r="F156" s="5" t="s">
         <v>47</v>
@@ -4808,19 +4794,19 @@
     </row>
     <row r="157" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A157" s="3">
-        <v>156</v>
+        <v>174</v>
       </c>
       <c r="B157" t="s">
-        <v>175</v>
+        <v>193</v>
       </c>
       <c r="C157" t="s">
         <v>9</v>
       </c>
       <c r="D157" t="s">
-        <v>175</v>
+        <v>193</v>
       </c>
       <c r="E157" s="8">
-        <v>46285.190972222219</v>
+        <v>46288.899305555547</v>
       </c>
       <c r="F157" s="5" t="s">
         <v>47</v>
@@ -4828,19 +4814,19 @@
     </row>
     <row r="158" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A158" s="3">
-        <v>157</v>
+        <v>175</v>
       </c>
       <c r="B158" t="s">
-        <v>176</v>
+        <v>194</v>
       </c>
       <c r="C158" t="s">
         <v>9</v>
       </c>
       <c r="D158" t="s">
-        <v>176</v>
+        <v>194</v>
       </c>
       <c r="E158" s="8">
-        <v>46285.274305555547</v>
+        <v>46289.024305555547</v>
       </c>
       <c r="F158" s="5" t="s">
         <v>47</v>
@@ -4848,19 +4834,19 @@
     </row>
     <row r="159" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A159" s="3">
-        <v>158</v>
+        <v>176</v>
       </c>
       <c r="B159" t="s">
-        <v>177</v>
+        <v>195</v>
       </c>
       <c r="C159" t="s">
         <v>9</v>
       </c>
       <c r="D159" t="s">
-        <v>177</v>
+        <v>195</v>
       </c>
       <c r="E159" s="8">
-        <v>46285.732638888891</v>
+        <v>46289.190972222219</v>
       </c>
       <c r="F159" s="5" t="s">
         <v>47</v>
@@ -4868,19 +4854,19 @@
     </row>
     <row r="160" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A160" s="3">
-        <v>159</v>
+        <v>177</v>
       </c>
       <c r="B160" t="s">
-        <v>178</v>
+        <v>196</v>
       </c>
       <c r="C160" t="s">
         <v>9</v>
       </c>
       <c r="D160" t="s">
-        <v>178</v>
+        <v>196</v>
       </c>
       <c r="E160" s="8">
-        <v>46285.899305555547</v>
+        <v>46289.274305555547</v>
       </c>
       <c r="F160" s="5" t="s">
         <v>47</v>
@@ -4888,19 +4874,19 @@
     </row>
     <row r="161" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A161" s="3">
-        <v>160</v>
+        <v>178</v>
       </c>
       <c r="B161" t="s">
-        <v>179</v>
+        <v>197</v>
       </c>
       <c r="C161" t="s">
         <v>9</v>
       </c>
       <c r="D161" t="s">
-        <v>179</v>
+        <v>197</v>
       </c>
       <c r="E161" s="8">
-        <v>46286.024305555547</v>
+        <v>46289.732638888891</v>
       </c>
       <c r="F161" s="5" t="s">
         <v>47</v>
@@ -4908,19 +4894,19 @@
     </row>
     <row r="162" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A162" s="3">
-        <v>161</v>
+        <v>179</v>
       </c>
       <c r="B162" t="s">
-        <v>180</v>
+        <v>198</v>
       </c>
       <c r="C162" t="s">
         <v>9</v>
       </c>
       <c r="D162" t="s">
-        <v>180</v>
+        <v>198</v>
       </c>
       <c r="E162" s="8">
-        <v>46286.190972222219</v>
+        <v>46289.899305555547</v>
       </c>
       <c r="F162" s="5" t="s">
         <v>47</v>
@@ -4928,19 +4914,19 @@
     </row>
     <row r="163" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A163" s="3">
-        <v>162</v>
+        <v>180</v>
       </c>
       <c r="B163" t="s">
-        <v>181</v>
+        <v>199</v>
       </c>
       <c r="C163" t="s">
         <v>9</v>
       </c>
       <c r="D163" t="s">
-        <v>181</v>
+        <v>199</v>
       </c>
       <c r="E163" s="8">
-        <v>46286.274305555547</v>
+        <v>46290.024305555547</v>
       </c>
       <c r="F163" s="5" t="s">
         <v>47</v>
@@ -4948,19 +4934,19 @@
     </row>
     <row r="164" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A164" s="3">
-        <v>163</v>
+        <v>181</v>
       </c>
       <c r="B164" t="s">
-        <v>182</v>
+        <v>200</v>
       </c>
       <c r="C164" t="s">
         <v>9</v>
       </c>
       <c r="D164" t="s">
-        <v>182</v>
+        <v>200</v>
       </c>
       <c r="E164" s="8">
-        <v>46286.732638888891</v>
+        <v>46290.190972222219</v>
       </c>
       <c r="F164" s="5" t="s">
         <v>47</v>
@@ -4968,19 +4954,19 @@
     </row>
     <row r="165" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A165" s="3">
-        <v>164</v>
+        <v>182</v>
       </c>
       <c r="B165" t="s">
-        <v>183</v>
+        <v>201</v>
       </c>
       <c r="C165" t="s">
         <v>9</v>
       </c>
       <c r="D165" t="s">
-        <v>183</v>
+        <v>201</v>
       </c>
       <c r="E165" s="8">
-        <v>46286.899305555547</v>
+        <v>46290.274305555547</v>
       </c>
       <c r="F165" s="5" t="s">
         <v>47</v>
@@ -4988,19 +4974,19 @@
     </row>
     <row r="166" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A166" s="3">
-        <v>165</v>
+        <v>183</v>
       </c>
       <c r="B166" t="s">
-        <v>184</v>
+        <v>202</v>
       </c>
       <c r="C166" t="s">
         <v>9</v>
       </c>
       <c r="D166" t="s">
-        <v>184</v>
+        <v>202</v>
       </c>
       <c r="E166" s="8">
-        <v>46287.024305555547</v>
+        <v>46290.732638888891</v>
       </c>
       <c r="F166" s="5" t="s">
         <v>47</v>
@@ -5008,19 +4994,19 @@
     </row>
     <row r="167" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A167" s="3">
-        <v>166</v>
+        <v>184</v>
       </c>
       <c r="B167" t="s">
-        <v>185</v>
+        <v>203</v>
       </c>
       <c r="C167" t="s">
         <v>9</v>
       </c>
       <c r="D167" t="s">
-        <v>185</v>
+        <v>203</v>
       </c>
       <c r="E167" s="8">
-        <v>46287.190972222219</v>
+        <v>46290.899305555547</v>
       </c>
       <c r="F167" s="5" t="s">
         <v>47</v>
@@ -5028,19 +5014,19 @@
     </row>
     <row r="168" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A168" s="3">
-        <v>167</v>
+        <v>185</v>
       </c>
       <c r="B168" t="s">
-        <v>186</v>
+        <v>204</v>
       </c>
       <c r="C168" t="s">
         <v>9</v>
       </c>
       <c r="D168" t="s">
-        <v>186</v>
+        <v>204</v>
       </c>
       <c r="E168" s="8">
-        <v>46287.274305555547</v>
+        <v>46291.024305555547</v>
       </c>
       <c r="F168" s="5" t="s">
         <v>47</v>
@@ -5048,19 +5034,19 @@
     </row>
     <row r="169" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A169" s="3">
-        <v>168</v>
+        <v>186</v>
       </c>
       <c r="B169" t="s">
-        <v>187</v>
+        <v>205</v>
       </c>
       <c r="C169" t="s">
         <v>9</v>
       </c>
       <c r="D169" t="s">
-        <v>187</v>
+        <v>205</v>
       </c>
       <c r="E169" s="8">
-        <v>46287.732638888891</v>
+        <v>46291.190972222219</v>
       </c>
       <c r="F169" s="5" t="s">
         <v>47</v>
@@ -5068,19 +5054,19 @@
     </row>
     <row r="170" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A170" s="3">
-        <v>169</v>
+        <v>187</v>
       </c>
       <c r="B170" t="s">
-        <v>188</v>
+        <v>206</v>
       </c>
       <c r="C170" t="s">
         <v>9</v>
       </c>
       <c r="D170" t="s">
-        <v>188</v>
+        <v>206</v>
       </c>
       <c r="E170" s="8">
-        <v>46287.899305555547</v>
+        <v>46291.274305555547</v>
       </c>
       <c r="F170" s="5" t="s">
         <v>47</v>
@@ -5088,19 +5074,19 @@
     </row>
     <row r="171" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A171" s="3">
-        <v>170</v>
+        <v>188</v>
       </c>
       <c r="B171" t="s">
-        <v>189</v>
+        <v>207</v>
       </c>
       <c r="C171" t="s">
         <v>9</v>
       </c>
       <c r="D171" t="s">
-        <v>189</v>
+        <v>207</v>
       </c>
       <c r="E171" s="8">
-        <v>46288.024305555547</v>
+        <v>46291.732638888891</v>
       </c>
       <c r="F171" s="5" t="s">
         <v>47</v>
@@ -5108,19 +5094,19 @@
     </row>
     <row r="172" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A172" s="3">
-        <v>171</v>
+        <v>189</v>
       </c>
       <c r="B172" t="s">
-        <v>190</v>
+        <v>208</v>
       </c>
       <c r="C172" t="s">
         <v>9</v>
       </c>
       <c r="D172" t="s">
-        <v>190</v>
+        <v>208</v>
       </c>
       <c r="E172" s="8">
-        <v>46288.190972222219</v>
+        <v>46291.899305555547</v>
       </c>
       <c r="F172" s="5" t="s">
         <v>47</v>
@@ -5128,19 +5114,19 @@
     </row>
     <row r="173" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A173" s="3">
-        <v>172</v>
+        <v>190</v>
       </c>
       <c r="B173" t="s">
-        <v>191</v>
+        <v>209</v>
       </c>
       <c r="C173" t="s">
         <v>9</v>
       </c>
       <c r="D173" t="s">
-        <v>191</v>
+        <v>209</v>
       </c>
       <c r="E173" s="8">
-        <v>46288.274305555547</v>
+        <v>46292.024305555547</v>
       </c>
       <c r="F173" s="5" t="s">
         <v>47</v>
@@ -5148,19 +5134,19 @@
     </row>
     <row r="174" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A174" s="3">
-        <v>173</v>
+        <v>191</v>
       </c>
       <c r="B174" t="s">
-        <v>192</v>
+        <v>210</v>
       </c>
       <c r="C174" t="s">
         <v>9</v>
       </c>
       <c r="D174" t="s">
-        <v>192</v>
+        <v>210</v>
       </c>
       <c r="E174" s="8">
-        <v>46288.732638888891</v>
+        <v>46292.190972222219</v>
       </c>
       <c r="F174" s="5" t="s">
         <v>47</v>
@@ -5168,19 +5154,19 @@
     </row>
     <row r="175" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A175" s="3">
-        <v>174</v>
+        <v>192</v>
       </c>
       <c r="B175" t="s">
-        <v>193</v>
+        <v>211</v>
       </c>
       <c r="C175" t="s">
         <v>9</v>
       </c>
       <c r="D175" t="s">
-        <v>193</v>
+        <v>211</v>
       </c>
       <c r="E175" s="8">
-        <v>46288.899305555547</v>
+        <v>46292.274305555547</v>
       </c>
       <c r="F175" s="5" t="s">
         <v>47</v>
@@ -5188,19 +5174,19 @@
     </row>
     <row r="176" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A176" s="3">
-        <v>175</v>
+        <v>193</v>
       </c>
       <c r="B176" t="s">
-        <v>194</v>
+        <v>212</v>
       </c>
       <c r="C176" t="s">
         <v>9</v>
       </c>
       <c r="D176" t="s">
-        <v>194</v>
+        <v>212</v>
       </c>
       <c r="E176" s="8">
-        <v>46289.024305555547</v>
+        <v>46292.732638888891</v>
       </c>
       <c r="F176" s="5" t="s">
         <v>47</v>
@@ -5208,19 +5194,19 @@
     </row>
     <row r="177" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A177" s="3">
-        <v>176</v>
+        <v>194</v>
       </c>
       <c r="B177" t="s">
-        <v>195</v>
+        <v>213</v>
       </c>
       <c r="C177" t="s">
         <v>9</v>
       </c>
       <c r="D177" t="s">
-        <v>195</v>
+        <v>213</v>
       </c>
       <c r="E177" s="8">
-        <v>46289.190972222219</v>
+        <v>46292.899305555547</v>
       </c>
       <c r="F177" s="5" t="s">
         <v>47</v>
@@ -5228,19 +5214,19 @@
     </row>
     <row r="178" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A178" s="3">
-        <v>177</v>
+        <v>195</v>
       </c>
       <c r="B178" t="s">
-        <v>196</v>
+        <v>214</v>
       </c>
       <c r="C178" t="s">
         <v>9</v>
       </c>
       <c r="D178" t="s">
-        <v>196</v>
+        <v>214</v>
       </c>
       <c r="E178" s="8">
-        <v>46289.274305555547</v>
+        <v>46293.024305555547</v>
       </c>
       <c r="F178" s="5" t="s">
         <v>47</v>
@@ -5248,19 +5234,19 @@
     </row>
     <row r="179" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A179" s="3">
-        <v>178</v>
+        <v>196</v>
       </c>
       <c r="B179" t="s">
-        <v>197</v>
+        <v>215</v>
       </c>
       <c r="C179" t="s">
         <v>9</v>
       </c>
       <c r="D179" t="s">
-        <v>197</v>
+        <v>215</v>
       </c>
       <c r="E179" s="8">
-        <v>46289.732638888891</v>
+        <v>46293.190972222219</v>
       </c>
       <c r="F179" s="5" t="s">
         <v>47</v>
@@ -5268,19 +5254,19 @@
     </row>
     <row r="180" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A180" s="3">
-        <v>179</v>
+        <v>197</v>
       </c>
       <c r="B180" t="s">
-        <v>198</v>
+        <v>216</v>
       </c>
       <c r="C180" t="s">
         <v>9</v>
       </c>
       <c r="D180" t="s">
-        <v>198</v>
+        <v>216</v>
       </c>
       <c r="E180" s="8">
-        <v>46289.899305555547</v>
+        <v>46293.274305555547</v>
       </c>
       <c r="F180" s="5" t="s">
         <v>47</v>
@@ -5288,19 +5274,19 @@
     </row>
     <row r="181" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A181" s="3">
-        <v>180</v>
+        <v>198</v>
       </c>
       <c r="B181" t="s">
-        <v>199</v>
+        <v>217</v>
       </c>
       <c r="C181" t="s">
         <v>9</v>
       </c>
       <c r="D181" t="s">
-        <v>199</v>
+        <v>217</v>
       </c>
       <c r="E181" s="8">
-        <v>46290.024305555547</v>
+        <v>46293.732638888891</v>
       </c>
       <c r="F181" s="5" t="s">
         <v>47</v>
@@ -5308,19 +5294,19 @@
     </row>
     <row r="182" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A182" s="3">
-        <v>181</v>
+        <v>199</v>
       </c>
       <c r="B182" t="s">
-        <v>200</v>
+        <v>218</v>
       </c>
       <c r="C182" t="s">
         <v>9</v>
       </c>
       <c r="D182" t="s">
-        <v>200</v>
+        <v>218</v>
       </c>
       <c r="E182" s="8">
-        <v>46290.190972222219</v>
+        <v>46293.899305555547</v>
       </c>
       <c r="F182" s="5" t="s">
         <v>47</v>
@@ -5328,19 +5314,19 @@
     </row>
     <row r="183" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A183" s="3">
-        <v>182</v>
+        <v>200</v>
       </c>
       <c r="B183" t="s">
-        <v>201</v>
+        <v>219</v>
       </c>
       <c r="C183" t="s">
         <v>9</v>
       </c>
       <c r="D183" t="s">
-        <v>201</v>
+        <v>219</v>
       </c>
       <c r="E183" s="8">
-        <v>46290.274305555547</v>
+        <v>46294.024305555547</v>
       </c>
       <c r="F183" s="5" t="s">
         <v>47</v>
@@ -5348,19 +5334,19 @@
     </row>
     <row r="184" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A184" s="3">
-        <v>183</v>
+        <v>201</v>
       </c>
       <c r="B184" t="s">
-        <v>202</v>
+        <v>220</v>
       </c>
       <c r="C184" t="s">
         <v>9</v>
       </c>
       <c r="D184" t="s">
-        <v>202</v>
+        <v>220</v>
       </c>
       <c r="E184" s="8">
-        <v>46290.732638888891</v>
+        <v>46294.190972222219</v>
       </c>
       <c r="F184" s="5" t="s">
         <v>47</v>
@@ -5368,19 +5354,19 @@
     </row>
     <row r="185" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A185" s="3">
-        <v>184</v>
+        <v>202</v>
       </c>
       <c r="B185" t="s">
-        <v>203</v>
+        <v>221</v>
       </c>
       <c r="C185" t="s">
         <v>9</v>
       </c>
       <c r="D185" t="s">
-        <v>203</v>
+        <v>221</v>
       </c>
       <c r="E185" s="8">
-        <v>46290.899305555547</v>
+        <v>46294.274305555547</v>
       </c>
       <c r="F185" s="5" t="s">
         <v>47</v>
@@ -5388,19 +5374,19 @@
     </row>
     <row r="186" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A186" s="3">
-        <v>185</v>
+        <v>203</v>
       </c>
       <c r="B186" t="s">
-        <v>204</v>
+        <v>222</v>
       </c>
       <c r="C186" t="s">
         <v>9</v>
       </c>
       <c r="D186" t="s">
-        <v>204</v>
+        <v>222</v>
       </c>
       <c r="E186" s="8">
-        <v>46291.024305555547</v>
+        <v>46294.732638888891</v>
       </c>
       <c r="F186" s="5" t="s">
         <v>47</v>
@@ -5408,19 +5394,19 @@
     </row>
     <row r="187" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A187" s="3">
-        <v>186</v>
+        <v>204</v>
       </c>
       <c r="B187" t="s">
-        <v>205</v>
+        <v>223</v>
       </c>
       <c r="C187" t="s">
         <v>9</v>
       </c>
       <c r="D187" t="s">
-        <v>205</v>
+        <v>223</v>
       </c>
       <c r="E187" s="8">
-        <v>46291.190972222219</v>
+        <v>46294.899305555547</v>
       </c>
       <c r="F187" s="5" t="s">
         <v>47</v>
@@ -5428,19 +5414,19 @@
     </row>
     <row r="188" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A188" s="3">
-        <v>187</v>
+        <v>205</v>
       </c>
       <c r="B188" t="s">
-        <v>206</v>
+        <v>224</v>
       </c>
       <c r="C188" t="s">
         <v>9</v>
       </c>
       <c r="D188" t="s">
-        <v>206</v>
+        <v>224</v>
       </c>
       <c r="E188" s="8">
-        <v>46291.274305555547</v>
+        <v>46295.024305555547</v>
       </c>
       <c r="F188" s="5" t="s">
         <v>47</v>
@@ -5448,19 +5434,19 @@
     </row>
     <row r="189" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A189" s="3">
-        <v>188</v>
+        <v>206</v>
       </c>
       <c r="B189" t="s">
-        <v>207</v>
+        <v>225</v>
       </c>
       <c r="C189" t="s">
         <v>9</v>
       </c>
       <c r="D189" t="s">
-        <v>207</v>
+        <v>225</v>
       </c>
       <c r="E189" s="8">
-        <v>46291.732638888891</v>
+        <v>46295.190972222219</v>
       </c>
       <c r="F189" s="5" t="s">
         <v>47</v>
@@ -5468,19 +5454,19 @@
     </row>
     <row r="190" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A190" s="3">
-        <v>189</v>
+        <v>207</v>
       </c>
       <c r="B190" t="s">
-        <v>208</v>
+        <v>226</v>
       </c>
       <c r="C190" t="s">
         <v>9</v>
       </c>
       <c r="D190" t="s">
-        <v>208</v>
+        <v>226</v>
       </c>
       <c r="E190" s="8">
-        <v>46291.899305555547</v>
+        <v>46295.274305555547</v>
       </c>
       <c r="F190" s="5" t="s">
         <v>47</v>
@@ -5488,19 +5474,19 @@
     </row>
     <row r="191" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A191" s="3">
-        <v>190</v>
+        <v>208</v>
       </c>
       <c r="B191" t="s">
-        <v>209</v>
+        <v>227</v>
       </c>
       <c r="C191" t="s">
         <v>9</v>
       </c>
       <c r="D191" t="s">
-        <v>209</v>
+        <v>227</v>
       </c>
       <c r="E191" s="8">
-        <v>46292.024305555547</v>
+        <v>46295.732638888891</v>
       </c>
       <c r="F191" s="5" t="s">
         <v>47</v>
@@ -5508,19 +5494,19 @@
     </row>
     <row r="192" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A192" s="3">
-        <v>191</v>
+        <v>209</v>
       </c>
       <c r="B192" t="s">
-        <v>210</v>
+        <v>228</v>
       </c>
       <c r="C192" t="s">
         <v>9</v>
       </c>
       <c r="D192" t="s">
-        <v>210</v>
+        <v>228</v>
       </c>
       <c r="E192" s="8">
-        <v>46292.190972222219</v>
+        <v>46295.899305555547</v>
       </c>
       <c r="F192" s="5" t="s">
         <v>47</v>
@@ -5528,19 +5514,19 @@
     </row>
     <row r="193" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A193" s="3">
-        <v>192</v>
+        <v>210</v>
       </c>
       <c r="B193" t="s">
-        <v>211</v>
+        <v>229</v>
       </c>
       <c r="C193" t="s">
         <v>9</v>
       </c>
       <c r="D193" t="s">
-        <v>211</v>
+        <v>229</v>
       </c>
       <c r="E193" s="8">
-        <v>46292.274305555547</v>
+        <v>46296.024305555547</v>
       </c>
       <c r="F193" s="5" t="s">
         <v>47</v>
@@ -5548,19 +5534,19 @@
     </row>
     <row r="194" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A194" s="3">
-        <v>193</v>
+        <v>211</v>
       </c>
       <c r="B194" t="s">
-        <v>212</v>
+        <v>230</v>
       </c>
       <c r="C194" t="s">
         <v>9</v>
       </c>
       <c r="D194" t="s">
-        <v>212</v>
+        <v>230</v>
       </c>
       <c r="E194" s="8">
-        <v>46292.732638888891</v>
+        <v>46296.190972222219</v>
       </c>
       <c r="F194" s="5" t="s">
         <v>47</v>
@@ -5568,19 +5554,19 @@
     </row>
     <row r="195" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A195" s="3">
-        <v>194</v>
+        <v>212</v>
       </c>
       <c r="B195" t="s">
-        <v>213</v>
+        <v>231</v>
       </c>
       <c r="C195" t="s">
         <v>9</v>
       </c>
       <c r="D195" t="s">
-        <v>213</v>
+        <v>231</v>
       </c>
       <c r="E195" s="8">
-        <v>46292.899305555547</v>
+        <v>46296.274305555547</v>
       </c>
       <c r="F195" s="5" t="s">
         <v>47</v>
@@ -5588,19 +5574,19 @@
     </row>
     <row r="196" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A196" s="3">
-        <v>195</v>
+        <v>213</v>
       </c>
       <c r="B196" t="s">
-        <v>214</v>
+        <v>232</v>
       </c>
       <c r="C196" t="s">
         <v>9</v>
       </c>
       <c r="D196" t="s">
-        <v>214</v>
+        <v>232</v>
       </c>
       <c r="E196" s="8">
-        <v>46293.024305555547</v>
+        <v>46296.732638888891</v>
       </c>
       <c r="F196" s="5" t="s">
         <v>47</v>
@@ -5608,19 +5594,19 @@
     </row>
     <row r="197" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A197" s="3">
-        <v>196</v>
+        <v>214</v>
       </c>
       <c r="B197" t="s">
-        <v>215</v>
+        <v>233</v>
       </c>
       <c r="C197" t="s">
         <v>9</v>
       </c>
       <c r="D197" t="s">
-        <v>215</v>
+        <v>233</v>
       </c>
       <c r="E197" s="8">
-        <v>46293.190972222219</v>
+        <v>46296.899305555547</v>
       </c>
       <c r="F197" s="5" t="s">
         <v>47</v>
@@ -5628,19 +5614,19 @@
     </row>
     <row r="198" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A198" s="3">
-        <v>197</v>
+        <v>215</v>
       </c>
       <c r="B198" t="s">
-        <v>216</v>
+        <v>234</v>
       </c>
       <c r="C198" t="s">
         <v>9</v>
       </c>
       <c r="D198" t="s">
-        <v>216</v>
+        <v>234</v>
       </c>
       <c r="E198" s="8">
-        <v>46293.274305555547</v>
+        <v>46297.024305555547</v>
       </c>
       <c r="F198" s="5" t="s">
         <v>47</v>
@@ -5648,19 +5634,19 @@
     </row>
     <row r="199" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A199" s="3">
-        <v>198</v>
+        <v>216</v>
       </c>
       <c r="B199" t="s">
-        <v>217</v>
+        <v>235</v>
       </c>
       <c r="C199" t="s">
         <v>9</v>
       </c>
       <c r="D199" t="s">
-        <v>217</v>
+        <v>235</v>
       </c>
       <c r="E199" s="8">
-        <v>46293.732638888891</v>
+        <v>46297.190972222219</v>
       </c>
       <c r="F199" s="5" t="s">
         <v>47</v>
@@ -5668,19 +5654,19 @@
     </row>
     <row r="200" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A200" s="3">
-        <v>199</v>
+        <v>217</v>
       </c>
       <c r="B200" t="s">
-        <v>218</v>
+        <v>236</v>
       </c>
       <c r="C200" t="s">
         <v>9</v>
       </c>
       <c r="D200" t="s">
-        <v>218</v>
+        <v>236</v>
       </c>
       <c r="E200" s="8">
-        <v>46293.899305555547</v>
+        <v>46297.274305555547</v>
       </c>
       <c r="F200" s="5" t="s">
         <v>47</v>
@@ -5688,19 +5674,19 @@
     </row>
     <row r="201" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A201" s="3">
-        <v>200</v>
+        <v>218</v>
       </c>
       <c r="B201" t="s">
-        <v>219</v>
+        <v>237</v>
       </c>
       <c r="C201" t="s">
         <v>9</v>
       </c>
       <c r="D201" t="s">
-        <v>219</v>
+        <v>237</v>
       </c>
       <c r="E201" s="8">
-        <v>46294.024305555547</v>
+        <v>46297.732638888891</v>
       </c>
       <c r="F201" s="5" t="s">
         <v>47</v>
@@ -5708,19 +5694,19 @@
     </row>
     <row r="202" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A202" s="3">
-        <v>201</v>
+        <v>219</v>
       </c>
       <c r="B202" t="s">
-        <v>220</v>
+        <v>238</v>
       </c>
       <c r="C202" t="s">
         <v>9</v>
       </c>
       <c r="D202" t="s">
-        <v>220</v>
+        <v>238</v>
       </c>
       <c r="E202" s="8">
-        <v>46294.190972222219</v>
+        <v>46297.899305555547</v>
       </c>
       <c r="F202" s="5" t="s">
         <v>47</v>
@@ -5728,19 +5714,19 @@
     </row>
     <row r="203" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A203" s="3">
-        <v>202</v>
+        <v>220</v>
       </c>
       <c r="B203" t="s">
-        <v>221</v>
+        <v>239</v>
       </c>
       <c r="C203" t="s">
         <v>9</v>
       </c>
       <c r="D203" t="s">
-        <v>221</v>
+        <v>239</v>
       </c>
       <c r="E203" s="8">
-        <v>46294.274305555547</v>
+        <v>46298.024305555547</v>
       </c>
       <c r="F203" s="5" t="s">
         <v>47</v>
@@ -5748,19 +5734,19 @@
     </row>
     <row r="204" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A204" s="3">
-        <v>203</v>
+        <v>221</v>
       </c>
       <c r="B204" t="s">
-        <v>222</v>
+        <v>240</v>
       </c>
       <c r="C204" t="s">
         <v>9</v>
       </c>
       <c r="D204" t="s">
-        <v>222</v>
+        <v>240</v>
       </c>
       <c r="E204" s="8">
-        <v>46294.732638888891</v>
+        <v>46298.190972222219</v>
       </c>
       <c r="F204" s="5" t="s">
         <v>47</v>
@@ -5768,19 +5754,19 @@
     </row>
     <row r="205" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A205" s="3">
-        <v>204</v>
+        <v>222</v>
       </c>
       <c r="B205" t="s">
-        <v>223</v>
+        <v>241</v>
       </c>
       <c r="C205" t="s">
         <v>9</v>
       </c>
       <c r="D205" t="s">
-        <v>223</v>
+        <v>241</v>
       </c>
       <c r="E205" s="8">
-        <v>46294.899305555547</v>
+        <v>46298.274305555547</v>
       </c>
       <c r="F205" s="5" t="s">
         <v>47</v>
@@ -5788,19 +5774,19 @@
     </row>
     <row r="206" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A206" s="3">
-        <v>205</v>
+        <v>223</v>
       </c>
       <c r="B206" t="s">
-        <v>224</v>
+        <v>242</v>
       </c>
       <c r="C206" t="s">
         <v>9</v>
       </c>
       <c r="D206" t="s">
-        <v>224</v>
+        <v>242</v>
       </c>
       <c r="E206" s="8">
-        <v>46295.024305555547</v>
+        <v>46298.732638888891</v>
       </c>
       <c r="F206" s="5" t="s">
         <v>47</v>
@@ -5808,19 +5794,19 @@
     </row>
     <row r="207" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A207" s="3">
-        <v>206</v>
+        <v>224</v>
       </c>
       <c r="B207" t="s">
-        <v>225</v>
+        <v>243</v>
       </c>
       <c r="C207" t="s">
         <v>9</v>
       </c>
       <c r="D207" t="s">
-        <v>225</v>
+        <v>243</v>
       </c>
       <c r="E207" s="8">
-        <v>46295.190972222219</v>
+        <v>46298.899305555547</v>
       </c>
       <c r="F207" s="5" t="s">
         <v>47</v>
@@ -5828,19 +5814,19 @@
     </row>
     <row r="208" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A208" s="3">
-        <v>207</v>
+        <v>225</v>
       </c>
       <c r="B208" t="s">
-        <v>226</v>
+        <v>244</v>
       </c>
       <c r="C208" t="s">
         <v>9</v>
       </c>
       <c r="D208" t="s">
-        <v>226</v>
+        <v>244</v>
       </c>
       <c r="E208" s="8">
-        <v>46295.274305555547</v>
+        <v>46299.024305555547</v>
       </c>
       <c r="F208" s="5" t="s">
         <v>47</v>
@@ -5848,19 +5834,19 @@
     </row>
     <row r="209" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A209" s="3">
-        <v>208</v>
+        <v>226</v>
       </c>
       <c r="B209" t="s">
-        <v>227</v>
+        <v>245</v>
       </c>
       <c r="C209" t="s">
         <v>9</v>
       </c>
       <c r="D209" t="s">
-        <v>227</v>
+        <v>245</v>
       </c>
       <c r="E209" s="8">
-        <v>46295.732638888891</v>
+        <v>46299.190972222219</v>
       </c>
       <c r="F209" s="5" t="s">
         <v>47</v>
@@ -5868,19 +5854,19 @@
     </row>
     <row r="210" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A210" s="3">
-        <v>209</v>
+        <v>227</v>
       </c>
       <c r="B210" t="s">
-        <v>228</v>
+        <v>246</v>
       </c>
       <c r="C210" t="s">
         <v>9</v>
       </c>
       <c r="D210" t="s">
-        <v>228</v>
+        <v>246</v>
       </c>
       <c r="E210" s="8">
-        <v>46295.899305555547</v>
+        <v>46299.274305555547</v>
       </c>
       <c r="F210" s="5" t="s">
         <v>47</v>
@@ -5888,19 +5874,19 @@
     </row>
     <row r="211" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A211" s="3">
-        <v>210</v>
+        <v>228</v>
       </c>
       <c r="B211" t="s">
-        <v>229</v>
+        <v>247</v>
       </c>
       <c r="C211" t="s">
         <v>9</v>
       </c>
       <c r="D211" t="s">
-        <v>229</v>
+        <v>247</v>
       </c>
       <c r="E211" s="8">
-        <v>46296.024305555547</v>
+        <v>46299.732638888891</v>
       </c>
       <c r="F211" s="5" t="s">
         <v>47</v>
@@ -5908,19 +5894,19 @@
     </row>
     <row r="212" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A212" s="3">
-        <v>211</v>
+        <v>229</v>
       </c>
       <c r="B212" t="s">
-        <v>230</v>
+        <v>248</v>
       </c>
       <c r="C212" t="s">
         <v>9</v>
       </c>
       <c r="D212" t="s">
-        <v>230</v>
+        <v>248</v>
       </c>
       <c r="E212" s="8">
-        <v>46296.190972222219</v>
+        <v>46299.899305555547</v>
       </c>
       <c r="F212" s="5" t="s">
         <v>47</v>
@@ -5928,19 +5914,19 @@
     </row>
     <row r="213" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A213" s="3">
-        <v>212</v>
+        <v>230</v>
       </c>
       <c r="B213" t="s">
-        <v>231</v>
+        <v>249</v>
       </c>
       <c r="C213" t="s">
         <v>9</v>
       </c>
       <c r="D213" t="s">
-        <v>231</v>
+        <v>249</v>
       </c>
       <c r="E213" s="8">
-        <v>46296.274305555547</v>
+        <v>46300.024305555547</v>
       </c>
       <c r="F213" s="5" t="s">
         <v>47</v>
@@ -5948,19 +5934,19 @@
     </row>
     <row r="214" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A214" s="3">
-        <v>213</v>
+        <v>231</v>
       </c>
       <c r="B214" t="s">
-        <v>232</v>
+        <v>250</v>
       </c>
       <c r="C214" t="s">
         <v>9</v>
       </c>
       <c r="D214" t="s">
-        <v>232</v>
+        <v>250</v>
       </c>
       <c r="E214" s="8">
-        <v>46296.732638888891</v>
+        <v>46300.190972222219</v>
       </c>
       <c r="F214" s="5" t="s">
         <v>47</v>
@@ -5968,19 +5954,19 @@
     </row>
     <row r="215" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A215" s="3">
-        <v>214</v>
+        <v>232</v>
       </c>
       <c r="B215" t="s">
-        <v>233</v>
+        <v>251</v>
       </c>
       <c r="C215" t="s">
         <v>9</v>
       </c>
       <c r="D215" t="s">
-        <v>233</v>
+        <v>251</v>
       </c>
       <c r="E215" s="8">
-        <v>46296.899305555547</v>
+        <v>46300.274305555547</v>
       </c>
       <c r="F215" s="5" t="s">
         <v>47</v>
@@ -5988,19 +5974,19 @@
     </row>
     <row r="216" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A216" s="3">
-        <v>215</v>
+        <v>233</v>
       </c>
       <c r="B216" t="s">
-        <v>234</v>
+        <v>252</v>
       </c>
       <c r="C216" t="s">
         <v>9</v>
       </c>
       <c r="D216" t="s">
-        <v>234</v>
+        <v>252</v>
       </c>
       <c r="E216" s="8">
-        <v>46297.024305555547</v>
+        <v>46300.732638888891</v>
       </c>
       <c r="F216" s="5" t="s">
         <v>47</v>
@@ -6008,19 +5994,19 @@
     </row>
     <row r="217" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A217" s="3">
-        <v>216</v>
+        <v>234</v>
       </c>
       <c r="B217" t="s">
-        <v>235</v>
+        <v>253</v>
       </c>
       <c r="C217" t="s">
         <v>9</v>
       </c>
       <c r="D217" t="s">
-        <v>235</v>
+        <v>253</v>
       </c>
       <c r="E217" s="8">
-        <v>46297.190972222219</v>
+        <v>46300.899305555547</v>
       </c>
       <c r="F217" s="5" t="s">
         <v>47</v>
@@ -6028,19 +6014,19 @@
     </row>
     <row r="218" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A218" s="3">
-        <v>217</v>
+        <v>235</v>
       </c>
       <c r="B218" t="s">
-        <v>236</v>
+        <v>254</v>
       </c>
       <c r="C218" t="s">
         <v>9</v>
       </c>
       <c r="D218" t="s">
-        <v>236</v>
+        <v>254</v>
       </c>
       <c r="E218" s="8">
-        <v>46297.274305555547</v>
+        <v>46301.024305555547</v>
       </c>
       <c r="F218" s="5" t="s">
         <v>47</v>
@@ -6048,19 +6034,19 @@
     </row>
     <row r="219" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A219" s="3">
-        <v>218</v>
+        <v>236</v>
       </c>
       <c r="B219" t="s">
-        <v>237</v>
+        <v>255</v>
       </c>
       <c r="C219" t="s">
         <v>9</v>
       </c>
       <c r="D219" t="s">
-        <v>237</v>
+        <v>255</v>
       </c>
       <c r="E219" s="8">
-        <v>46297.732638888891</v>
+        <v>46301.190972222219</v>
       </c>
       <c r="F219" s="5" t="s">
         <v>47</v>
@@ -6068,19 +6054,19 @@
     </row>
     <row r="220" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A220" s="3">
-        <v>219</v>
+        <v>237</v>
       </c>
       <c r="B220" t="s">
-        <v>238</v>
+        <v>256</v>
       </c>
       <c r="C220" t="s">
         <v>9</v>
       </c>
       <c r="D220" t="s">
-        <v>238</v>
+        <v>256</v>
       </c>
       <c r="E220" s="8">
-        <v>46297.899305555547</v>
+        <v>46301.274305555547</v>
       </c>
       <c r="F220" s="5" t="s">
         <v>47</v>
@@ -6088,19 +6074,19 @@
     </row>
     <row r="221" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A221" s="3">
-        <v>220</v>
+        <v>238</v>
       </c>
       <c r="B221" t="s">
-        <v>239</v>
+        <v>257</v>
       </c>
       <c r="C221" t="s">
         <v>9</v>
       </c>
       <c r="D221" t="s">
-        <v>239</v>
+        <v>257</v>
       </c>
       <c r="E221" s="8">
-        <v>46298.024305555547</v>
+        <v>46301.732638888891</v>
       </c>
       <c r="F221" s="5" t="s">
         <v>47</v>
@@ -6108,19 +6094,19 @@
     </row>
     <row r="222" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A222" s="3">
-        <v>221</v>
+        <v>239</v>
       </c>
       <c r="B222" t="s">
-        <v>240</v>
+        <v>258</v>
       </c>
       <c r="C222" t="s">
         <v>9</v>
       </c>
       <c r="D222" t="s">
-        <v>240</v>
+        <v>258</v>
       </c>
       <c r="E222" s="8">
-        <v>46298.190972222219</v>
+        <v>46301.899305555547</v>
       </c>
       <c r="F222" s="5" t="s">
         <v>47</v>
@@ -6128,19 +6114,19 @@
     </row>
     <row r="223" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A223" s="3">
-        <v>222</v>
+        <v>240</v>
       </c>
       <c r="B223" t="s">
-        <v>241</v>
+        <v>259</v>
       </c>
       <c r="C223" t="s">
         <v>9</v>
       </c>
       <c r="D223" t="s">
-        <v>241</v>
+        <v>259</v>
       </c>
       <c r="E223" s="8">
-        <v>46298.274305555547</v>
+        <v>46302.024305555547</v>
       </c>
       <c r="F223" s="5" t="s">
         <v>47</v>
@@ -6148,19 +6134,19 @@
     </row>
     <row r="224" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A224" s="3">
-        <v>223</v>
+        <v>241</v>
       </c>
       <c r="B224" t="s">
-        <v>242</v>
+        <v>260</v>
       </c>
       <c r="C224" t="s">
         <v>9</v>
       </c>
       <c r="D224" t="s">
-        <v>242</v>
+        <v>260</v>
       </c>
       <c r="E224" s="8">
-        <v>46298.732638888891</v>
+        <v>46302.190972222219</v>
       </c>
       <c r="F224" s="5" t="s">
         <v>47</v>
@@ -6168,19 +6154,19 @@
     </row>
     <row r="225" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A225" s="3">
-        <v>224</v>
+        <v>242</v>
       </c>
       <c r="B225" t="s">
-        <v>243</v>
+        <v>261</v>
       </c>
       <c r="C225" t="s">
         <v>9</v>
       </c>
       <c r="D225" t="s">
-        <v>243</v>
+        <v>261</v>
       </c>
       <c r="E225" s="8">
-        <v>46298.899305555547</v>
+        <v>46302.274305555547</v>
       </c>
       <c r="F225" s="5" t="s">
         <v>47</v>
@@ -6188,19 +6174,19 @@
     </row>
     <row r="226" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A226" s="3">
-        <v>225</v>
+        <v>243</v>
       </c>
       <c r="B226" t="s">
-        <v>244</v>
+        <v>262</v>
       </c>
       <c r="C226" t="s">
         <v>9</v>
       </c>
       <c r="D226" t="s">
-        <v>244</v>
+        <v>262</v>
       </c>
       <c r="E226" s="8">
-        <v>46299.024305555547</v>
+        <v>46302.732638888891</v>
       </c>
       <c r="F226" s="5" t="s">
         <v>47</v>
@@ -6208,19 +6194,19 @@
     </row>
     <row r="227" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A227" s="3">
-        <v>226</v>
+        <v>244</v>
       </c>
       <c r="B227" t="s">
-        <v>245</v>
+        <v>263</v>
       </c>
       <c r="C227" t="s">
         <v>9</v>
       </c>
       <c r="D227" t="s">
-        <v>245</v>
+        <v>263</v>
       </c>
       <c r="E227" s="8">
-        <v>46299.190972222219</v>
+        <v>46302.899305555547</v>
       </c>
       <c r="F227" s="5" t="s">
         <v>47</v>
@@ -6228,19 +6214,19 @@
     </row>
     <row r="228" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A228" s="3">
-        <v>227</v>
+        <v>245</v>
       </c>
       <c r="B228" t="s">
-        <v>246</v>
+        <v>264</v>
       </c>
       <c r="C228" t="s">
         <v>9</v>
       </c>
       <c r="D228" t="s">
-        <v>246</v>
+        <v>264</v>
       </c>
       <c r="E228" s="8">
-        <v>46299.274305555547</v>
+        <v>46303.024305555547</v>
       </c>
       <c r="F228" s="5" t="s">
         <v>47</v>
@@ -6248,19 +6234,19 @@
     </row>
     <row r="229" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A229" s="3">
-        <v>228</v>
+        <v>246</v>
       </c>
       <c r="B229" t="s">
-        <v>247</v>
+        <v>265</v>
       </c>
       <c r="C229" t="s">
         <v>9</v>
       </c>
       <c r="D229" t="s">
-        <v>247</v>
+        <v>265</v>
       </c>
       <c r="E229" s="8">
-        <v>46299.732638888891</v>
+        <v>46303.190972222219</v>
       </c>
       <c r="F229" s="5" t="s">
         <v>47</v>
@@ -6268,19 +6254,19 @@
     </row>
     <row r="230" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A230" s="3">
-        <v>229</v>
+        <v>247</v>
       </c>
       <c r="B230" t="s">
-        <v>248</v>
+        <v>266</v>
       </c>
       <c r="C230" t="s">
         <v>9</v>
       </c>
       <c r="D230" t="s">
-        <v>248</v>
+        <v>266</v>
       </c>
       <c r="E230" s="8">
-        <v>46299.899305555547</v>
+        <v>46303.274305555547</v>
       </c>
       <c r="F230" s="5" t="s">
         <v>47</v>
@@ -6288,19 +6274,19 @@
     </row>
     <row r="231" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A231" s="3">
-        <v>230</v>
+        <v>248</v>
       </c>
       <c r="B231" t="s">
-        <v>249</v>
+        <v>267</v>
       </c>
       <c r="C231" t="s">
         <v>9</v>
       </c>
       <c r="D231" t="s">
-        <v>249</v>
+        <v>267</v>
       </c>
       <c r="E231" s="8">
-        <v>46300.024305555547</v>
+        <v>46303.732638888891</v>
       </c>
       <c r="F231" s="5" t="s">
         <v>47</v>
@@ -6308,19 +6294,19 @@
     </row>
     <row r="232" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A232" s="3">
-        <v>231</v>
+        <v>249</v>
       </c>
       <c r="B232" t="s">
-        <v>250</v>
+        <v>268</v>
       </c>
       <c r="C232" t="s">
         <v>9</v>
       </c>
       <c r="D232" t="s">
-        <v>250</v>
+        <v>268</v>
       </c>
       <c r="E232" s="8">
-        <v>46300.190972222219</v>
+        <v>46303.899305555547</v>
       </c>
       <c r="F232" s="5" t="s">
         <v>47</v>
@@ -6328,19 +6314,19 @@
     </row>
     <row r="233" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A233" s="3">
-        <v>232</v>
+        <v>250</v>
       </c>
       <c r="B233" t="s">
-        <v>251</v>
+        <v>269</v>
       </c>
       <c r="C233" t="s">
         <v>9</v>
       </c>
       <c r="D233" t="s">
-        <v>251</v>
+        <v>269</v>
       </c>
       <c r="E233" s="8">
-        <v>46300.274305555547</v>
+        <v>46304.024305555547</v>
       </c>
       <c r="F233" s="5" t="s">
         <v>47</v>
@@ -6348,19 +6334,19 @@
     </row>
     <row r="234" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A234" s="3">
-        <v>233</v>
+        <v>251</v>
       </c>
       <c r="B234" t="s">
-        <v>252</v>
+        <v>270</v>
       </c>
       <c r="C234" t="s">
         <v>9</v>
       </c>
       <c r="D234" t="s">
-        <v>252</v>
+        <v>270</v>
       </c>
       <c r="E234" s="8">
-        <v>46300.732638888891</v>
+        <v>46304.190972222219</v>
       </c>
       <c r="F234" s="5" t="s">
         <v>47</v>
@@ -6368,19 +6354,19 @@
     </row>
     <row r="235" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A235" s="3">
-        <v>234</v>
+        <v>252</v>
       </c>
       <c r="B235" t="s">
-        <v>253</v>
+        <v>271</v>
       </c>
       <c r="C235" t="s">
         <v>9</v>
       </c>
       <c r="D235" t="s">
-        <v>253</v>
+        <v>271</v>
       </c>
       <c r="E235" s="8">
-        <v>46300.899305555547</v>
+        <v>46304.274305555547</v>
       </c>
       <c r="F235" s="5" t="s">
         <v>47</v>
@@ -6388,19 +6374,19 @@
     </row>
     <row r="236" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A236" s="3">
-        <v>235</v>
+        <v>253</v>
       </c>
       <c r="B236" t="s">
-        <v>254</v>
+        <v>272</v>
       </c>
       <c r="C236" t="s">
         <v>9</v>
       </c>
       <c r="D236" t="s">
-        <v>254</v>
+        <v>272</v>
       </c>
       <c r="E236" s="8">
-        <v>46301.024305555547</v>
+        <v>46304.732638888891</v>
       </c>
       <c r="F236" s="5" t="s">
         <v>47</v>
@@ -6408,19 +6394,19 @@
     </row>
     <row r="237" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A237" s="3">
-        <v>236</v>
+        <v>254</v>
       </c>
       <c r="B237" t="s">
-        <v>255</v>
+        <v>273</v>
       </c>
       <c r="C237" t="s">
         <v>9</v>
       </c>
       <c r="D237" t="s">
-        <v>255</v>
+        <v>273</v>
       </c>
       <c r="E237" s="8">
-        <v>46301.190972222219</v>
+        <v>46304.899305555547</v>
       </c>
       <c r="F237" s="5" t="s">
         <v>47</v>
@@ -6428,19 +6414,19 @@
     </row>
     <row r="238" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A238" s="3">
-        <v>237</v>
+        <v>255</v>
       </c>
       <c r="B238" t="s">
-        <v>256</v>
+        <v>274</v>
       </c>
       <c r="C238" t="s">
         <v>9</v>
       </c>
       <c r="D238" t="s">
-        <v>256</v>
+        <v>274</v>
       </c>
       <c r="E238" s="8">
-        <v>46301.274305555547</v>
+        <v>46305.024305555547</v>
       </c>
       <c r="F238" s="5" t="s">
         <v>47</v>
@@ -6448,19 +6434,19 @@
     </row>
     <row r="239" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A239" s="3">
-        <v>238</v>
+        <v>256</v>
       </c>
       <c r="B239" t="s">
-        <v>257</v>
+        <v>275</v>
       </c>
       <c r="C239" t="s">
         <v>9</v>
       </c>
       <c r="D239" t="s">
-        <v>257</v>
+        <v>275</v>
       </c>
       <c r="E239" s="8">
-        <v>46301.732638888891</v>
+        <v>46305.190972222219</v>
       </c>
       <c r="F239" s="5" t="s">
         <v>47</v>
@@ -6468,19 +6454,19 @@
     </row>
     <row r="240" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A240" s="3">
-        <v>239</v>
+        <v>257</v>
       </c>
       <c r="B240" t="s">
-        <v>258</v>
+        <v>276</v>
       </c>
       <c r="C240" t="s">
         <v>9</v>
       </c>
       <c r="D240" t="s">
-        <v>258</v>
+        <v>276</v>
       </c>
       <c r="E240" s="8">
-        <v>46301.899305555547</v>
+        <v>46305.274305555547</v>
       </c>
       <c r="F240" s="5" t="s">
         <v>47</v>
@@ -6488,19 +6474,19 @@
     </row>
     <row r="241" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A241" s="3">
-        <v>240</v>
+        <v>258</v>
       </c>
       <c r="B241" t="s">
-        <v>259</v>
+        <v>277</v>
       </c>
       <c r="C241" t="s">
         <v>9</v>
       </c>
       <c r="D241" t="s">
-        <v>259</v>
+        <v>277</v>
       </c>
       <c r="E241" s="8">
-        <v>46302.024305555547</v>
+        <v>46305.732638888891</v>
       </c>
       <c r="F241" s="5" t="s">
         <v>47</v>
@@ -6508,19 +6494,19 @@
     </row>
     <row r="242" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A242" s="3">
-        <v>241</v>
+        <v>259</v>
       </c>
       <c r="B242" t="s">
-        <v>260</v>
+        <v>278</v>
       </c>
       <c r="C242" t="s">
         <v>9</v>
       </c>
       <c r="D242" t="s">
-        <v>260</v>
+        <v>278</v>
       </c>
       <c r="E242" s="8">
-        <v>46302.190972222219</v>
+        <v>46305.899305555547</v>
       </c>
       <c r="F242" s="5" t="s">
         <v>47</v>
@@ -6528,19 +6514,19 @@
     </row>
     <row r="243" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A243" s="3">
-        <v>242</v>
+        <v>260</v>
       </c>
       <c r="B243" t="s">
-        <v>261</v>
+        <v>279</v>
       </c>
       <c r="C243" t="s">
         <v>9</v>
       </c>
       <c r="D243" t="s">
-        <v>261</v>
+        <v>279</v>
       </c>
       <c r="E243" s="8">
-        <v>46302.274305555547</v>
+        <v>46306.024305555547</v>
       </c>
       <c r="F243" s="5" t="s">
         <v>47</v>
@@ -6548,19 +6534,19 @@
     </row>
     <row r="244" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A244" s="3">
-        <v>243</v>
+        <v>261</v>
       </c>
       <c r="B244" t="s">
-        <v>262</v>
+        <v>280</v>
       </c>
       <c r="C244" t="s">
         <v>9</v>
       </c>
       <c r="D244" t="s">
-        <v>262</v>
+        <v>280</v>
       </c>
       <c r="E244" s="8">
-        <v>46302.732638888891</v>
+        <v>46306.190972222219</v>
       </c>
       <c r="F244" s="5" t="s">
         <v>47</v>
@@ -6568,19 +6554,19 @@
     </row>
     <row r="245" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A245" s="3">
-        <v>244</v>
+        <v>262</v>
       </c>
       <c r="B245" t="s">
-        <v>263</v>
+        <v>281</v>
       </c>
       <c r="C245" t="s">
         <v>9</v>
       </c>
       <c r="D245" t="s">
-        <v>263</v>
+        <v>281</v>
       </c>
       <c r="E245" s="8">
-        <v>46302.899305555547</v>
+        <v>46306.274305555547</v>
       </c>
       <c r="F245" s="5" t="s">
         <v>47</v>
@@ -6588,19 +6574,19 @@
     </row>
     <row r="246" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A246" s="3">
-        <v>245</v>
+        <v>263</v>
       </c>
       <c r="B246" t="s">
-        <v>264</v>
+        <v>282</v>
       </c>
       <c r="C246" t="s">
         <v>9</v>
       </c>
       <c r="D246" t="s">
-        <v>264</v>
+        <v>282</v>
       </c>
       <c r="E246" s="8">
-        <v>46303.024305555547</v>
+        <v>46306.732638888891</v>
       </c>
       <c r="F246" s="5" t="s">
         <v>47</v>
@@ -6608,19 +6594,19 @@
     </row>
     <row r="247" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A247" s="3">
-        <v>246</v>
+        <v>264</v>
       </c>
       <c r="B247" t="s">
-        <v>265</v>
+        <v>283</v>
       </c>
       <c r="C247" t="s">
         <v>9</v>
       </c>
       <c r="D247" t="s">
-        <v>265</v>
+        <v>283</v>
       </c>
       <c r="E247" s="8">
-        <v>46303.190972222219</v>
+        <v>46306.899305555547</v>
       </c>
       <c r="F247" s="5" t="s">
         <v>47</v>
@@ -6628,19 +6614,19 @@
     </row>
     <row r="248" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A248" s="3">
-        <v>247</v>
+        <v>265</v>
       </c>
       <c r="B248" t="s">
-        <v>266</v>
+        <v>284</v>
       </c>
       <c r="C248" t="s">
         <v>9</v>
       </c>
       <c r="D248" t="s">
-        <v>266</v>
+        <v>284</v>
       </c>
       <c r="E248" s="8">
-        <v>46303.274305555547</v>
+        <v>46307.024305555547</v>
       </c>
       <c r="F248" s="5" t="s">
         <v>47</v>
@@ -6648,19 +6634,19 @@
     </row>
     <row r="249" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A249" s="3">
-        <v>248</v>
+        <v>266</v>
       </c>
       <c r="B249" t="s">
-        <v>267</v>
+        <v>285</v>
       </c>
       <c r="C249" t="s">
         <v>9</v>
       </c>
       <c r="D249" t="s">
-        <v>267</v>
+        <v>285</v>
       </c>
       <c r="E249" s="8">
-        <v>46303.732638888891</v>
+        <v>46307.190972222219</v>
       </c>
       <c r="F249" s="5" t="s">
         <v>47</v>
@@ -6668,19 +6654,19 @@
     </row>
     <row r="250" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A250" s="3">
-        <v>249</v>
+        <v>267</v>
       </c>
       <c r="B250" t="s">
-        <v>268</v>
+        <v>286</v>
       </c>
       <c r="C250" t="s">
         <v>9</v>
       </c>
       <c r="D250" t="s">
-        <v>268</v>
+        <v>286</v>
       </c>
       <c r="E250" s="8">
-        <v>46303.899305555547</v>
+        <v>46307.274305555547</v>
       </c>
       <c r="F250" s="5" t="s">
         <v>47</v>
@@ -6688,19 +6674,19 @@
     </row>
     <row r="251" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A251" s="3">
-        <v>250</v>
+        <v>268</v>
       </c>
       <c r="B251" t="s">
-        <v>269</v>
+        <v>287</v>
       </c>
       <c r="C251" t="s">
         <v>9</v>
       </c>
       <c r="D251" t="s">
-        <v>269</v>
-      </c>
-      <c r="E251" s="8">
-        <v>46304.024305555547</v>
+        <v>287</v>
+      </c>
+      <c r="E251" s="4">
+        <v>46307.732638888891</v>
       </c>
       <c r="F251" s="5" t="s">
         <v>47</v>
@@ -6708,19 +6694,19 @@
     </row>
     <row r="252" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A252" s="3">
-        <v>251</v>
+        <v>269</v>
       </c>
       <c r="B252" t="s">
-        <v>270</v>
+        <v>288</v>
       </c>
       <c r="C252" t="s">
         <v>9</v>
       </c>
       <c r="D252" t="s">
-        <v>270</v>
+        <v>288</v>
       </c>
       <c r="E252" s="8">
-        <v>46304.190972222219</v>
+        <v>46307.899305555547</v>
       </c>
       <c r="F252" s="5" t="s">
         <v>47</v>
@@ -6728,19 +6714,19 @@
     </row>
     <row r="253" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A253" s="3">
-        <v>252</v>
+        <v>270</v>
       </c>
       <c r="B253" t="s">
-        <v>271</v>
+        <v>289</v>
       </c>
       <c r="C253" t="s">
         <v>9</v>
       </c>
       <c r="D253" t="s">
-        <v>271</v>
+        <v>289</v>
       </c>
       <c r="E253" s="8">
-        <v>46304.274305555547</v>
+        <v>46308.024305555547</v>
       </c>
       <c r="F253" s="5" t="s">
         <v>47</v>
@@ -6748,19 +6734,19 @@
     </row>
     <row r="254" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A254" s="3">
-        <v>253</v>
+        <v>271</v>
       </c>
       <c r="B254" t="s">
-        <v>272</v>
+        <v>290</v>
       </c>
       <c r="C254" t="s">
         <v>9</v>
       </c>
       <c r="D254" t="s">
-        <v>272</v>
+        <v>290</v>
       </c>
       <c r="E254" s="8">
-        <v>46304.732638888891</v>
+        <v>46308.190972222219</v>
       </c>
       <c r="F254" s="5" t="s">
         <v>47</v>
@@ -6768,19 +6754,19 @@
     </row>
     <row r="255" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A255" s="3">
-        <v>254</v>
+        <v>272</v>
       </c>
       <c r="B255" t="s">
-        <v>273</v>
+        <v>291</v>
       </c>
       <c r="C255" t="s">
         <v>9</v>
       </c>
       <c r="D255" t="s">
-        <v>273</v>
+        <v>291</v>
       </c>
       <c r="E255" s="8">
-        <v>46304.899305555547</v>
+        <v>46308.274305555547</v>
       </c>
       <c r="F255" s="5" t="s">
         <v>47</v>
@@ -6788,19 +6774,19 @@
     </row>
     <row r="256" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A256" s="3">
-        <v>255</v>
+        <v>273</v>
       </c>
       <c r="B256" t="s">
-        <v>274</v>
+        <v>292</v>
       </c>
       <c r="C256" t="s">
         <v>9</v>
       </c>
       <c r="D256" t="s">
-        <v>274</v>
+        <v>292</v>
       </c>
       <c r="E256" s="8">
-        <v>46305.024305555547</v>
+        <v>46308.732638888891</v>
       </c>
       <c r="F256" s="5" t="s">
         <v>47</v>
@@ -6808,19 +6794,19 @@
     </row>
     <row r="257" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A257" s="3">
-        <v>256</v>
+        <v>274</v>
       </c>
       <c r="B257" t="s">
-        <v>275</v>
+        <v>293</v>
       </c>
       <c r="C257" t="s">
         <v>9</v>
       </c>
       <c r="D257" t="s">
-        <v>275</v>
+        <v>293</v>
       </c>
       <c r="E257" s="8">
-        <v>46305.190972222219</v>
+        <v>46308.899305555547</v>
       </c>
       <c r="F257" s="5" t="s">
         <v>47</v>
@@ -6828,19 +6814,19 @@
     </row>
     <row r="258" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A258" s="3">
-        <v>257</v>
+        <v>275</v>
       </c>
       <c r="B258" t="s">
-        <v>276</v>
+        <v>294</v>
       </c>
       <c r="C258" t="s">
         <v>9</v>
       </c>
       <c r="D258" t="s">
-        <v>276</v>
+        <v>294</v>
       </c>
       <c r="E258" s="8">
-        <v>46305.274305555547</v>
+        <v>46309.024305555547</v>
       </c>
       <c r="F258" s="5" t="s">
         <v>47</v>
@@ -6848,19 +6834,19 @@
     </row>
     <row r="259" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A259" s="3">
-        <v>258</v>
+        <v>276</v>
       </c>
       <c r="B259" t="s">
-        <v>277</v>
+        <v>295</v>
       </c>
       <c r="C259" t="s">
         <v>9</v>
       </c>
       <c r="D259" t="s">
-        <v>277</v>
+        <v>295</v>
       </c>
       <c r="E259" s="8">
-        <v>46305.732638888891</v>
+        <v>46309.190972222219</v>
       </c>
       <c r="F259" s="5" t="s">
         <v>47</v>
@@ -6868,19 +6854,19 @@
     </row>
     <row r="260" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A260" s="3">
-        <v>259</v>
+        <v>277</v>
       </c>
       <c r="B260" t="s">
-        <v>278</v>
+        <v>296</v>
       </c>
       <c r="C260" t="s">
         <v>9</v>
       </c>
       <c r="D260" t="s">
-        <v>278</v>
+        <v>296</v>
       </c>
       <c r="E260" s="8">
-        <v>46305.899305555547</v>
+        <v>46309.274305555547</v>
       </c>
       <c r="F260" s="5" t="s">
         <v>47</v>
@@ -6888,19 +6874,19 @@
     </row>
     <row r="261" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A261" s="3">
-        <v>260</v>
+        <v>278</v>
       </c>
       <c r="B261" t="s">
-        <v>279</v>
+        <v>297</v>
       </c>
       <c r="C261" t="s">
         <v>9</v>
       </c>
       <c r="D261" t="s">
-        <v>279</v>
+        <v>297</v>
       </c>
       <c r="E261" s="8">
-        <v>46306.024305555547</v>
+        <v>46309.732638888891</v>
       </c>
       <c r="F261" s="5" t="s">
         <v>47</v>
@@ -6908,19 +6894,19 @@
     </row>
     <row r="262" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A262" s="3">
-        <v>261</v>
+        <v>279</v>
       </c>
       <c r="B262" t="s">
-        <v>280</v>
+        <v>298</v>
       </c>
       <c r="C262" t="s">
         <v>9</v>
       </c>
       <c r="D262" t="s">
-        <v>280</v>
+        <v>298</v>
       </c>
       <c r="E262" s="8">
-        <v>46306.190972222219</v>
+        <v>46309.899305555547</v>
       </c>
       <c r="F262" s="5" t="s">
         <v>47</v>
@@ -6928,19 +6914,19 @@
     </row>
     <row r="263" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A263" s="3">
-        <v>262</v>
+        <v>280</v>
       </c>
       <c r="B263" t="s">
-        <v>281</v>
+        <v>299</v>
       </c>
       <c r="C263" t="s">
         <v>9</v>
       </c>
       <c r="D263" t="s">
-        <v>281</v>
+        <v>299</v>
       </c>
       <c r="E263" s="8">
-        <v>46306.274305555547</v>
+        <v>46310.024305555547</v>
       </c>
       <c r="F263" s="5" t="s">
         <v>47</v>
@@ -6948,19 +6934,19 @@
     </row>
     <row r="264" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A264" s="3">
-        <v>263</v>
+        <v>281</v>
       </c>
       <c r="B264" t="s">
-        <v>282</v>
+        <v>300</v>
       </c>
       <c r="C264" t="s">
         <v>9</v>
       </c>
       <c r="D264" t="s">
-        <v>282</v>
+        <v>300</v>
       </c>
       <c r="E264" s="8">
-        <v>46306.732638888891</v>
+        <v>46310.190972222219</v>
       </c>
       <c r="F264" s="5" t="s">
         <v>47</v>
@@ -6968,19 +6954,19 @@
     </row>
     <row r="265" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A265" s="3">
-        <v>264</v>
+        <v>282</v>
       </c>
       <c r="B265" t="s">
-        <v>283</v>
+        <v>301</v>
       </c>
       <c r="C265" t="s">
         <v>9</v>
       </c>
       <c r="D265" t="s">
-        <v>283</v>
+        <v>301</v>
       </c>
       <c r="E265" s="8">
-        <v>46306.899305555547</v>
+        <v>46310.274305555547</v>
       </c>
       <c r="F265" s="5" t="s">
         <v>47</v>
@@ -6988,19 +6974,19 @@
     </row>
     <row r="266" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A266" s="3">
-        <v>265</v>
+        <v>283</v>
       </c>
       <c r="B266" t="s">
-        <v>284</v>
+        <v>302</v>
       </c>
       <c r="C266" t="s">
         <v>9</v>
       </c>
       <c r="D266" t="s">
-        <v>284</v>
+        <v>302</v>
       </c>
       <c r="E266" s="8">
-        <v>46307.024305555547</v>
+        <v>46310.732638888891</v>
       </c>
       <c r="F266" s="5" t="s">
         <v>47</v>
@@ -7008,19 +6994,19 @@
     </row>
     <row r="267" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A267" s="3">
-        <v>266</v>
+        <v>284</v>
       </c>
       <c r="B267" t="s">
-        <v>285</v>
+        <v>303</v>
       </c>
       <c r="C267" t="s">
         <v>9</v>
       </c>
       <c r="D267" t="s">
-        <v>285</v>
+        <v>303</v>
       </c>
       <c r="E267" s="8">
-        <v>46307.190972222219</v>
+        <v>46310.899305555547</v>
       </c>
       <c r="F267" s="5" t="s">
         <v>47</v>
@@ -7028,19 +7014,19 @@
     </row>
     <row r="268" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A268" s="3">
-        <v>267</v>
+        <v>285</v>
       </c>
       <c r="B268" t="s">
-        <v>286</v>
+        <v>304</v>
       </c>
       <c r="C268" t="s">
         <v>9</v>
       </c>
       <c r="D268" t="s">
-        <v>286</v>
+        <v>304</v>
       </c>
       <c r="E268" s="8">
-        <v>46307.274305555547</v>
+        <v>46311.024305555547</v>
       </c>
       <c r="F268" s="5" t="s">
         <v>47</v>
@@ -7048,19 +7034,19 @@
     </row>
     <row r="269" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A269" s="3">
-        <v>268</v>
+        <v>286</v>
       </c>
       <c r="B269" t="s">
-        <v>287</v>
+        <v>305</v>
       </c>
       <c r="C269" t="s">
         <v>9</v>
       </c>
       <c r="D269" t="s">
-        <v>287</v>
-      </c>
-      <c r="E269" s="4">
-        <v>46307.732638888891</v>
+        <v>305</v>
+      </c>
+      <c r="E269" s="8">
+        <v>46311.190972222219</v>
       </c>
       <c r="F269" s="5" t="s">
         <v>47</v>
@@ -7068,19 +7054,19 @@
     </row>
     <row r="270" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A270" s="3">
-        <v>269</v>
+        <v>287</v>
       </c>
       <c r="B270" t="s">
-        <v>288</v>
+        <v>306</v>
       </c>
       <c r="C270" t="s">
         <v>9</v>
       </c>
       <c r="D270" t="s">
-        <v>288</v>
+        <v>306</v>
       </c>
       <c r="E270" s="8">
-        <v>46307.899305555547</v>
+        <v>46311.274305555547</v>
       </c>
       <c r="F270" s="5" t="s">
         <v>47</v>
@@ -7088,19 +7074,19 @@
     </row>
     <row r="271" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A271" s="3">
-        <v>270</v>
+        <v>288</v>
       </c>
       <c r="B271" t="s">
-        <v>289</v>
+        <v>307</v>
       </c>
       <c r="C271" t="s">
         <v>9</v>
       </c>
       <c r="D271" t="s">
-        <v>289</v>
+        <v>307</v>
       </c>
       <c r="E271" s="8">
-        <v>46308.024305555547</v>
+        <v>46311.732638888891</v>
       </c>
       <c r="F271" s="5" t="s">
         <v>47</v>
@@ -7108,19 +7094,19 @@
     </row>
     <row r="272" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A272" s="3">
-        <v>271</v>
+        <v>289</v>
       </c>
       <c r="B272" t="s">
-        <v>290</v>
+        <v>308</v>
       </c>
       <c r="C272" t="s">
         <v>9</v>
       </c>
       <c r="D272" t="s">
-        <v>290</v>
+        <v>308</v>
       </c>
       <c r="E272" s="8">
-        <v>46308.190972222219</v>
+        <v>46311.899305555547</v>
       </c>
       <c r="F272" s="5" t="s">
         <v>47</v>
@@ -7128,19 +7114,19 @@
     </row>
     <row r="273" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A273" s="3">
-        <v>272</v>
+        <v>290</v>
       </c>
       <c r="B273" t="s">
-        <v>291</v>
+        <v>309</v>
       </c>
       <c r="C273" t="s">
         <v>9</v>
       </c>
       <c r="D273" t="s">
-        <v>291</v>
+        <v>309</v>
       </c>
       <c r="E273" s="8">
-        <v>46308.274305555547</v>
+        <v>46312.024305555547</v>
       </c>
       <c r="F273" s="5" t="s">
         <v>47</v>
@@ -7148,19 +7134,19 @@
     </row>
     <row r="274" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A274" s="3">
-        <v>273</v>
+        <v>291</v>
       </c>
       <c r="B274" t="s">
-        <v>292</v>
+        <v>310</v>
       </c>
       <c r="C274" t="s">
         <v>9</v>
       </c>
       <c r="D274" t="s">
-        <v>292</v>
+        <v>310</v>
       </c>
       <c r="E274" s="8">
-        <v>46308.732638888891</v>
+        <v>46312.190972222219</v>
       </c>
       <c r="F274" s="5" t="s">
         <v>47</v>
@@ -7168,19 +7154,19 @@
     </row>
     <row r="275" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A275" s="3">
-        <v>274</v>
+        <v>292</v>
       </c>
       <c r="B275" t="s">
-        <v>293</v>
+        <v>311</v>
       </c>
       <c r="C275" t="s">
         <v>9</v>
       </c>
       <c r="D275" t="s">
-        <v>293</v>
+        <v>311</v>
       </c>
       <c r="E275" s="8">
-        <v>46308.899305555547</v>
+        <v>46312.274305555547</v>
       </c>
       <c r="F275" s="5" t="s">
         <v>47</v>
@@ -7188,19 +7174,19 @@
     </row>
     <row r="276" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A276" s="3">
-        <v>275</v>
+        <v>293</v>
       </c>
       <c r="B276" t="s">
-        <v>294</v>
+        <v>312</v>
       </c>
       <c r="C276" t="s">
         <v>9</v>
       </c>
       <c r="D276" t="s">
-        <v>294</v>
+        <v>312</v>
       </c>
       <c r="E276" s="8">
-        <v>46309.024305555547</v>
+        <v>46312.732638888891</v>
       </c>
       <c r="F276" s="5" t="s">
         <v>47</v>
@@ -7208,19 +7194,19 @@
     </row>
     <row r="277" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A277" s="3">
-        <v>276</v>
+        <v>294</v>
       </c>
       <c r="B277" t="s">
-        <v>295</v>
+        <v>313</v>
       </c>
       <c r="C277" t="s">
         <v>9</v>
       </c>
       <c r="D277" t="s">
-        <v>295</v>
+        <v>313</v>
       </c>
       <c r="E277" s="8">
-        <v>46309.190972222219</v>
+        <v>46312.899305555547</v>
       </c>
       <c r="F277" s="5" t="s">
         <v>47</v>
@@ -7228,19 +7214,19 @@
     </row>
     <row r="278" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A278" s="3">
-        <v>277</v>
+        <v>295</v>
       </c>
       <c r="B278" t="s">
-        <v>296</v>
+        <v>314</v>
       </c>
       <c r="C278" t="s">
         <v>9</v>
       </c>
       <c r="D278" t="s">
-        <v>296</v>
+        <v>314</v>
       </c>
       <c r="E278" s="8">
-        <v>46309.274305555547</v>
+        <v>46313.024305555547</v>
       </c>
       <c r="F278" s="5" t="s">
         <v>47</v>
@@ -7248,19 +7234,19 @@
     </row>
     <row r="279" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A279" s="3">
-        <v>278</v>
+        <v>296</v>
       </c>
       <c r="B279" t="s">
-        <v>297</v>
+        <v>315</v>
       </c>
       <c r="C279" t="s">
         <v>9</v>
       </c>
       <c r="D279" t="s">
-        <v>297</v>
+        <v>315</v>
       </c>
       <c r="E279" s="8">
-        <v>46309.732638888891</v>
+        <v>46313.190972222219</v>
       </c>
       <c r="F279" s="5" t="s">
         <v>47</v>
@@ -7268,19 +7254,19 @@
     </row>
     <row r="280" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A280" s="3">
-        <v>279</v>
+        <v>297</v>
       </c>
       <c r="B280" t="s">
-        <v>298</v>
+        <v>316</v>
       </c>
       <c r="C280" t="s">
         <v>9</v>
       </c>
       <c r="D280" t="s">
-        <v>298</v>
+        <v>316</v>
       </c>
       <c r="E280" s="8">
-        <v>46309.899305555547</v>
+        <v>46313.274305555547</v>
       </c>
       <c r="F280" s="5" t="s">
         <v>47</v>
@@ -7288,19 +7274,19 @@
     </row>
     <row r="281" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A281" s="3">
-        <v>280</v>
+        <v>298</v>
       </c>
       <c r="B281" t="s">
-        <v>299</v>
+        <v>317</v>
       </c>
       <c r="C281" t="s">
         <v>9</v>
       </c>
       <c r="D281" t="s">
-        <v>299</v>
+        <v>317</v>
       </c>
       <c r="E281" s="8">
-        <v>46310.024305555547</v>
+        <v>46313.732638888891</v>
       </c>
       <c r="F281" s="5" t="s">
         <v>47</v>
@@ -7308,19 +7294,19 @@
     </row>
     <row r="282" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A282" s="3">
-        <v>281</v>
+        <v>299</v>
       </c>
       <c r="B282" t="s">
-        <v>300</v>
+        <v>318</v>
       </c>
       <c r="C282" t="s">
         <v>9</v>
       </c>
       <c r="D282" t="s">
-        <v>300</v>
+        <v>318</v>
       </c>
       <c r="E282" s="8">
-        <v>46310.190972222219</v>
+        <v>46313.899305555547</v>
       </c>
       <c r="F282" s="5" t="s">
         <v>47</v>
@@ -7328,19 +7314,19 @@
     </row>
     <row r="283" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A283" s="3">
-        <v>282</v>
+        <v>300</v>
       </c>
       <c r="B283" t="s">
-        <v>301</v>
+        <v>319</v>
       </c>
       <c r="C283" t="s">
         <v>9</v>
       </c>
       <c r="D283" t="s">
-        <v>301</v>
+        <v>319</v>
       </c>
       <c r="E283" s="8">
-        <v>46310.274305555547</v>
+        <v>46314.024305555547</v>
       </c>
       <c r="F283" s="5" t="s">
         <v>47</v>
@@ -7348,19 +7334,19 @@
     </row>
     <row r="284" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A284" s="3">
-        <v>283</v>
+        <v>301</v>
       </c>
       <c r="B284" t="s">
-        <v>302</v>
+        <v>320</v>
       </c>
       <c r="C284" t="s">
         <v>9</v>
       </c>
       <c r="D284" t="s">
-        <v>302</v>
+        <v>320</v>
       </c>
       <c r="E284" s="8">
-        <v>46310.732638888891</v>
+        <v>46314.190972222219</v>
       </c>
       <c r="F284" s="5" t="s">
         <v>47</v>
@@ -7368,19 +7354,19 @@
     </row>
     <row r="285" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A285" s="3">
-        <v>284</v>
+        <v>302</v>
       </c>
       <c r="B285" t="s">
-        <v>303</v>
+        <v>321</v>
       </c>
       <c r="C285" t="s">
         <v>9</v>
       </c>
       <c r="D285" t="s">
-        <v>303</v>
+        <v>321</v>
       </c>
       <c r="E285" s="8">
-        <v>46310.899305555547</v>
+        <v>46314.274305555547</v>
       </c>
       <c r="F285" s="5" t="s">
         <v>47</v>
@@ -7388,19 +7374,19 @@
     </row>
     <row r="286" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A286" s="3">
-        <v>285</v>
+        <v>303</v>
       </c>
       <c r="B286" t="s">
-        <v>304</v>
+        <v>322</v>
       </c>
       <c r="C286" t="s">
         <v>9</v>
       </c>
       <c r="D286" t="s">
-        <v>304</v>
+        <v>322</v>
       </c>
       <c r="E286" s="8">
-        <v>46311.024305555547</v>
+        <v>46314.732638888891</v>
       </c>
       <c r="F286" s="5" t="s">
         <v>47</v>
@@ -7408,19 +7394,19 @@
     </row>
     <row r="287" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A287" s="3">
-        <v>286</v>
+        <v>304</v>
       </c>
       <c r="B287" t="s">
-        <v>305</v>
+        <v>323</v>
       </c>
       <c r="C287" t="s">
         <v>9</v>
       </c>
       <c r="D287" t="s">
-        <v>305</v>
+        <v>323</v>
       </c>
       <c r="E287" s="8">
-        <v>46311.190972222219</v>
+        <v>46314.899305555547</v>
       </c>
       <c r="F287" s="5" t="s">
         <v>47</v>
@@ -7428,19 +7414,19 @@
     </row>
     <row r="288" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A288" s="3">
-        <v>287</v>
+        <v>305</v>
       </c>
       <c r="B288" t="s">
-        <v>306</v>
+        <v>324</v>
       </c>
       <c r="C288" t="s">
         <v>9</v>
       </c>
       <c r="D288" t="s">
-        <v>306</v>
+        <v>324</v>
       </c>
       <c r="E288" s="8">
-        <v>46311.274305555547</v>
+        <v>46315.024305555547</v>
       </c>
       <c r="F288" s="5" t="s">
         <v>47</v>
@@ -7448,19 +7434,19 @@
     </row>
     <row r="289" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A289" s="3">
-        <v>288</v>
+        <v>306</v>
       </c>
       <c r="B289" t="s">
-        <v>307</v>
+        <v>325</v>
       </c>
       <c r="C289" t="s">
         <v>9</v>
       </c>
       <c r="D289" t="s">
-        <v>307</v>
+        <v>325</v>
       </c>
       <c r="E289" s="8">
-        <v>46311.732638888891</v>
+        <v>46315.190972222219</v>
       </c>
       <c r="F289" s="5" t="s">
         <v>47</v>
@@ -7468,19 +7454,19 @@
     </row>
     <row r="290" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A290" s="3">
-        <v>289</v>
+        <v>307</v>
       </c>
       <c r="B290" t="s">
-        <v>308</v>
+        <v>326</v>
       </c>
       <c r="C290" t="s">
         <v>9</v>
       </c>
       <c r="D290" t="s">
-        <v>308</v>
+        <v>326</v>
       </c>
       <c r="E290" s="8">
-        <v>46311.899305555547</v>
+        <v>46315.274305555547</v>
       </c>
       <c r="F290" s="5" t="s">
         <v>47</v>
@@ -7488,19 +7474,19 @@
     </row>
     <row r="291" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A291" s="3">
-        <v>290</v>
+        <v>308</v>
       </c>
       <c r="B291" t="s">
-        <v>309</v>
+        <v>327</v>
       </c>
       <c r="C291" t="s">
         <v>9</v>
       </c>
       <c r="D291" t="s">
-        <v>309</v>
+        <v>327</v>
       </c>
       <c r="E291" s="8">
-        <v>46312.024305555547</v>
+        <v>46315.732638888891</v>
       </c>
       <c r="F291" s="5" t="s">
         <v>47</v>
@@ -7508,19 +7494,19 @@
     </row>
     <row r="292" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A292" s="3">
-        <v>291</v>
+        <v>309</v>
       </c>
       <c r="B292" t="s">
-        <v>310</v>
+        <v>328</v>
       </c>
       <c r="C292" t="s">
         <v>9</v>
       </c>
       <c r="D292" t="s">
-        <v>310</v>
+        <v>328</v>
       </c>
       <c r="E292" s="8">
-        <v>46312.190972222219</v>
+        <v>46315.899305555547</v>
       </c>
       <c r="F292" s="5" t="s">
         <v>47</v>
@@ -7528,19 +7514,19 @@
     </row>
     <row r="293" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A293" s="3">
-        <v>292</v>
+        <v>310</v>
       </c>
       <c r="B293" t="s">
-        <v>311</v>
+        <v>329</v>
       </c>
       <c r="C293" t="s">
         <v>9</v>
       </c>
       <c r="D293" t="s">
-        <v>311</v>
+        <v>329</v>
       </c>
       <c r="E293" s="8">
-        <v>46312.274305555547</v>
+        <v>46316.024305555547</v>
       </c>
       <c r="F293" s="5" t="s">
         <v>47</v>
@@ -7548,19 +7534,19 @@
     </row>
     <row r="294" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A294" s="3">
-        <v>293</v>
+        <v>311</v>
       </c>
       <c r="B294" t="s">
-        <v>312</v>
+        <v>330</v>
       </c>
       <c r="C294" t="s">
         <v>9</v>
       </c>
       <c r="D294" t="s">
-        <v>312</v>
+        <v>330</v>
       </c>
       <c r="E294" s="8">
-        <v>46312.732638888891</v>
+        <v>46316.190972222219</v>
       </c>
       <c r="F294" s="5" t="s">
         <v>47</v>
@@ -7568,19 +7554,19 @@
     </row>
     <row r="295" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A295" s="3">
-        <v>294</v>
+        <v>312</v>
       </c>
       <c r="B295" t="s">
-        <v>313</v>
+        <v>331</v>
       </c>
       <c r="C295" t="s">
         <v>9</v>
       </c>
       <c r="D295" t="s">
-        <v>313</v>
+        <v>331</v>
       </c>
       <c r="E295" s="8">
-        <v>46312.899305555547</v>
+        <v>46316.274305555547</v>
       </c>
       <c r="F295" s="5" t="s">
         <v>47</v>
@@ -7588,19 +7574,19 @@
     </row>
     <row r="296" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A296" s="3">
-        <v>295</v>
+        <v>313</v>
       </c>
       <c r="B296" t="s">
-        <v>314</v>
+        <v>332</v>
       </c>
       <c r="C296" t="s">
         <v>9</v>
       </c>
       <c r="D296" t="s">
-        <v>314</v>
+        <v>332</v>
       </c>
       <c r="E296" s="8">
-        <v>46313.024305555547</v>
+        <v>46316.732638888891</v>
       </c>
       <c r="F296" s="5" t="s">
         <v>47</v>
@@ -7608,19 +7594,19 @@
     </row>
     <row r="297" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A297" s="3">
-        <v>296</v>
+        <v>314</v>
       </c>
       <c r="B297" t="s">
-        <v>315</v>
+        <v>333</v>
       </c>
       <c r="C297" t="s">
         <v>9</v>
       </c>
       <c r="D297" t="s">
-        <v>315</v>
+        <v>333</v>
       </c>
       <c r="E297" s="8">
-        <v>46313.190972222219</v>
+        <v>46316.899305555547</v>
       </c>
       <c r="F297" s="5" t="s">
         <v>47</v>
@@ -7628,19 +7614,19 @@
     </row>
     <row r="298" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A298" s="3">
-        <v>297</v>
+        <v>315</v>
       </c>
       <c r="B298" t="s">
-        <v>316</v>
+        <v>334</v>
       </c>
       <c r="C298" t="s">
         <v>9</v>
       </c>
       <c r="D298" t="s">
-        <v>316</v>
+        <v>334</v>
       </c>
       <c r="E298" s="8">
-        <v>46313.274305555547</v>
+        <v>46317.024305555547</v>
       </c>
       <c r="F298" s="5" t="s">
         <v>47</v>
@@ -7648,19 +7634,19 @@
     </row>
     <row r="299" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A299" s="3">
-        <v>298</v>
+        <v>316</v>
       </c>
       <c r="B299" t="s">
-        <v>317</v>
+        <v>335</v>
       </c>
       <c r="C299" t="s">
         <v>9</v>
       </c>
       <c r="D299" t="s">
-        <v>317</v>
+        <v>335</v>
       </c>
       <c r="E299" s="8">
-        <v>46313.732638888891</v>
+        <v>46317.190972222219</v>
       </c>
       <c r="F299" s="5" t="s">
         <v>47</v>
@@ -7668,19 +7654,19 @@
     </row>
     <row r="300" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A300" s="3">
-        <v>299</v>
+        <v>317</v>
       </c>
       <c r="B300" t="s">
-        <v>318</v>
+        <v>336</v>
       </c>
       <c r="C300" t="s">
         <v>9</v>
       </c>
       <c r="D300" t="s">
-        <v>318</v>
+        <v>336</v>
       </c>
       <c r="E300" s="8">
-        <v>46313.899305555547</v>
+        <v>46317.274305555547</v>
       </c>
       <c r="F300" s="5" t="s">
         <v>47</v>
@@ -7688,19 +7674,19 @@
     </row>
     <row r="301" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A301" s="3">
-        <v>300</v>
+        <v>318</v>
       </c>
       <c r="B301" t="s">
-        <v>319</v>
+        <v>337</v>
       </c>
       <c r="C301" t="s">
         <v>9</v>
       </c>
       <c r="D301" t="s">
-        <v>319</v>
+        <v>337</v>
       </c>
       <c r="E301" s="8">
-        <v>46314.024305555547</v>
+        <v>46317.732638888891</v>
       </c>
       <c r="F301" s="5" t="s">
         <v>47</v>
@@ -7708,19 +7694,19 @@
     </row>
     <row r="302" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A302" s="3">
-        <v>301</v>
+        <v>319</v>
       </c>
       <c r="B302" t="s">
-        <v>320</v>
+        <v>338</v>
       </c>
       <c r="C302" t="s">
         <v>9</v>
       </c>
       <c r="D302" t="s">
-        <v>320</v>
+        <v>338</v>
       </c>
       <c r="E302" s="8">
-        <v>46314.190972222219</v>
+        <v>46317.899305555547</v>
       </c>
       <c r="F302" s="5" t="s">
         <v>47</v>
@@ -7728,19 +7714,19 @@
     </row>
     <row r="303" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A303" s="3">
-        <v>302</v>
+        <v>320</v>
       </c>
       <c r="B303" t="s">
-        <v>321</v>
+        <v>339</v>
       </c>
       <c r="C303" t="s">
         <v>9</v>
       </c>
       <c r="D303" t="s">
-        <v>321</v>
+        <v>339</v>
       </c>
       <c r="E303" s="8">
-        <v>46314.274305555547</v>
+        <v>46318.024305555547</v>
       </c>
       <c r="F303" s="5" t="s">
         <v>47</v>
@@ -7748,19 +7734,19 @@
     </row>
     <row r="304" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A304" s="3">
-        <v>303</v>
+        <v>321</v>
       </c>
       <c r="B304" t="s">
-        <v>322</v>
+        <v>340</v>
       </c>
       <c r="C304" t="s">
         <v>9</v>
       </c>
       <c r="D304" t="s">
-        <v>322</v>
+        <v>340</v>
       </c>
       <c r="E304" s="8">
-        <v>46314.732638888891</v>
+        <v>46318.190972222219</v>
       </c>
       <c r="F304" s="5" t="s">
         <v>47</v>
@@ -7768,19 +7754,19 @@
     </row>
     <row r="305" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A305" s="3">
-        <v>304</v>
+        <v>322</v>
       </c>
       <c r="B305" t="s">
-        <v>323</v>
+        <v>341</v>
       </c>
       <c r="C305" t="s">
         <v>9</v>
       </c>
       <c r="D305" t="s">
-        <v>323</v>
+        <v>341</v>
       </c>
       <c r="E305" s="8">
-        <v>46314.899305555547</v>
+        <v>46318.274305555547</v>
       </c>
       <c r="F305" s="5" t="s">
         <v>47</v>
@@ -7788,19 +7774,19 @@
     </row>
     <row r="306" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A306" s="3">
-        <v>305</v>
+        <v>323</v>
       </c>
       <c r="B306" t="s">
-        <v>324</v>
+        <v>342</v>
       </c>
       <c r="C306" t="s">
         <v>9</v>
       </c>
       <c r="D306" t="s">
-        <v>324</v>
+        <v>342</v>
       </c>
       <c r="E306" s="8">
-        <v>46315.024305555547</v>
+        <v>46318.732638888891</v>
       </c>
       <c r="F306" s="5" t="s">
         <v>47</v>
@@ -7808,19 +7794,19 @@
     </row>
     <row r="307" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A307" s="3">
-        <v>306</v>
+        <v>324</v>
       </c>
       <c r="B307" t="s">
-        <v>325</v>
+        <v>343</v>
       </c>
       <c r="C307" t="s">
         <v>9</v>
       </c>
       <c r="D307" t="s">
-        <v>325</v>
+        <v>343</v>
       </c>
       <c r="E307" s="8">
-        <v>46315.190972222219</v>
+        <v>46318.899305555547</v>
       </c>
       <c r="F307" s="5" t="s">
         <v>47</v>
@@ -7828,19 +7814,19 @@
     </row>
     <row r="308" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A308" s="3">
-        <v>307</v>
+        <v>325</v>
       </c>
       <c r="B308" t="s">
-        <v>326</v>
+        <v>344</v>
       </c>
       <c r="C308" t="s">
         <v>9</v>
       </c>
       <c r="D308" t="s">
-        <v>326</v>
+        <v>344</v>
       </c>
       <c r="E308" s="8">
-        <v>46315.274305555547</v>
+        <v>46319.024305555547</v>
       </c>
       <c r="F308" s="5" t="s">
         <v>47</v>
@@ -7848,19 +7834,19 @@
     </row>
     <row r="309" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A309" s="3">
-        <v>308</v>
+        <v>326</v>
       </c>
       <c r="B309" t="s">
-        <v>327</v>
+        <v>345</v>
       </c>
       <c r="C309" t="s">
         <v>9</v>
       </c>
       <c r="D309" t="s">
-        <v>327</v>
+        <v>345</v>
       </c>
       <c r="E309" s="8">
-        <v>46315.732638888891</v>
+        <v>46319.190972222219</v>
       </c>
       <c r="F309" s="5" t="s">
         <v>47</v>
@@ -7868,19 +7854,19 @@
     </row>
     <row r="310" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A310" s="3">
-        <v>309</v>
+        <v>327</v>
       </c>
       <c r="B310" t="s">
-        <v>328</v>
+        <v>346</v>
       </c>
       <c r="C310" t="s">
         <v>9</v>
       </c>
       <c r="D310" t="s">
-        <v>328</v>
+        <v>346</v>
       </c>
       <c r="E310" s="8">
-        <v>46315.899305555547</v>
+        <v>46319.274305555547</v>
       </c>
       <c r="F310" s="5" t="s">
         <v>47</v>
@@ -7888,19 +7874,19 @@
     </row>
     <row r="311" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A311" s="3">
-        <v>310</v>
+        <v>328</v>
       </c>
       <c r="B311" t="s">
-        <v>329</v>
+        <v>347</v>
       </c>
       <c r="C311" t="s">
         <v>9</v>
       </c>
       <c r="D311" t="s">
-        <v>329</v>
+        <v>347</v>
       </c>
       <c r="E311" s="8">
-        <v>46316.024305555547</v>
+        <v>46319.732638888891</v>
       </c>
       <c r="F311" s="5" t="s">
         <v>47</v>
@@ -7908,19 +7894,19 @@
     </row>
     <row r="312" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A312" s="3">
-        <v>311</v>
+        <v>329</v>
       </c>
       <c r="B312" t="s">
-        <v>330</v>
+        <v>348</v>
       </c>
       <c r="C312" t="s">
         <v>9</v>
       </c>
       <c r="D312" t="s">
-        <v>330</v>
+        <v>348</v>
       </c>
       <c r="E312" s="8">
-        <v>46316.190972222219</v>
+        <v>46319.899305555547</v>
       </c>
       <c r="F312" s="5" t="s">
         <v>47</v>
@@ -7928,19 +7914,19 @@
     </row>
     <row r="313" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A313" s="3">
-        <v>312</v>
+        <v>330</v>
       </c>
       <c r="B313" t="s">
-        <v>331</v>
+        <v>349</v>
       </c>
       <c r="C313" t="s">
         <v>9</v>
       </c>
       <c r="D313" t="s">
-        <v>331</v>
+        <v>349</v>
       </c>
       <c r="E313" s="8">
-        <v>46316.274305555547</v>
+        <v>46320.024305555547</v>
       </c>
       <c r="F313" s="5" t="s">
         <v>47</v>
@@ -7948,19 +7934,19 @@
     </row>
     <row r="314" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A314" s="3">
-        <v>313</v>
+        <v>331</v>
       </c>
       <c r="B314" t="s">
-        <v>332</v>
+        <v>350</v>
       </c>
       <c r="C314" t="s">
         <v>9</v>
       </c>
       <c r="D314" t="s">
-        <v>332</v>
+        <v>350</v>
       </c>
       <c r="E314" s="8">
-        <v>46316.732638888891</v>
+        <v>46320.190972222219</v>
       </c>
       <c r="F314" s="5" t="s">
         <v>47</v>
@@ -7968,19 +7954,19 @@
     </row>
     <row r="315" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A315" s="3">
-        <v>314</v>
+        <v>332</v>
       </c>
       <c r="B315" t="s">
-        <v>333</v>
+        <v>351</v>
       </c>
       <c r="C315" t="s">
         <v>9</v>
       </c>
       <c r="D315" t="s">
-        <v>333</v>
+        <v>351</v>
       </c>
       <c r="E315" s="8">
-        <v>46316.899305555547</v>
+        <v>46320.274305555547</v>
       </c>
       <c r="F315" s="5" t="s">
         <v>47</v>
@@ -7988,19 +7974,19 @@
     </row>
     <row r="316" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A316" s="3">
-        <v>315</v>
+        <v>333</v>
       </c>
       <c r="B316" t="s">
-        <v>334</v>
+        <v>352</v>
       </c>
       <c r="C316" t="s">
         <v>9</v>
       </c>
       <c r="D316" t="s">
-        <v>334</v>
+        <v>352</v>
       </c>
       <c r="E316" s="8">
-        <v>46317.024305555547</v>
+        <v>46320.732638888891</v>
       </c>
       <c r="F316" s="5" t="s">
         <v>47</v>
@@ -8008,19 +7994,19 @@
     </row>
     <row r="317" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A317" s="3">
-        <v>316</v>
+        <v>334</v>
       </c>
       <c r="B317" t="s">
-        <v>335</v>
+        <v>353</v>
       </c>
       <c r="C317" t="s">
         <v>9</v>
       </c>
       <c r="D317" t="s">
-        <v>335</v>
+        <v>353</v>
       </c>
       <c r="E317" s="8">
-        <v>46317.190972222219</v>
+        <v>46320.899305555547</v>
       </c>
       <c r="F317" s="5" t="s">
         <v>47</v>
@@ -8028,19 +8014,19 @@
     </row>
     <row r="318" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A318" s="3">
-        <v>317</v>
+        <v>335</v>
       </c>
       <c r="B318" t="s">
-        <v>336</v>
+        <v>354</v>
       </c>
       <c r="C318" t="s">
         <v>9</v>
       </c>
       <c r="D318" t="s">
-        <v>336</v>
+        <v>354</v>
       </c>
       <c r="E318" s="8">
-        <v>46317.274305555547</v>
+        <v>46321.024305555547</v>
       </c>
       <c r="F318" s="5" t="s">
         <v>47</v>
@@ -8048,19 +8034,19 @@
     </row>
     <row r="319" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A319" s="3">
-        <v>318</v>
+        <v>336</v>
       </c>
       <c r="B319" t="s">
-        <v>337</v>
+        <v>355</v>
       </c>
       <c r="C319" t="s">
         <v>9</v>
       </c>
       <c r="D319" t="s">
-        <v>337</v>
+        <v>355</v>
       </c>
       <c r="E319" s="8">
-        <v>46317.732638888891</v>
+        <v>46321.190972222219</v>
       </c>
       <c r="F319" s="5" t="s">
         <v>47</v>
@@ -8068,19 +8054,19 @@
     </row>
     <row r="320" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A320" s="3">
-        <v>319</v>
+        <v>337</v>
       </c>
       <c r="B320" t="s">
-        <v>338</v>
+        <v>356</v>
       </c>
       <c r="C320" t="s">
         <v>9</v>
       </c>
       <c r="D320" t="s">
-        <v>338</v>
+        <v>356</v>
       </c>
       <c r="E320" s="8">
-        <v>46317.899305555547</v>
+        <v>46321.274305555547</v>
       </c>
       <c r="F320" s="5" t="s">
         <v>47</v>
@@ -8088,19 +8074,19 @@
     </row>
     <row r="321" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A321" s="3">
-        <v>320</v>
+        <v>338</v>
       </c>
       <c r="B321" t="s">
-        <v>339</v>
+        <v>357</v>
       </c>
       <c r="C321" t="s">
         <v>9</v>
       </c>
       <c r="D321" t="s">
-        <v>339</v>
+        <v>357</v>
       </c>
       <c r="E321" s="8">
-        <v>46318.024305555547</v>
+        <v>46321.732638888891</v>
       </c>
       <c r="F321" s="5" t="s">
         <v>47</v>
@@ -8108,19 +8094,19 @@
     </row>
     <row r="322" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A322" s="3">
-        <v>321</v>
+        <v>339</v>
       </c>
       <c r="B322" t="s">
-        <v>340</v>
+        <v>358</v>
       </c>
       <c r="C322" t="s">
         <v>9</v>
       </c>
       <c r="D322" t="s">
-        <v>340</v>
+        <v>358</v>
       </c>
       <c r="E322" s="8">
-        <v>46318.190972222219</v>
+        <v>46321.899305555547</v>
       </c>
       <c r="F322" s="5" t="s">
         <v>47</v>
@@ -8128,19 +8114,19 @@
     </row>
     <row r="323" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A323" s="3">
-        <v>322</v>
+        <v>340</v>
       </c>
       <c r="B323" t="s">
-        <v>341</v>
+        <v>359</v>
       </c>
       <c r="C323" t="s">
         <v>9</v>
       </c>
       <c r="D323" t="s">
-        <v>341</v>
-      </c>
-      <c r="E323" s="8">
-        <v>46318.274305555547</v>
+        <v>359</v>
+      </c>
+      <c r="E323" s="4">
+        <v>46322.024305555547</v>
       </c>
       <c r="F323" s="5" t="s">
         <v>47</v>
@@ -8148,19 +8134,19 @@
     </row>
     <row r="324" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A324" s="3">
-        <v>323</v>
+        <v>341</v>
       </c>
       <c r="B324" t="s">
-        <v>342</v>
+        <v>360</v>
       </c>
       <c r="C324" t="s">
         <v>9</v>
       </c>
       <c r="D324" t="s">
-        <v>342</v>
-      </c>
-      <c r="E324" s="8">
-        <v>46318.732638888891</v>
+        <v>360</v>
+      </c>
+      <c r="E324" s="4">
+        <v>46322.190972222219</v>
       </c>
       <c r="F324" s="5" t="s">
         <v>47</v>
@@ -8168,19 +8154,19 @@
     </row>
     <row r="325" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A325" s="3">
-        <v>324</v>
+        <v>342</v>
       </c>
       <c r="B325" t="s">
-        <v>343</v>
+        <v>361</v>
       </c>
       <c r="C325" t="s">
         <v>9</v>
       </c>
       <c r="D325" t="s">
-        <v>343</v>
-      </c>
-      <c r="E325" s="8">
-        <v>46318.899305555547</v>
+        <v>361</v>
+      </c>
+      <c r="E325" s="4">
+        <v>46322.274305555547</v>
       </c>
       <c r="F325" s="5" t="s">
         <v>47</v>
@@ -8188,19 +8174,19 @@
     </row>
     <row r="326" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A326" s="3">
-        <v>325</v>
+        <v>343</v>
       </c>
       <c r="B326" t="s">
-        <v>344</v>
+        <v>362</v>
       </c>
       <c r="C326" t="s">
         <v>9</v>
       </c>
       <c r="D326" t="s">
-        <v>344</v>
-      </c>
-      <c r="E326" s="8">
-        <v>46319.024305555547</v>
+        <v>362</v>
+      </c>
+      <c r="E326" s="4">
+        <v>46322.732638888891</v>
       </c>
       <c r="F326" s="5" t="s">
         <v>47</v>
@@ -8208,19 +8194,19 @@
     </row>
     <row r="327" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A327" s="3">
-        <v>326</v>
+        <v>344</v>
       </c>
       <c r="B327" t="s">
-        <v>345</v>
+        <v>363</v>
       </c>
       <c r="C327" t="s">
         <v>9</v>
       </c>
       <c r="D327" t="s">
-        <v>345</v>
-      </c>
-      <c r="E327" s="8">
-        <v>46319.190972222219</v>
+        <v>363</v>
+      </c>
+      <c r="E327" s="4">
+        <v>46322.899305555547</v>
       </c>
       <c r="F327" s="5" t="s">
         <v>47</v>
@@ -8228,19 +8214,19 @@
     </row>
     <row r="328" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A328" s="3">
-        <v>327</v>
+        <v>345</v>
       </c>
       <c r="B328" t="s">
-        <v>346</v>
+        <v>364</v>
       </c>
       <c r="C328" t="s">
         <v>9</v>
       </c>
       <c r="D328" t="s">
-        <v>346</v>
-      </c>
-      <c r="E328" s="8">
-        <v>46319.274305555547</v>
+        <v>364</v>
+      </c>
+      <c r="E328" s="4">
+        <v>46323.024305555547</v>
       </c>
       <c r="F328" s="5" t="s">
         <v>47</v>
@@ -8248,19 +8234,19 @@
     </row>
     <row r="329" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A329" s="3">
-        <v>328</v>
+        <v>346</v>
       </c>
       <c r="B329" t="s">
-        <v>347</v>
+        <v>365</v>
       </c>
       <c r="C329" t="s">
         <v>9</v>
       </c>
       <c r="D329" t="s">
-        <v>347</v>
-      </c>
-      <c r="E329" s="8">
-        <v>46319.732638888891</v>
+        <v>365</v>
+      </c>
+      <c r="E329" s="4">
+        <v>46323.190972222219</v>
       </c>
       <c r="F329" s="5" t="s">
         <v>47</v>
@@ -8268,19 +8254,19 @@
     </row>
     <row r="330" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A330" s="3">
-        <v>329</v>
+        <v>347</v>
       </c>
       <c r="B330" t="s">
-        <v>348</v>
+        <v>366</v>
       </c>
       <c r="C330" t="s">
         <v>9</v>
       </c>
       <c r="D330" t="s">
-        <v>348</v>
-      </c>
-      <c r="E330" s="8">
-        <v>46319.899305555547</v>
+        <v>366</v>
+      </c>
+      <c r="E330" s="4">
+        <v>46323.274305555547</v>
       </c>
       <c r="F330" s="5" t="s">
         <v>47</v>
@@ -8288,19 +8274,19 @@
     </row>
     <row r="331" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A331" s="3">
-        <v>330</v>
+        <v>348</v>
       </c>
       <c r="B331" t="s">
-        <v>349</v>
+        <v>367</v>
       </c>
       <c r="C331" t="s">
         <v>9</v>
       </c>
       <c r="D331" t="s">
-        <v>349</v>
-      </c>
-      <c r="E331" s="8">
-        <v>46320.024305555547</v>
+        <v>367</v>
+      </c>
+      <c r="E331" s="4">
+        <v>46323.732638888891</v>
       </c>
       <c r="F331" s="5" t="s">
         <v>47</v>
@@ -8308,19 +8294,19 @@
     </row>
     <row r="332" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A332" s="3">
-        <v>331</v>
+        <v>349</v>
       </c>
       <c r="B332" t="s">
-        <v>350</v>
+        <v>368</v>
       </c>
       <c r="C332" t="s">
         <v>9</v>
       </c>
       <c r="D332" t="s">
-        <v>350</v>
-      </c>
-      <c r="E332" s="8">
-        <v>46320.190972222219</v>
+        <v>368</v>
+      </c>
+      <c r="E332" s="4">
+        <v>46323.899305555547</v>
       </c>
       <c r="F332" s="5" t="s">
         <v>47</v>
@@ -8328,19 +8314,19 @@
     </row>
     <row r="333" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A333" s="3">
-        <v>332</v>
+        <v>350</v>
       </c>
       <c r="B333" t="s">
-        <v>351</v>
+        <v>369</v>
       </c>
       <c r="C333" t="s">
         <v>9</v>
       </c>
       <c r="D333" t="s">
-        <v>351</v>
-      </c>
-      <c r="E333" s="8">
-        <v>46320.274305555547</v>
+        <v>369</v>
+      </c>
+      <c r="E333" s="4">
+        <v>46324.024305555547</v>
       </c>
       <c r="F333" s="5" t="s">
         <v>47</v>
@@ -8348,19 +8334,19 @@
     </row>
     <row r="334" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A334" s="3">
-        <v>333</v>
+        <v>351</v>
       </c>
       <c r="B334" t="s">
-        <v>352</v>
+        <v>370</v>
       </c>
       <c r="C334" t="s">
         <v>9</v>
       </c>
       <c r="D334" t="s">
-        <v>352</v>
-      </c>
-      <c r="E334" s="8">
-        <v>46320.732638888891</v>
+        <v>370</v>
+      </c>
+      <c r="E334" s="4">
+        <v>46324.190972222219</v>
       </c>
       <c r="F334" s="5" t="s">
         <v>47</v>
@@ -8368,19 +8354,19 @@
     </row>
     <row r="335" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A335" s="3">
-        <v>334</v>
+        <v>352</v>
       </c>
       <c r="B335" t="s">
-        <v>353</v>
+        <v>371</v>
       </c>
       <c r="C335" t="s">
         <v>9</v>
       </c>
       <c r="D335" t="s">
-        <v>353</v>
-      </c>
-      <c r="E335" s="8">
-        <v>46320.899305555547</v>
+        <v>371</v>
+      </c>
+      <c r="E335" s="4">
+        <v>46324.274305555547</v>
       </c>
       <c r="F335" s="5" t="s">
         <v>47</v>
@@ -8388,19 +8374,19 @@
     </row>
     <row r="336" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A336" s="3">
-        <v>335</v>
+        <v>353</v>
       </c>
       <c r="B336" t="s">
-        <v>354</v>
+        <v>372</v>
       </c>
       <c r="C336" t="s">
         <v>9</v>
       </c>
       <c r="D336" t="s">
-        <v>354</v>
-      </c>
-      <c r="E336" s="8">
-        <v>46321.024305555547</v>
+        <v>372</v>
+      </c>
+      <c r="E336" s="4">
+        <v>46324.732638888891</v>
       </c>
       <c r="F336" s="5" t="s">
         <v>47</v>
@@ -8408,19 +8394,19 @@
     </row>
     <row r="337" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A337" s="3">
-        <v>336</v>
+        <v>354</v>
       </c>
       <c r="B337" t="s">
-        <v>355</v>
+        <v>373</v>
       </c>
       <c r="C337" t="s">
         <v>9</v>
       </c>
       <c r="D337" t="s">
-        <v>355</v>
-      </c>
-      <c r="E337" s="8">
-        <v>46321.190972222219</v>
+        <v>373</v>
+      </c>
+      <c r="E337" s="4">
+        <v>46324.899305555547</v>
       </c>
       <c r="F337" s="5" t="s">
         <v>47</v>
@@ -8428,19 +8414,19 @@
     </row>
     <row r="338" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A338" s="3">
-        <v>337</v>
+        <v>355</v>
       </c>
       <c r="B338" t="s">
-        <v>356</v>
+        <v>374</v>
       </c>
       <c r="C338" t="s">
         <v>9</v>
       </c>
       <c r="D338" t="s">
-        <v>356</v>
-      </c>
-      <c r="E338" s="8">
-        <v>46321.274305555547</v>
+        <v>374</v>
+      </c>
+      <c r="E338" s="4">
+        <v>46325.024305555547</v>
       </c>
       <c r="F338" s="5" t="s">
         <v>47</v>
@@ -8448,19 +8434,19 @@
     </row>
     <row r="339" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A339" s="3">
-        <v>338</v>
+        <v>356</v>
       </c>
       <c r="B339" t="s">
-        <v>357</v>
+        <v>375</v>
       </c>
       <c r="C339" t="s">
         <v>9</v>
       </c>
       <c r="D339" t="s">
-        <v>357</v>
-      </c>
-      <c r="E339" s="8">
-        <v>46321.732638888891</v>
+        <v>375</v>
+      </c>
+      <c r="E339" s="4">
+        <v>46325.190972222219</v>
       </c>
       <c r="F339" s="5" t="s">
         <v>47</v>
@@ -8468,19 +8454,19 @@
     </row>
     <row r="340" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A340" s="3">
-        <v>339</v>
+        <v>357</v>
       </c>
       <c r="B340" t="s">
-        <v>358</v>
+        <v>376</v>
       </c>
       <c r="C340" t="s">
         <v>9</v>
       </c>
       <c r="D340" t="s">
-        <v>358</v>
-      </c>
-      <c r="E340" s="8">
-        <v>46321.899305555547</v>
+        <v>376</v>
+      </c>
+      <c r="E340" s="4">
+        <v>46325.274305555547</v>
       </c>
       <c r="F340" s="5" t="s">
         <v>47</v>
@@ -8488,19 +8474,19 @@
     </row>
     <row r="341" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A341" s="3">
-        <v>340</v>
+        <v>358</v>
       </c>
       <c r="B341" t="s">
-        <v>359</v>
+        <v>377</v>
       </c>
       <c r="C341" t="s">
         <v>9</v>
       </c>
       <c r="D341" t="s">
-        <v>359</v>
+        <v>377</v>
       </c>
       <c r="E341" s="4">
-        <v>46322.024305555547</v>
+        <v>46325.732638888891</v>
       </c>
       <c r="F341" s="5" t="s">
         <v>47</v>
@@ -8508,19 +8494,19 @@
     </row>
     <row r="342" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A342" s="3">
-        <v>341</v>
+        <v>359</v>
       </c>
       <c r="B342" t="s">
-        <v>360</v>
+        <v>378</v>
       </c>
       <c r="C342" t="s">
         <v>9</v>
       </c>
       <c r="D342" t="s">
-        <v>360</v>
+        <v>378</v>
       </c>
       <c r="E342" s="4">
-        <v>46322.190972222219</v>
+        <v>46325.899305555547</v>
       </c>
       <c r="F342" s="5" t="s">
         <v>47</v>
@@ -8528,19 +8514,19 @@
     </row>
     <row r="343" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A343" s="3">
-        <v>342</v>
+        <v>360</v>
       </c>
       <c r="B343" t="s">
-        <v>361</v>
+        <v>379</v>
       </c>
       <c r="C343" t="s">
         <v>9</v>
       </c>
       <c r="D343" t="s">
-        <v>361</v>
+        <v>379</v>
       </c>
       <c r="E343" s="4">
-        <v>46322.274305555547</v>
+        <v>46326.024305555547</v>
       </c>
       <c r="F343" s="5" t="s">
         <v>47</v>
@@ -8548,19 +8534,19 @@
     </row>
     <row r="344" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A344" s="3">
-        <v>343</v>
+        <v>361</v>
       </c>
       <c r="B344" t="s">
-        <v>362</v>
+        <v>20</v>
       </c>
       <c r="C344" t="s">
         <v>9</v>
       </c>
       <c r="D344" t="s">
-        <v>362</v>
-      </c>
-      <c r="E344" s="4">
-        <v>46322.732638888891</v>
+        <v>20</v>
+      </c>
+      <c r="E344" s="8">
+        <v>46326.190972222219</v>
       </c>
       <c r="F344" s="5" t="s">
         <v>47</v>
@@ -8568,19 +8554,19 @@
     </row>
     <row r="345" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A345" s="3">
-        <v>344</v>
+        <v>362</v>
       </c>
       <c r="B345" t="s">
-        <v>363</v>
+        <v>21</v>
       </c>
       <c r="C345" t="s">
         <v>9</v>
       </c>
       <c r="D345" t="s">
-        <v>363</v>
-      </c>
-      <c r="E345" s="4">
-        <v>46322.899305555547</v>
+        <v>21</v>
+      </c>
+      <c r="E345" s="8">
+        <v>46326.274305555555</v>
       </c>
       <c r="F345" s="5" t="s">
         <v>47</v>
@@ -8588,19 +8574,19 @@
     </row>
     <row r="346" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A346" s="3">
-        <v>345</v>
+        <v>363</v>
       </c>
       <c r="B346" t="s">
-        <v>364</v>
+        <v>22</v>
       </c>
       <c r="C346" t="s">
         <v>9</v>
       </c>
       <c r="D346" t="s">
-        <v>364</v>
-      </c>
-      <c r="E346" s="4">
-        <v>46323.024305555547</v>
+        <v>22</v>
+      </c>
+      <c r="E346" s="8">
+        <v>46326.732638888891</v>
       </c>
       <c r="F346" s="5" t="s">
         <v>47</v>
@@ -8608,19 +8594,19 @@
     </row>
     <row r="347" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A347" s="3">
-        <v>346</v>
+        <v>364</v>
       </c>
       <c r="B347" t="s">
-        <v>365</v>
+        <v>23</v>
       </c>
       <c r="C347" t="s">
         <v>9</v>
       </c>
       <c r="D347" t="s">
-        <v>365</v>
-      </c>
-      <c r="E347" s="4">
-        <v>46323.190972222219</v>
+        <v>23</v>
+      </c>
+      <c r="E347" s="8">
+        <v>46326.899305555555</v>
       </c>
       <c r="F347" s="5" t="s">
         <v>47</v>
@@ -8628,19 +8614,19 @@
     </row>
     <row r="348" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A348" s="3">
-        <v>347</v>
+        <v>365</v>
       </c>
       <c r="B348" t="s">
-        <v>366</v>
+        <v>24</v>
       </c>
       <c r="C348" t="s">
         <v>9</v>
       </c>
       <c r="D348" t="s">
-        <v>366</v>
-      </c>
-      <c r="E348" s="4">
-        <v>46323.274305555547</v>
+        <v>24</v>
+      </c>
+      <c r="E348" s="8">
+        <v>46327.024305555555</v>
       </c>
       <c r="F348" s="5" t="s">
         <v>47</v>
@@ -8648,19 +8634,19 @@
     </row>
     <row r="349" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A349" s="3">
-        <v>348</v>
+        <v>366</v>
       </c>
       <c r="B349" t="s">
-        <v>367</v>
+        <v>25</v>
       </c>
       <c r="C349" t="s">
         <v>9</v>
       </c>
       <c r="D349" t="s">
-        <v>367</v>
-      </c>
-      <c r="E349" s="4">
-        <v>46323.732638888891</v>
+        <v>25</v>
+      </c>
+      <c r="E349" s="8">
+        <v>46327.190972222219</v>
       </c>
       <c r="F349" s="5" t="s">
         <v>47</v>
@@ -8668,19 +8654,19 @@
     </row>
     <row r="350" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A350" s="3">
-        <v>349</v>
+        <v>367</v>
       </c>
       <c r="B350" t="s">
-        <v>368</v>
+        <v>28</v>
       </c>
       <c r="C350" t="s">
         <v>9</v>
       </c>
       <c r="D350" t="s">
-        <v>368</v>
-      </c>
-      <c r="E350" s="4">
-        <v>46323.899305555547</v>
+        <v>28</v>
+      </c>
+      <c r="E350" s="8">
+        <v>46327.274305555555</v>
       </c>
       <c r="F350" s="5" t="s">
         <v>47</v>
@@ -8688,19 +8674,19 @@
     </row>
     <row r="351" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A351" s="3">
-        <v>350</v>
+        <v>368</v>
       </c>
       <c r="B351" t="s">
-        <v>369</v>
+        <v>29</v>
       </c>
       <c r="C351" t="s">
         <v>9</v>
       </c>
       <c r="D351" t="s">
-        <v>369</v>
-      </c>
-      <c r="E351" s="4">
-        <v>46324.024305555547</v>
+        <v>29</v>
+      </c>
+      <c r="E351" s="8">
+        <v>46327.732638888891</v>
       </c>
       <c r="F351" s="5" t="s">
         <v>47</v>
@@ -8708,19 +8694,19 @@
     </row>
     <row r="352" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A352" s="3">
-        <v>351</v>
+        <v>369</v>
       </c>
       <c r="B352" t="s">
-        <v>370</v>
+        <v>32</v>
       </c>
       <c r="C352" t="s">
         <v>9</v>
       </c>
       <c r="D352" t="s">
-        <v>370</v>
-      </c>
-      <c r="E352" s="4">
-        <v>46324.190972222219</v>
+        <v>32</v>
+      </c>
+      <c r="E352" s="8">
+        <v>46327.899305555555</v>
       </c>
       <c r="F352" s="5" t="s">
         <v>47</v>
@@ -8728,19 +8714,19 @@
     </row>
     <row r="353" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A353" s="3">
-        <v>352</v>
+        <v>370</v>
       </c>
       <c r="B353" t="s">
-        <v>371</v>
+        <v>33</v>
       </c>
       <c r="C353" t="s">
         <v>9</v>
       </c>
       <c r="D353" t="s">
-        <v>371</v>
-      </c>
-      <c r="E353" s="4">
-        <v>46324.274305555547</v>
+        <v>33</v>
+      </c>
+      <c r="E353" s="8">
+        <v>46328.024305555555</v>
       </c>
       <c r="F353" s="5" t="s">
         <v>47</v>
@@ -8748,19 +8734,19 @@
     </row>
     <row r="354" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A354" s="3">
-        <v>353</v>
+        <v>371</v>
       </c>
       <c r="B354" t="s">
-        <v>372</v>
+        <v>34</v>
       </c>
       <c r="C354" t="s">
         <v>9</v>
       </c>
       <c r="D354" t="s">
-        <v>372</v>
-      </c>
-      <c r="E354" s="4">
-        <v>46324.732638888891</v>
+        <v>34</v>
+      </c>
+      <c r="E354" s="8">
+        <v>46328.190972222219</v>
       </c>
       <c r="F354" s="5" t="s">
         <v>47</v>
@@ -8768,19 +8754,19 @@
     </row>
     <row r="355" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A355" s="3">
-        <v>354</v>
+        <v>372</v>
       </c>
       <c r="B355" t="s">
-        <v>373</v>
+        <v>37</v>
       </c>
       <c r="C355" t="s">
         <v>9</v>
       </c>
       <c r="D355" t="s">
-        <v>373</v>
-      </c>
-      <c r="E355" s="4">
-        <v>46324.899305555547</v>
+        <v>37</v>
+      </c>
+      <c r="E355" s="8">
+        <v>46328.274305555555</v>
       </c>
       <c r="F355" s="5" t="s">
         <v>47</v>
@@ -8788,19 +8774,19 @@
     </row>
     <row r="356" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A356" s="3">
-        <v>355</v>
+        <v>373</v>
       </c>
       <c r="B356" t="s">
-        <v>374</v>
+        <v>38</v>
       </c>
       <c r="C356" t="s">
         <v>9</v>
       </c>
       <c r="D356" t="s">
-        <v>374</v>
-      </c>
-      <c r="E356" s="4">
-        <v>46325.024305555547</v>
+        <v>38</v>
+      </c>
+      <c r="E356" s="8">
+        <v>46328.732638888891</v>
       </c>
       <c r="F356" s="5" t="s">
         <v>47</v>
@@ -8808,19 +8794,19 @@
     </row>
     <row r="357" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A357" s="3">
-        <v>356</v>
+        <v>374</v>
       </c>
       <c r="B357" t="s">
-        <v>375</v>
+        <v>41</v>
       </c>
       <c r="C357" t="s">
         <v>9</v>
       </c>
       <c r="D357" t="s">
-        <v>375</v>
-      </c>
-      <c r="E357" s="4">
-        <v>46325.190972222219</v>
+        <v>41</v>
+      </c>
+      <c r="E357" s="8">
+        <v>46328.899305555555</v>
       </c>
       <c r="F357" s="5" t="s">
         <v>47</v>
@@ -8828,19 +8814,19 @@
     </row>
     <row r="358" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A358" s="3">
-        <v>357</v>
+        <v>375</v>
       </c>
       <c r="B358" t="s">
-        <v>376</v>
+        <v>42</v>
       </c>
       <c r="C358" t="s">
         <v>9</v>
       </c>
       <c r="D358" t="s">
-        <v>376</v>
-      </c>
-      <c r="E358" s="4">
-        <v>46325.274305555547</v>
+        <v>42</v>
+      </c>
+      <c r="E358" s="8">
+        <v>46329.024305555555</v>
       </c>
       <c r="F358" s="5" t="s">
         <v>47</v>
@@ -8848,19 +8834,19 @@
     </row>
     <row r="359" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A359" s="3">
-        <v>358</v>
+        <v>376</v>
       </c>
       <c r="B359" t="s">
-        <v>377</v>
+        <v>43</v>
       </c>
       <c r="C359" t="s">
         <v>9</v>
       </c>
       <c r="D359" t="s">
-        <v>377</v>
-      </c>
-      <c r="E359" s="4">
-        <v>46325.732638888891</v>
+        <v>43</v>
+      </c>
+      <c r="E359" s="8">
+        <v>46329.190972222219</v>
       </c>
       <c r="F359" s="5" t="s">
         <v>47</v>
@@ -8868,19 +8854,19 @@
     </row>
     <row r="360" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A360" s="3">
-        <v>359</v>
+        <v>377</v>
       </c>
       <c r="B360" t="s">
-        <v>378</v>
+        <v>44</v>
       </c>
       <c r="C360" t="s">
         <v>9</v>
       </c>
       <c r="D360" t="s">
-        <v>378</v>
-      </c>
-      <c r="E360" s="4">
-        <v>46325.899305555547</v>
+        <v>44</v>
+      </c>
+      <c r="E360" s="8">
+        <v>46329.274305555555</v>
       </c>
       <c r="F360" s="5" t="s">
         <v>47</v>
@@ -8888,19 +8874,19 @@
     </row>
     <row r="361" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A361" s="3">
-        <v>360</v>
+        <v>378</v>
       </c>
       <c r="B361" t="s">
-        <v>379</v>
+        <v>45</v>
       </c>
       <c r="C361" t="s">
         <v>9</v>
       </c>
       <c r="D361" t="s">
-        <v>379</v>
-      </c>
-      <c r="E361" s="4">
-        <v>46326.024305555547</v>
+        <v>45</v>
+      </c>
+      <c r="E361" s="8">
+        <v>46259.550694444442</v>
       </c>
       <c r="F361" s="5" t="s">
         <v>47</v>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -926,9 +926,14 @@
       <c r="E11" s="8" t="n">
         <v>46259.73263888889</v>
       </c>
-      <c r="F11" s="5" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F11" s="9" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>1646324223766581</t>
         </is>
       </c>
     </row>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -959,9 +959,14 @@
       <c r="E12" s="8" t="n">
         <v>46259.89930555555</v>
       </c>
-      <c r="F12" s="5" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F12" s="9" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>1047002248202981</t>
         </is>
       </c>
     </row>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -992,9 +992,14 @@
       <c r="E13" s="8" t="n">
         <v>46260.02430555555</v>
       </c>
-      <c r="F13" s="5" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F13" s="9" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>1615012526848897</t>
         </is>
       </c>
     </row>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -1025,9 +1025,14 @@
       <c r="E14" s="8" t="n">
         <v>46260.19097222222</v>
       </c>
-      <c r="F14" s="5" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F14" s="9" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>1062786846385426</t>
         </is>
       </c>
     </row>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -1058,9 +1058,14 @@
       <c r="E15" s="8" t="n">
         <v>46260.27430555555</v>
       </c>
-      <c r="F15" s="5" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F15" s="9" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>1816175539746948</t>
         </is>
       </c>
     </row>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -1091,9 +1091,14 @@
       <c r="E16" s="8" t="n">
         <v>46260.73263888889</v>
       </c>
-      <c r="F16" s="5" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F16" s="9" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>1382482490709244</t>
         </is>
       </c>
     </row>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -1124,9 +1124,14 @@
       <c r="E17" s="8" t="n">
         <v>46260.89930555555</v>
       </c>
-      <c r="F17" s="5" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F17" s="9" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>1379537594271169</t>
         </is>
       </c>
     </row>
@@ -1152,9 +1157,14 @@
       <c r="E18" s="8" t="n">
         <v>46261.02430555555</v>
       </c>
-      <c r="F18" s="5" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F18" s="9" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>968006099647991</t>
         </is>
       </c>
     </row>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -1190,9 +1190,14 @@
       <c r="E19" s="8" t="n">
         <v>46261.19097222222</v>
       </c>
-      <c r="F19" s="5" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F19" s="9" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>1400278515654769</t>
         </is>
       </c>
     </row>
@@ -1218,9 +1223,14 @@
       <c r="E20" s="8" t="n">
         <v>46261.27430555555</v>
       </c>
-      <c r="F20" s="5" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F20" s="9" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>2073696469925810</t>
         </is>
       </c>
     </row>
@@ -1246,9 +1256,14 @@
       <c r="E21" s="8" t="n">
         <v>46261.73263888889</v>
       </c>
-      <c r="F21" s="5" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F21" s="9" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>4471600019781352</t>
         </is>
       </c>
     </row>
@@ -1274,9 +1289,14 @@
       <c r="E22" s="8" t="n">
         <v>46261.89930555555</v>
       </c>
-      <c r="F22" s="5" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F22" s="9" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>1419803220066211</t>
         </is>
       </c>
     </row>
@@ -1302,9 +1322,14 @@
       <c r="E23" s="8" t="n">
         <v>46262.02430555555</v>
       </c>
-      <c r="F23" s="5" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F23" s="9" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>980542901712984</t>
         </is>
       </c>
     </row>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -1355,9 +1355,14 @@
       <c r="E24" s="8" t="n">
         <v>46262.19097222222</v>
       </c>
-      <c r="F24" s="5" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F24" s="9" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>2855201134836150</t>
         </is>
       </c>
     </row>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -1388,9 +1388,14 @@
       <c r="E25" s="8" t="n">
         <v>46262.27430555555</v>
       </c>
-      <c r="F25" s="5" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F25" s="9" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>1085127460839377</t>
         </is>
       </c>
     </row>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -1421,9 +1421,14 @@
       <c r="E26" s="8" t="n">
         <v>46262.73263888889</v>
       </c>
-      <c r="F26" s="5" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F26" s="9" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>1090753636803513</t>
         </is>
       </c>
     </row>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -1454,9 +1454,14 @@
       <c r="E27" s="8" t="n">
         <v>46262.89930555555</v>
       </c>
-      <c r="F27" s="5" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F27" s="9" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>4614832588736792</t>
         </is>
       </c>
     </row>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -1487,9 +1487,14 @@
       <c r="E28" s="8" t="n">
         <v>46263.02430555555</v>
       </c>
-      <c r="F28" s="5" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F28" s="9" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>2174044776788088</t>
         </is>
       </c>
     </row>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -1520,9 +1520,14 @@
       <c r="E29" s="8" t="n">
         <v>46263.19097222222</v>
       </c>
-      <c r="F29" s="5" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F29" s="9" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>907291235369614</t>
         </is>
       </c>
     </row>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -1553,9 +1553,14 @@
       <c r="E30" s="8" t="n">
         <v>46263.27430555555</v>
       </c>
-      <c r="F30" s="5" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F30" s="9" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>1067905262838785</t>
         </is>
       </c>
     </row>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -1586,9 +1586,14 @@
       <c r="E31" s="8" t="n">
         <v>46263.73263888889</v>
       </c>
-      <c r="F31" s="5" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F31" s="9" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>2133895374199090</t>
         </is>
       </c>
     </row>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -1619,9 +1619,14 @@
       <c r="E32" s="8" t="n">
         <v>46263.89930555555</v>
       </c>
-      <c r="F32" s="5" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F32" s="9" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>1079209528090418</t>
         </is>
       </c>
     </row>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -1652,9 +1652,14 @@
       <c r="E33" s="8" t="n">
         <v>46264.02430555555</v>
       </c>
-      <c r="F33" s="5" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F33" s="9" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>4116794568560002</t>
         </is>
       </c>
     </row>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -1685,9 +1685,14 @@
       <c r="E34" s="8" t="n">
         <v>46264.19097222222</v>
       </c>
-      <c r="F34" s="5" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F34" s="9" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>1039989652276235</t>
         </is>
       </c>
     </row>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -1718,9 +1718,14 @@
       <c r="E35" s="8" t="n">
         <v>46264.27430555555</v>
       </c>
-      <c r="F35" s="5" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F35" s="9" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>1598966401973632</t>
         </is>
       </c>
     </row>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -1751,9 +1751,14 @@
       <c r="E36" s="8" t="n">
         <v>46264.73263888889</v>
       </c>
-      <c r="F36" s="5" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F36" s="9" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>1396883642588299</t>
         </is>
       </c>
     </row>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -1784,9 +1784,14 @@
       <c r="E37" s="8" t="n">
         <v>46264.89930555555</v>
       </c>
-      <c r="F37" s="5" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F37" s="9" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>1567924141466326</t>
         </is>
       </c>
     </row>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -1817,9 +1817,14 @@
       <c r="E38" s="8" t="n">
         <v>46265.02430555555</v>
       </c>
-      <c r="F38" s="5" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F38" s="9" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>1572277541219176</t>
         </is>
       </c>
     </row>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -1850,9 +1850,14 @@
       <c r="E39" s="8" t="n">
         <v>46265.19097222222</v>
       </c>
-      <c r="F39" s="5" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F39" s="9" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>2137360753541075</t>
         </is>
       </c>
     </row>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -1883,9 +1883,14 @@
       <c r="E40" s="8" t="n">
         <v>46265.27430555555</v>
       </c>
-      <c r="F40" s="5" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F40" s="9" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>1736670857607205</t>
         </is>
       </c>
     </row>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -1916,9 +1916,14 @@
       <c r="E41" s="8" t="n">
         <v>46265.73263888889</v>
       </c>
-      <c r="F41" s="5" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F41" s="9" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>1064608329695536</t>
         </is>
       </c>
     </row>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -1949,9 +1949,14 @@
       <c r="E42" s="8" t="n">
         <v>46265.89930555555</v>
       </c>
-      <c r="F42" s="5" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F42" s="9" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>2163443604573755</t>
         </is>
       </c>
     </row>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -1982,9 +1982,14 @@
       <c r="E43" s="8" t="n">
         <v>46266.02430555555</v>
       </c>
-      <c r="F43" s="5" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F43" s="9" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>1058196437058595</t>
         </is>
       </c>
     </row>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -2015,9 +2015,14 @@
       <c r="E44" s="8" t="n">
         <v>46266.19097222222</v>
       </c>
-      <c r="F44" s="5" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F44" s="9" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>3201225746733554</t>
         </is>
       </c>
     </row>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -2048,9 +2048,14 @@
       <c r="E45" s="8" t="n">
         <v>46266.27430555555</v>
       </c>
-      <c r="F45" s="5" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F45" s="9" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>4539112076362200</t>
         </is>
       </c>
     </row>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -2081,9 +2081,14 @@
       <c r="E46" s="8" t="n">
         <v>46266.73263888889</v>
       </c>
-      <c r="F46" s="5" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F46" s="9" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>1593836635578182</t>
         </is>
       </c>
     </row>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -2114,9 +2114,14 @@
       <c r="E47" s="8" t="n">
         <v>46266.89930555555</v>
       </c>
-      <c r="F47" s="5" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F47" s="9" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>1258549729689236</t>
         </is>
       </c>
     </row>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -2147,9 +2147,14 @@
       <c r="E48" s="8" t="n">
         <v>46267.02430555555</v>
       </c>
-      <c r="F48" s="5" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F48" s="9" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>2139559523580951</t>
         </is>
       </c>
     </row>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -2180,9 +2180,14 @@
       <c r="E49" s="8" t="n">
         <v>46267.19097222222</v>
       </c>
-      <c r="F49" s="5" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F49" s="9" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>1678892823174881</t>
         </is>
       </c>
     </row>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -2213,9 +2213,14 @@
       <c r="E50" s="8" t="n">
         <v>46267.27430555555</v>
       </c>
-      <c r="F50" s="5" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F50" s="9" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>1804551430561401</t>
         </is>
       </c>
     </row>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -2246,9 +2246,14 @@
       <c r="E51" s="8" t="n">
         <v>46267.73263888889</v>
       </c>
-      <c r="F51" s="5" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F51" s="9" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>2073641000185170</t>
         </is>
       </c>
     </row>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -2279,9 +2279,14 @@
       <c r="E52" s="8" t="n">
         <v>46267.89930555555</v>
       </c>
-      <c r="F52" s="5" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F52" s="9" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>4288456228037977</t>
         </is>
       </c>
     </row>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -2312,9 +2312,14 @@
       <c r="E53" s="8" t="n">
         <v>46268.02430555555</v>
       </c>
-      <c r="F53" s="5" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F53" s="9" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>28175876455366384</t>
         </is>
       </c>
     </row>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -2345,9 +2345,14 @@
       <c r="E54" s="8" t="n">
         <v>46268.19097222222</v>
       </c>
-      <c r="F54" s="5" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F54" s="9" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>1304310124972815</t>
         </is>
       </c>
     </row>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -2378,9 +2378,14 @@
       <c r="E55" s="8" t="n">
         <v>46268.27430555555</v>
       </c>
-      <c r="F55" s="5" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F55" s="9" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>1420847559971959</t>
         </is>
       </c>
     </row>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -2411,9 +2411,14 @@
       <c r="E56" s="8" t="n">
         <v>46268.73263888889</v>
       </c>
-      <c r="F56" s="5" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F56" s="9" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>2496659557512410</t>
         </is>
       </c>
     </row>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -2444,9 +2444,14 @@
       <c r="E57" s="8" t="n">
         <v>46268.89930555555</v>
       </c>
-      <c r="F57" s="5" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F57" s="9" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>1756571608990330</t>
         </is>
       </c>
     </row>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -2477,9 +2477,14 @@
       <c r="E58" s="8" t="n">
         <v>46269.02430555555</v>
       </c>
-      <c r="F58" s="5" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F58" s="9" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>1785272012616969</t>
         </is>
       </c>
     </row>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -2510,9 +2510,14 @@
       <c r="E59" s="8" t="n">
         <v>46269.19097222222</v>
       </c>
-      <c r="F59" s="5" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F59" s="9" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>1385666956342574</t>
         </is>
       </c>
     </row>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -2543,9 +2543,14 @@
       <c r="E60" s="8" t="n">
         <v>46269.27430555555</v>
       </c>
-      <c r="F60" s="5" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F60" s="9" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>1048882681095596</t>
         </is>
       </c>
     </row>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -2576,9 +2576,14 @@
       <c r="E61" s="8" t="n">
         <v>46269.73263888889</v>
       </c>
-      <c r="F61" s="5" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F61" s="9" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>982462961524932</t>
         </is>
       </c>
     </row>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -2609,9 +2609,14 @@
       <c r="E62" s="8" t="n">
         <v>46269.89930555555</v>
       </c>
-      <c r="F62" s="5" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F62" s="9" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>1419232680133570</t>
         </is>
       </c>
     </row>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -2642,9 +2642,14 @@
       <c r="E63" s="8" t="n">
         <v>46270.02430555555</v>
       </c>
-      <c r="F63" s="5" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F63" s="9" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>28013474495014024</t>
         </is>
       </c>
     </row>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -2675,9 +2675,14 @@
       <c r="E64" s="8" t="n">
         <v>46270.19097222222</v>
       </c>
-      <c r="F64" s="5" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F64" s="9" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>1404208468575430</t>
         </is>
       </c>
     </row>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -2708,9 +2708,14 @@
       <c r="E65" s="8" t="n">
         <v>46270.27430555555</v>
       </c>
-      <c r="F65" s="5" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F65" s="9" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>26425083827189596</t>
         </is>
       </c>
     </row>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -2741,9 +2741,14 @@
       <c r="E66" s="8" t="n">
         <v>46270.73263888889</v>
       </c>
-      <c r="F66" s="5" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F66" s="9" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>2129862514582162</t>
         </is>
       </c>
     </row>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -2774,9 +2774,14 @@
       <c r="E67" s="8" t="n">
         <v>46270.89930555555</v>
       </c>
-      <c r="F67" s="5" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F67" s="9" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>947197624407908</t>
         </is>
       </c>
     </row>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -2807,9 +2807,14 @@
       <c r="E68" s="8" t="n">
         <v>46271.02430555555</v>
       </c>
-      <c r="F68" s="5" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F68" s="9" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>1473374134597979</t>
         </is>
       </c>
     </row>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -2840,9 +2840,14 @@
       <c r="E69" s="8" t="n">
         <v>46271.19097222222</v>
       </c>
-      <c r="F69" s="5" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F69" s="9" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>2051680028787120</t>
         </is>
       </c>
     </row>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -2873,9 +2873,14 @@
       <c r="E70" s="8" t="n">
         <v>46271.27430555555</v>
       </c>
-      <c r="F70" s="5" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F70" s="9" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>1086491677181245</t>
         </is>
       </c>
     </row>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -2906,9 +2906,14 @@
       <c r="E71" s="8" t="n">
         <v>46271.73263888889</v>
       </c>
-      <c r="F71" s="5" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F71" s="9" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>1394389685401415</t>
         </is>
       </c>
     </row>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -2939,9 +2939,14 @@
       <c r="E72" s="8" t="n">
         <v>46271.89930555555</v>
       </c>
-      <c r="F72" s="5" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F72" s="9" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>2267320717451422</t>
         </is>
       </c>
     </row>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -2972,9 +2972,14 @@
       <c r="E73" s="8" t="n">
         <v>46272.02430555555</v>
       </c>
-      <c r="F73" s="5" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F73" s="9" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>1298651812230409</t>
         </is>
       </c>
     </row>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -3005,9 +3005,14 @@
       <c r="E74" s="8" t="n">
         <v>46272.19097222222</v>
       </c>
-      <c r="F74" s="5" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F74" s="9" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>1746213196500528</t>
         </is>
       </c>
     </row>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -3038,9 +3038,14 @@
       <c r="E75" s="4" t="n">
         <v>46272.27430555555</v>
       </c>
-      <c r="F75" s="5" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F75" s="9" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>2563718630793892</t>
         </is>
       </c>
     </row>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -3071,9 +3071,14 @@
       <c r="E76" s="8" t="n">
         <v>46272.73263888889</v>
       </c>
-      <c r="F76" s="5" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F76" s="9" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>2316768615820664</t>
         </is>
       </c>
     </row>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -3104,9 +3104,14 @@
       <c r="E77" s="8" t="n">
         <v>46272.89930555555</v>
       </c>
-      <c r="F77" s="5" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F77" s="9" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>1359269679623433</t>
         </is>
       </c>
     </row>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -3137,9 +3137,14 @@
       <c r="E78" s="4" t="n">
         <v>46273.02430555555</v>
       </c>
-      <c r="F78" s="5" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F78" s="9" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>1053978303924003</t>
         </is>
       </c>
     </row>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -3170,9 +3170,14 @@
       <c r="E79" s="8" t="n">
         <v>46273.19097222222</v>
       </c>
-      <c r="F79" s="5" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F79" s="9" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>1080144327756179</t>
         </is>
       </c>
     </row>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -3203,9 +3203,14 @@
       <c r="E80" s="8" t="n">
         <v>46273.27430555555</v>
       </c>
-      <c r="F80" s="5" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F80" s="9" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>895302933443322</t>
         </is>
       </c>
     </row>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -3236,9 +3236,14 @@
       <c r="E81" s="8" t="n">
         <v>46273.73263888889</v>
       </c>
-      <c r="F81" s="5" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F81" s="9" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>922268853935443</t>
         </is>
       </c>
     </row>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -3269,9 +3269,14 @@
       <c r="E82" s="8" t="n">
         <v>46273.89930555555</v>
       </c>
-      <c r="F82" s="5" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F82" s="9" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>1372133198244009</t>
         </is>
       </c>
     </row>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -3302,9 +3302,14 @@
       <c r="E83" s="8" t="n">
         <v>46274.02430555555</v>
       </c>
-      <c r="F83" s="5" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F83" s="9" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>909436105259162</t>
         </is>
       </c>
     </row>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -3335,9 +3335,14 @@
       <c r="E84" s="8" t="n">
         <v>46274.19097222222</v>
       </c>
-      <c r="F84" s="5" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F84" s="9" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>3018709178481737</t>
         </is>
       </c>
     </row>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -3368,9 +3368,14 @@
       <c r="E85" s="8" t="n">
         <v>46274.27430555555</v>
       </c>
-      <c r="F85" s="5" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F85" s="9" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>1755290962459717</t>
         </is>
       </c>
     </row>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -3401,9 +3401,14 @@
       <c r="E86" s="8" t="n">
         <v>46274.73263888889</v>
       </c>
-      <c r="F86" s="5" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F86" s="9" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>1642425400781784</t>
         </is>
       </c>
     </row>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -3434,9 +3434,14 @@
       <c r="E87" s="8" t="n">
         <v>46274.89930555555</v>
       </c>
-      <c r="F87" s="5" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F87" s="9" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>1557932209714304</t>
         </is>
       </c>
     </row>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -3467,9 +3467,14 @@
       <c r="E88" s="8" t="n">
         <v>46275.02430555555</v>
       </c>
-      <c r="F88" s="5" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F88" s="9" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>917400074362114</t>
         </is>
       </c>
     </row>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -3500,9 +3500,14 @@
       <c r="E89" s="8" t="n">
         <v>46275.19097222222</v>
       </c>
-      <c r="F89" s="5" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F89" s="9" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>1524217346417974</t>
         </is>
       </c>
     </row>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -3533,9 +3533,14 @@
       <c r="E90" s="8" t="n">
         <v>46275.27430555555</v>
       </c>
-      <c r="F90" s="5" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F90" s="9" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>1786620899082634</t>
         </is>
       </c>
     </row>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -3566,9 +3566,14 @@
       <c r="E91" s="8" t="n">
         <v>46275.73263888889</v>
       </c>
-      <c r="F91" s="5" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F91" s="9" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>1742854766766698</t>
         </is>
       </c>
     </row>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -3599,9 +3599,14 @@
       <c r="E92" s="8" t="n">
         <v>46275.89930555555</v>
       </c>
-      <c r="F92" s="5" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F92" s="9" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>2284437472097805</t>
         </is>
       </c>
     </row>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -3632,9 +3632,14 @@
       <c r="E93" s="8" t="n">
         <v>46276.02430555555</v>
       </c>
-      <c r="F93" s="5" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F93" s="9" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>1460415132586579</t>
         </is>
       </c>
     </row>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -3665,9 +3665,14 @@
       <c r="E94" s="8" t="n">
         <v>46276.19097222222</v>
       </c>
-      <c r="F94" s="5" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F94" s="9" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>1611974423667933</t>
         </is>
       </c>
     </row>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -3698,9 +3698,14 @@
       <c r="E95" s="8" t="n">
         <v>46276.27430555555</v>
       </c>
-      <c r="F95" s="5" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F95" s="9" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>28102537296039518</t>
         </is>
       </c>
     </row>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -3731,9 +3731,14 @@
       <c r="E96" s="8" t="n">
         <v>46276.73263888889</v>
       </c>
-      <c r="F96" s="5" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F96" s="9" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>1406287518309106</t>
         </is>
       </c>
     </row>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -3764,9 +3764,14 @@
       <c r="E97" s="8" t="n">
         <v>46276.89930555555</v>
       </c>
-      <c r="F97" s="5" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F97" s="9" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>1366276569053084</t>
         </is>
       </c>
     </row>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -3797,9 +3797,14 @@
       <c r="E98" s="8" t="n">
         <v>46277.02430555555</v>
       </c>
-      <c r="F98" s="5" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F98" s="9" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>4430244680521630</t>
         </is>
       </c>
     </row>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -3830,9 +3830,14 @@
       <c r="E99" s="8" t="n">
         <v>46277.19097222222</v>
       </c>
-      <c r="F99" s="5" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F99" s="9" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>2327556814742228</t>
         </is>
       </c>
     </row>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -3863,9 +3863,14 @@
       <c r="E100" s="8" t="n">
         <v>46277.27430555555</v>
       </c>
-      <c r="F100" s="5" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F100" s="9" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>1067029562857050</t>
         </is>
       </c>
     </row>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -3896,9 +3896,14 @@
       <c r="E101" s="8" t="n">
         <v>46277.73263888889</v>
       </c>
-      <c r="F101" s="5" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F101" s="9" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>1075291931785354</t>
         </is>
       </c>
     </row>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -3929,9 +3929,14 @@
       <c r="E102" s="8" t="n">
         <v>46277.89930555555</v>
       </c>
-      <c r="F102" s="5" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F102" s="9" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>1583058649944531</t>
         </is>
       </c>
     </row>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -3962,9 +3962,14 @@
       <c r="E103" s="8" t="n">
         <v>46278.02430555555</v>
       </c>
-      <c r="F103" s="5" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F103" s="9" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>2386704088524492</t>
         </is>
       </c>
     </row>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -3995,9 +3995,14 @@
       <c r="E104" s="8" t="n">
         <v>46278.19097222222</v>
       </c>
-      <c r="F104" s="5" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F104" s="9" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>2833096440402280</t>
         </is>
       </c>
     </row>

--- a/facebook_content_calendar.xlsx
+++ b/facebook_content_calendar.xlsx
@@ -4028,9 +4028,14 @@
       <c r="E105" s="8" t="n">
         <v>46278.27430555555</v>
       </c>
-      <c r="F105" s="5" t="inlineStr">
-        <is>
-          <t>Pending</t>
+      <c r="F105" s="9" t="inlineStr">
+        <is>
+          <t>Done</t>
+        </is>
+      </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>1012718891828961</t>
         </is>
       </c>
     </row>
